--- a/data/paper_notes_68_fulltext.xlsx
+++ b/data/paper_notes_68_fulltext.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="68篇笔记·全文已补" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="这份表怎么用" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25篇待取全文" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5篇仍缺全文" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,6 +39,11 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="000D47A1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="007A5200"/>
       <sz val="9"/>
     </font>
@@ -51,7 +56,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -66,6 +71,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E3F2FD"/>
       </patternFill>
     </fill>
     <fill>
@@ -91,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -105,11 +115,14 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -676,7 +689,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>全文已读 · PMC10899785</t>
+          <t>全文已读 · PMC · PMC10899785</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
@@ -808,7 +821,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>全文已读 · PMC8177725</t>
+          <t>全文已读 · PMC · PMC8177725</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
@@ -940,7 +953,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>全文已读 · PMC8356967</t>
+          <t>全文已读 · PMC · PMC8356967</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
@@ -1072,7 +1085,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>全文已读 · PMC6754277</t>
+          <t>全文已读 · PMC · PMC6754277</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
@@ -1204,7 +1217,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>全文已读 · PMC6559361</t>
+          <t>全文已读 · PMC · PMC6559361</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
@@ -1336,7 +1349,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>全文已读 · PMC9789169</t>
+          <t>全文已读 · PMC · PMC9789169</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
@@ -1468,7 +1481,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>全文已读 · PMC8653786</t>
+          <t>全文已读 · PMC · PMC8653786</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
@@ -1600,7 +1613,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>全文已读 · PMC8127995</t>
+          <t>全文已读 · PMC · PMC8127995</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
@@ -1732,7 +1745,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>全文已读 · PMC10620050</t>
+          <t>全文已读 · PMC · PMC10620050</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
@@ -1864,7 +1877,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>全文已读 · PMC13083262</t>
+          <t>全文已读 · PMC · PMC13083262</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
@@ -1996,7 +2009,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>全文已读 · PMC</t>
+          <t xml:space="preserve">全文已读 · PMC · </t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
@@ -2128,7 +2141,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>全文已读 · PMC6836734</t>
+          <t>全文已读 · PMC · PMC6836734</t>
         </is>
       </c>
       <c r="G13" s="2" t="n">
@@ -2260,7 +2273,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>全文已读 · PMC3141258</t>
+          <t>全文已读 · PMC · PMC3141258</t>
         </is>
       </c>
       <c r="G14" s="2" t="n">
@@ -2392,7 +2405,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>全文已读 · PMC5712218</t>
+          <t>全文已读 · PMC · PMC5712218</t>
         </is>
       </c>
       <c r="G15" s="2" t="n">
@@ -2524,7 +2537,7 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>仅摘要（无开放全文）</t>
+          <t>全文已读 · 你提供的 PDF · 1-s2.0-S109727651400121X-m</t>
         </is>
       </c>
       <c r="G16" s="2" t="n">
@@ -2565,7 +2578,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】读全文时需找：(1) TAIL-seq建库流程图（通常为Figure 1），确认专用接头设计如何跨过poly(A)同聚物读出3′端序列；(2) 说明其单核苷酸分辨率的图/表，看能否分辨1-2nt级别的尾长差异；(3) 文中是否有小RNA或miRNA相关的补充方法/图，若无则需查找该组后续是否发表miRNA版TAIL-seq（第二种方法，即后续改良版是否称为"mTAIL-seq"或类似)。</t>
+          <t>Figure 3A/3B 支持"mRNA广泛3'尿苷化"的主张：约一半mRNA物种的U-tail频率&gt;5%，80%的mRNA物种尿苷化频率高于2%，且U-tail通常连接在短poly(A)尾（&lt;25 nt）之后，可信度依据是转录组尺度的TAIL-seq定量分析（覆盖4,176个小鼠及4,091个人类基因，支持≥30 poly(A)+ tags）。Figure 4A/4B以同样方法呈现G-tail与poly(A)长度的关系（G-tail多见于较长poly(A)尾&gt;40 nt），两者互为对照，提示U/G尾巴功能不同但均由同一独立定量流程（GMHMM+Viterbi解码，spike-in校准RMSE 14.8%）验证，并有Hire-PAT（Figure 1D）与northern blot（Figure S3B）两种独立方法交叉验证poly(A)长度测量的可靠性，增强了这些定量结论的可信度。</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2580,12 +2593,12 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】读全文时需逐条核对：(1) 是否设置了已知半衰期的mRNA作为阳性对照来验证TAIL-seq测得的poly(A)长度-半衰期相关性；(2) 测序深度/reads数是否足以支持miRNA这类短RNA的定量重复性；(3) 是否有生物学重复及不同细胞系间的一致性验证；(4) U-tail/G-tail的检出是否排除了测序/建库产生的人工尾巴(artifact)干扰。</t>
+          <t>文中明确做了的对照包括：用0–118 nt不同长度的合成spike-in poly(A) oligo（500 reads/spike-in）训练GMHMM并估计RMSE=14.8%，作为测序准确性的内参对照；用Hire-PAT对5个spike-in和10个内源mRNA做独立验证（Figure 1D、S2C、S3A）；用northern blot对Spp1 mRNA的RNase H切割产物做独立验证（Figure S3B）；miR-1 transfection实验中以"非靶标基因（gray dots）"作为miR-1靶标（red dots）的对照组，并设3/6/9小时多个时间点比较poly(A)变化与mRNA水平变化的先后关系（Figure 2F）。缺少的关键对照：文中未提及针对U-tailing或G-tailing本身的功能性对照，例如敲低候选尿苷转移酶（TUT4/7等）或鸟苷转移酶后观察U/G-tail频率变化，这对于确认这些修饰是酶促且具有因果性（而非测序伪影或随机附加）非常重要，但全文未见此类基因扰动实验。</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>摘要给出的数字：HeLa和NIH 3T3细胞中poly(A)中位长度为50-100 nt；U尾主要接在&lt;25nt的短poly(A)后，G尾主要接在&gt;40nt的长poly(A)后。【摘要未报告数字】读全文时需补充：miRNA/小RNA尾长的分辨率（能分辨到几个核苷酸）、每个转录本平均测序深度、U/G尾修饰的全转录组比例。</t>
+          <t>全文提供多组准确定量数字：NIH 3T3与HeLa细胞中位poly(A)长度分别为60 nt和59 nt（8–231 nt窗口内），基于中位数的转录组中位长度为61 nt（NIH 3T3）和60 nt（HeLa），poly(A)&gt;231 nt仅占总体2%（正文Global Analysis of Poly(A) Tail段）。poly(A)长度与mRNA半衰期相关性p=2.83×10⁻⁵（Figure 2E）；与翻译效率无显著相关，p=0.893（NIH 3T3）、p=0.449（HeLa）（Figure S4B文字说明）。尿苷化方面：约50%的mRNA物种U-tail频率&gt;5%，80%物种尿苷化频率&gt;2%，SOGA2和PABPC4 mRNA尿苷化频率分别达41%和24%（Figure 3A对应正文段落）。miR-1转染实验中，poly(A)长度变化的Mann-Whitney U检验p值为：3小时5.84×10⁻⁴，6小时1.87×10⁻⁵，9小时6.63×10⁻⁴（Figure 2F图注）。spike-in测量误差RMSE平均14.8%（正文TAIL-seq方法学部分）。</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -2620,7 +2633,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】读全文时需从参考文献里挑三类：(1) 同期发表的竞争性尾巴测序方法（如Bartel lab的PAL-seq）以对比技术优劣；(2) TUT4/7（也称ZCCHC11/ZCCHC6）介导RNA尿苷化的机制性引文，确认其在miRNA降解（尤其let-7、miR-29）中的已知作用；(3) 本文方法后续被用于miRNA专用测序的改良版引文（如mTAIL-seq），确认是否已有人做过miR-29的TAIL-seq数据。</t>
+          <t>Behm-Ansmant, I., et al. (2006)《mRNA degradation by miRNAs and GW182 requires both CCR4:NOT deadenylase and DCP1:DCP2 decapping complexes》Genes Dev — 与方向①相关，阐述miRNA介导的去腺苷化机制，为TDMD/miRNA稳态调控提供背景。Guo, H., et al. (2010)《Mammalian microRNAs predominantly act to decrease target mRNA levels》Nature — 本文miR-1 transfection实验的靶标定义直接引自此文献，与方向①③miRNA稳态调控密切相关。Heo, I., et al. (2012)《Mono-uridylation of pre-microRNA as a key step in the biogenesis of group II let-7 microRNAs》Cell — 与方向②TUT4/7尿苷化miRNA生物合成直接相关，值得优先排查。Schmidt, M.J., West, S., and Norbury, C.J. (2011)《The human cytoplasmic RNA terminal U-transferase ZCCHC11 targets histone mRNAs for degradation》RNA — ZCCHC11即TUT4，与方向②TUT4/7介导的3'尿苷化机制高度相关。Rissland, O.S., Mikulasova, A., and Norbury, C.J. (2007)《Efficient RNA polyuridylation by noncanonical poly(A) polymerases》Mol. Cell. Biol. — 涉及非典型poly(A)聚合酶介导的尿苷化，与方向②TUT4/7对miR-29尿苷化的酶学机制相关。</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2656,7 +2669,7 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>仅摘要（无开放全文）</t>
+          <t>全文已读 · 你提供的 PDF · WIRES-miRNA-stability-degr</t>
         </is>
       </c>
       <c r="G17" s="2" t="n">
@@ -2697,7 +2710,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】读全文时要找：(1)综述中总结TDMD/uridylation/nuclease三条通路的示意图，确认是否列出了具体测半衰期的方法（如metabolic labeling、actinomycin D chase、4-thioU pulse-chase）及各方法的时间分辨率；(2)是否有第二种半衰期定量方式（如全基因组turnover rate建模）可与他计划用的方法对照；(3)"compartment-specific degradation"部分是否给出肠腔/循环中miRNA半衰期的具体数值范围。</t>
+          <t>文中提供的图注仅覆盖 Figure 1（miRNA biogenesis pathway 示意图）和 Figure 2（miRISC 靶向沉默机制示意图），二者均为综述性示意图，未见实验数据图。正文提到 Figure 3 用于描绘 ZSWIM8-CUL3-RBX1-ARIH1 介导 AGO 多聚泛素化及后续降解的分级组装模型（TDMD 通路），但给到的文本中没有抓取到 Figure 3 的图注文字，故无法核实其具体标注内容。由于全文属于 Advanced Review 类综述，所有图均为机制示意图而非原始实验数据图，没有 n 值、重复次数或统计方法可供评估可信度，因此本文所有图均不能用作独立实验证据支持 AMPK-ZSWIM8、TUT4/7-miR-29 或乳酸修饰相关主张。</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2712,12 +2725,12 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】读全文时要逐条打勾：(1)综述在讨论TDMD时是否明确要求区分pri/pre-miRNA转录抑制 vs 成熟体降解（对应他的竞争解释——TGF-β/Smad3转录抑制miR-29的干扰因素）；(2)是否列出各降解通路研究中使用的阴性对照（如ZSWIM8催化死突变、TUT4/7双敲低对照）；(3)是否说明uridylation studies中如何排除转录变化的对照设计。</t>
+          <t>给到的文本中没有 Methods/Experimental Procedures 正文（该部分仅显示参考文献列表片段），也没有本综述自身开展的实验及对照。文中对 TDMD 机制的描述（ZSWIM8 识别 match-bulge-match 结构、CUL3-Elongin BC-RBX1-ARIH1 分级组装、AGO 多聚泛素化后蛋白酶体降解）均引用自 Han et al. 2020 和 Shi et al. 2020 等原始研究，本文未做任何新实验或对照设计。因此本文缺少与 Sheldon 三个方向直接相关的对照实验（如 AMPK 激酶死突变体、ZSWIM8 S608/S609 磷酸化位点突变对照、TUT4/7 敲低后 miR-29 尿苷化水平的野生型对照、乳酸处理与未处理细胞的 AGO2/ZSWIM8 乳酰化对照），这些缺失的对照对验证磷酸化/尿苷化/乳酰化是否是因果驱动因素至关重要，仅靠综述描述无法替代。</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>【摘要未报告数字】读全文时优先补：(1)ZSWIM8-TDMD导致的miRNA半衰期缩短倍数或时间常数(t1/2)的具体数值范围；(2)TUT4/7尿苷化对miR-29或类似miRNA降解速率的定量影响（如fold-change in decay rate）；(3)肠腔/循环等compartment中miRNA半衰期的已报道数值，用于建立他自己实验的对照基准。</t>
+          <t>【全文未见定量数字】。给到的正文段落（摘要、Introduction、miRNA biogenesis/action 章节、TDMD 机制描述）均为机制性叙述，没有出现具体倍数、百分比、p 值或样本量 n 等定量数据。文中提及的 miR-21、miR-208a、miR-122、let-7 等案例也只是定性描述其功能后果（如"促进乳腺癌转移""驱动病理性心脏重构"），未附带原始论文中的数字。若需要获取具体效应量，需查阅该综述引用的原始实验论文（如 Han et al. 2020、Shi et al. 2020、Boele et al. 2014 等），而非本综述文本本身。</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2752,7 +2765,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】读全文时要挑三类参考文献：①ZSWIM8-TDMD原始发现及后续机制论文（用于确认TDMD后核酸酶研究现状，判断方向1的可行性和竞争格局）；②TUT4/7-DIS3L2-miR-29/let-7降解相关原始论文（直接对应方向2，判断是否已有人在纤维化/肠道组织中做过）；③测定miRNA半衰期方法学论文（如metabolic labeling、pulse-chase、genome-wide turnover建模），用于补齐他"缺的技能"清单中的半衰期测定方案。</t>
+          <t>1. Han, J. et al. 2020《Han et al. 2020》（文中引用，标题未在给到的参考文献段中完整列出，但正文多次引用其提出 ZSWIM8 识别 match-bulge-match 结构并驱动 TDMD 分级组装模型，与方向①AMPK-ZSWIM8-TDMD 直接相关，值得排队核实原文）。2. de la Mata, M., D. Gaidatzis, M. Vitanescu, et al. 2015《Potent Degradation of Neuronal miRNAs Induced by Highly Complementary Targets》EMBO Reports——阐述高互补性靶标诱导神经元 miRNA 降解的机制，是 TDMD 现象学基础文献，对理解 ZSWIM8-TDMD 通路的靶标识别原理有帮助，对应方向①。3. Boele, J., H. Persson, J. W. Shin, et al. 2014《PAPD5-Mediated 3′ Adenylation and Subsequent Degradation of miR-21 Is Disrupted in Proliferative Disease》PNAS——展示末端修饰（腺苷化）调控特定 miRNA 稳定性及降解的范例，方法学上可类比 TUT4/7 尿苷化对 miR-29 稳定性的调控，对应方向②。4. A. Yang, T. J. Shao, X. Bofill-De Ros, et al. 2020《AGO-Bound Mature miRNAs Are Oligouridylated by TUTs and Subsequently Degraded by DIS3L2》Nature Communications——直接描述 TUT 介导的 AGO 结合成熟 miRNA 尾部尿苷化及 DIS3L2 降解机制，与方向② TUT4/7-miR-29 尿苷化通路高度相关，值得排队查阅其具体实验体系是否可迁移至 miR-29/纤维化模型。5. D'Ambrogio, A., W. Gu, T. Udagawa, C. C. Mello, and J. D. Richter 2012《Specific miRNA Stabilization by Gld2-Catalyzed Monoadenylation》Cell Reports——展示特定核苷酸转移酶催化的单核苷酸加尾修饰对 miRNA 稳定性的正向调控，为理解代谢/翻译后修饰（可类比乳酰化）如何重编程 miRNA 稳态提供方法学参照，对应方向③。</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2788,7 +2801,7 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>仅摘要（无开放全文）</t>
+          <t>全文已读 · 你提供的 PDF · FEBS-1995-Dale-AMPK-motifs</t>
         </is>
       </c>
       <c r="G18" s="2" t="n">
@@ -2829,7 +2842,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】读全文时要找：(1) 24个肽变体的完整列表及各自的磷酸化相对活性数值表（通常是Table 1或2），确定−3/−4/+4位每个突变对活性的定量影响百分比；(2) 是否有第二种方法（如定点突变的天然蛋白底物验证，而非仅合成肽）来交叉验证该基序；(3) 图中是否给出了HRK-A/Snf1/CaMKI四者motif差异的并列比较图，以便判断我的ZSWIM8 S608/S609位点两侧序列是否严格符合phi-beta-XX-S-XXX-phi。</t>
+          <t>全文未抓到独立图注块，仅有 Table 1 与 Table 2 两个数据表，无 Fig 编号可点名。Table 1 给出 AMPK 与 HRK-A 对 'SAMS' 与 'AMARA' 及其22个变体肽的 V、Km、V/Km 稳态动力学参数（均标注±标准误），支持"AMARA'及其变体是AMPK/HRK-A底物识别的定量工具"这一主张；可信度依据是每个数值均带统计误差（由文献[22]的统计方法拟合Michaelis-Menten方程得出），但正文未提及重复次数(n)，也没有第二种独立方法（如质谱或结构法）验证，仅为体外激酶动力学测定。Table 2 是单一肽浓度(40 μM)下四种激酶（AMPK、HRK-A、SNF1、CaMKI）对24个变体肽的相对初始磷酸化速率，同样标注±SEM（"3-6 determinations"），用于比较四种激酶识别基序的异同，但该表本身不构成独立图，故可信度层面只能视为同一套数据的两种呈现方式，缺乏跨方法交叉验证。</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2844,12 +2857,12 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】读全文时要核对的对照清单：①是否包含不含任何S/T的阴性对照肽以确认背景磷酸化本底；②是否用已知天然AMPK底物（如ACC1的Ser79位点序列）做阳性对照与合成肽结果比对一致性；③四种激酶的酶活力/比活是否用同一批肽标准化，避免因激酶制备批次差异导致基序权重判断偏差；④是否设置了非磷酸化位点（S→A突变）对照验证信号确实来自靶位点而非非特异磷酸化。</t>
+          <t>文中做了的对照包括：用snf1-Δ10缺失株与其同源野生型比较'AMARA'及变体#3、#4的磷酸化，证实野生型经葡萄糖饥饿后磷酸化被刺激约10倍，而snf1-Δ株无此增加；并将snf1-Δ株的粗提物经同一纯化流程处理后确认不再磷酸化'AMARA'，以排除其他激酶污染。CaMKI组做的对照是所有肽的磷酸化均需CaMKIα activator预激活才能进行（未预激活则不磷酸化，正文标注"not shown"）。AMPK/HRK-A组做的对照是AMP刺激作用在'AMARA'与所有变体上与'SAMS'肽相同（"not shown"）。缺少的关键对照是：全文没有针对AGARAASAAALARRR等关键突变肽做非激酶对照（如无酶空白或热失活酶对照）的直接数据展示，也没有提供n值和重复次数的具体记录，这使得跨激酶效应量的比较缺乏独立验证支撑。</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>【摘要未报告数字】读全文时优先补：每个位点突变（−5、−4、−3、+4等）导致磷酸化速率下降的具体倍数或百分比（如−3位R→A使活性降到多少%），以及AMPK与其他三种激酶对同一肽变体活性比值的定量数据，这些数字直接决定我的PSSM权重矩阵怎么打分。</t>
+          <t>'AMARA' 对 AMPK 的 V/Km 比 'SAMS' 肽高3.8倍，对 HRK-A 高4.5倍（Table 1 及摘要句"with V/K m values 3.8-fold and 4.5-fold higher respectively than for the 'SAMS' peptide"）。SNF1 对'AMARA'的 V/Km 比'SAMS'低5倍，主要因 Km 由26 μM（AMPK上SAMS的Km）升至约650 μM（SNF1对AMARA的Km≈650 μM vs. SAMS的108 μM，见正文3.2节）。CaMKI对'AMARA'的V/Km比synapsin I肽（LRRRLSDANF）低6倍（正文4节discussion首句）。葡萄糖饥饿使野生型酵母中'AMARA'及两个变体肽的磷酸化被刺激约10倍（"stimulated ≈10-fold by removal of glucose from the medium"）。</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
@@ -2884,7 +2897,11 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】读全文时要挑三类参考文献：①本文引用的AMPK天然底物（如ACC、HMG-CoA reductase）磷酸化位点原始鉴定文献，用于比对合成肽结果与天然蛋白的一致性；②SNF1/Snf1激酶家族的结构或系统发生学文献，帮助理解四种激酶基序差异的分子基础；③CaMKI/CaMKII底物基序相关文献，用于排除我的ZSWIM8位点是否会被CaMK交叉磷酸化产生实验混杂。</t>
+          <t>[9] Carling, D. et al. (1994) J. Biol. Chem. 269, 11442-11448 — 定义AMPK异源三聚体结构/激活机制，为方向①中AMPK磷酸化ZSWIM8(S608/S609)提供上游酶学基础。
+[10] Mitchelhill, K.I. et al. (1994) J. Biol. Chem. 269, 2361-2364 — 报道AMPK催化亚基结构与底物识别特性，支持方向①中AMPK底物motif分析。
+[12] Stapleton, D. et al. (1994) J. Biol. Chem. 269, 29343-29346 — AMPK亚基克隆/结构鉴定，可用于比对ZSWIM8磷酸化位点是否符合AMPK经典识别序列（方向①）。
+[14] Woods, A. et al. (1994) J. Biol. Chem. 269, 19509-19515 — 阐明AMPK与SNF1家族底物特异性关系，为跨激酶（AMPK/CaMKI）识别motif的方向①③提供保守性证据。
+[24] Knighton, D.R. et al. (1991) Science 253, 414-420 — 蛋白激酶催化域晶体结构，可为AGO2/ZSWIM8/TUT4-7潜在磷酸化/乳酰化位点的结构可及性分析（方向③）提供结构参照。</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2920,7 +2937,7 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>仅摘要（无开放全文）</t>
+          <t>全文已读 · 你提供的 PDF · 1-s2.0-S089865681500042X-m</t>
         </is>
       </c>
       <c r="G19" s="2" t="n">
@@ -2961,7 +2978,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】读全文时要找：(1)57个候选蛋白的富集质谱图/表格，及AMPK-activator处理组 vs AMPK-null组的定量对比方式(倍数变化/谱数计数);(2)cingulin S137和MFF S129/S146磷酸化位点特异抗体的免疫印迹图，是否有時间曲线(transient phosphorylation)的定量;(3)是否有第二种独立验证方法(如体外kinase assay/32P标记)佐证质谱结果，而非仅依赖抗体识别。</t>
+          <t>Fig. 1(A,B) 显示 AICAR(0.3 mM)+A769662(10 μM) 处理小鼠原代肝细胞 45 min 后，AMPKα T172、ACC 及 Raptor 磷酸化明显增强，p70S6K T389 磷酸化被抑制，p-AMPK motif 抗体识别的条带数量与强度也增加(Fig. 1A)；随后以该抗体或 IgG 对照做免疫沉淀，Coomassie 染色胶显示部分条带为处理组特异富集(Fig. 1B 星号标记)，用于后续 MS/MS 鉴定。可信度方面文中提到做了技术重复(exp1a/exp1b)以证实一致性和可重复性，但图注/正文未给出重复次数的统计检验(如 p 值)或第二种独立方法交叉验证富集条带的定量结果。Fig. 4 和 Fig. 5 分别用非磷酸化突变体(S129A/S146A)及内源 MFF 免疫沉淀+phospho-site 特异抗体验证 S129/S146 磷酸化随 AMPK 激活上调，Fig. 4A 图注明确标注"representative of two independent experiments"，可信度为两次独立重复但未见统计检验数字。</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2976,12 +2993,12 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】读全文时逐条核对：①是否设AMPK激活剂处理 vs 未处理的富集比较；②是否设AMPK基因缺失/敲低细胞系作为特异性阴性对照（排除抗体非特异结合）；③位点特异性磷酸抗体是否用非磷酸化突变体(S→A)细胞或磷酸酶处理组做特异性验证；④质谱鉴定磷酸化位点是否有生物学重复及统计阈值(FDR/倍数变化cutoff)。</t>
+          <t>文中明确做的对照包括：非特异性对照抗体(rabbit IgG)用于免疫沉淀对照(Fig. 1B)；COS-1 细胞转染野生型 vs S137A cingulin 或 S129A/S146A MFF 等非磷酸化突变体作为磷酸化位点特异性对照(Fig. 2B、Fig. 4A)；未转染细胞作为空载对照(Fig. 2B)；以及 λ-phosphatase 处理免疫沉淀的 FLAG-MFF 以验证抗体识别的是磷酸化形式(Methods 2.6)。缺少的关键对照：未见使用 AMPK 激酶失活突变体(kinase-dead)或 AMPKα1/α2 基因敲除细胞/组织来直接证明 Fig. 1、Fig. 4、Fig. 5 中观察到的磷酸化确实依赖 AMPK 本身而非其他激酶(文中摘要提到用了"absent in hepatocytes lacking AMPK"的比较来筛选57个蛋白，但该敲除对照未在给定图注/正文段落中详细展示于 Fig.4/5 的验证实验里)；也未见针对 MFF/cingulin 磷酸化对其功能(如线粒体分裂)影响的功能性对照实验。</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>摘要给出唯一定量数字：识别到57个在激活剂处理肝细胞中特异富集、而AMPK缺失肝细胞中缺失的蛋白（57 proteins uniquely enriched...absent in AMPK-lacking hepatocytes）；MFF位点定位为S129(共有)与S146(变异体特异)，cingulin位点为S137；未报告富集倍数、质谱谱数、位点占有率等统计量——读全文时需补充这些数字。</t>
+          <t>正文摘要给出的定量数字为：通过该蛋白质组学方法鉴定出 57 个在激活剂处理的肝细胞中特异富集、但在缺乳 AMPK 的肝细胞中不存在的蛋白(摘要句"We identified 57 proteins that were uniquely enriched in the activator-treated hepatocytes, but were absent in hepatocytes lacking AMPK.")。此外结果部分提到通过 LC-MS/MS 共检测到 549 个蛋白(2 肽段最低、95% 置信度)("A total of 549 proteins were detected (2 peptides minimum with 95% probability) across…")。AICAR 与 A769662 处理浓度及时间为定量参数：0.3 mM AICAR + 10 μM A769662，处理 45 min(Fig. 1 图注及 Methods)。除上述数字外，全文未见针对磷酸化条带强度倍数变化或统计学 p 值的具体定量数字。</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
@@ -3016,7 +3033,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】读全文时从参考文献里挑：①AMPK底物识别基序(consensus motif)最初定义/PSSM构建的原始文献，用于校验我自己对ZSWIM8位点的基序打分依据；②本文所用phospho-AMPK-substrate motif抗体的原始开发/验证文献，判断该抗体识别特异性边界；③其他利用同类质谱/亲和富集策略发现AMPK新底物的平行研究，用于排查是否已有人筛到ZSWIM8/TUT4-7/AGO2同源位点，评估竞争风险。</t>
+          <t>对 Sheldon 三个方向（AMPK 磷酸化调控代谢/TDMD、TUT/尿苷化纤维化、乳酸乳酰化重编程蛋白稳态）最相关的排队文献如下：[1] D.G. Hardie, F.A. Ross, S.A. Hawley《Nat. Rev. Mol. Cell Biol. 13 (2012) 251–262》— AMPK 综述，梳理 AMPK 激活机制与底物识别模体，是理解 AMPK 磷酸化 ZSWIM8 类底物模体的基础背景文献。[12] D.G. Hardie《Genes Dev. 25 (2011) 1895–1908》— 系统阐述 AMPK 底物识别模体(−5/−3位碱性、−5/+4位疏水)，直接支撑本文抗体设计思路，对研究 AMPK 磷酸化 ZSWIM8(S608/S609)的模体识别机制有参考价值。[33] D.F. Egan et al.《Science 331 (2011) 456–461》— AMPK 直接磷酸化 ULK1 调控自噬，展示 AMPK 磷酸化下游效应蛋白改变细胞稳态的范式，可类比 AMPK-ZSWIM8 磷酸化如何重塑 miRNA 代谢记忆通路。[16] D.M. Gwinn et al.《Mol. Cell 30 (2008) 214–226》— AMPK 磷酸化 TSC2 调控 mTOR 信号，作为 AMPK 底物磷酸化影响下游稳态调控机制的另一实例，对方向①中"AMPK 磷酸化加速降解相关底物"的机制类比有参考价值。以上文献均聚焦 AMPK 底物识别与磷酸化下游效应机制，与方向②(TUT4/7-miR-29-纤维化)及方向③(乳酸乳酰化修饰)在本文参考文献表中未见直接相关文献，故未排队。</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -3052,7 +3069,7 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>仅摘要（无开放全文）</t>
+          <t>全文已读 · 你提供的 PDF · 1-s2.0-S0022283601953161-m</t>
         </is>
       </c>
       <c r="G20" s="2" t="n">
@@ -3093,7 +3110,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】读全文时要找：(1) GST-ACC 25个突变体和GST-KD 7个突变体的完整Km/Vmax或kcat/Km表格及对应图，确认哪些位点的动力学参数变化倍数最大(判定"关键"位点的定量阈值)；(2) 结构模型图(基于哪个已知激酶晶体结构模板同源建模，如CaMKI或CDK)及其与后续AMPK真实晶体结构(如有引用/后续对比)的吻合度；(3) 是否有第二种独立方法(如ITC、SPR或肽阵列筛选)验证该结合模型，还是仅依赖突变-动力学一种手段。</t>
+          <t>Fig. 1 展示 AMPK α1 kinase domain 与底物 ACC1(60-85) 的结构模型，标出 M74(P-5)、R75(P-4)、S79(P)、L83(P+4) 等关键残基位置，支持"底物以 amphipathic helix 结合于疏水槽"的核心主张，但此图本身是同源建模而非晶体结构，可信度有限。Fig. 5、Fig. 6、Fig. 7、Fig. 8 分别用 kcat/Km 的 bar chart/graph（配 standard errors of the mean）对模型预测的关键残基（R75/M74、H73、amphipathic helix 上的 alanine scan、H82/L83）做突变验证，属于独立的酶活性动力学数据，与结构模型形成两种方法互证，可信度较高；但文中未给出这些图的具体重复次数(n)或统计检验方法（仅提及"error bars are standard errors of the mean"）。Fig. 2(a)(b) 用 AMPK activity assay 和 Western blot 两种独立方法证明 GFP-α1-KD 不依赖 β1/γ1 亚基即可稳定表达并保持活性，是本文少数有明确对照（±β1γ1 共转染）的图。</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -3108,12 +3125,12 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】读全文时要逐条核对：①T172D组成性激活突变是否与野生型激酶经上游激酶(如LKB1/CaMKKβ)磷酸化激活后的动力学参数做过平行对照，以排除T172D本身改变底物特异性；②是否有GST单独(无融合底物/无融合激酶结构域)的阴性对照排除GST标签本身的非特异磷酸化贡献；③突变体的表达量/折叠正确性是否用CD光谱或类似方法确认，排除突变导致的错误折叠被误判为"结合减弱"；④是否用非底物肽或随机序列肽作为阴性对照验证磷酸化的序列特异性而非激酶的非特异性活性。</t>
+          <t>明确做了的对照包括：①Fig. 2 中 GFP-α1 和 GFP-α1-KD 在"有/无 β1、γ1 亚基共表达"两种条件下的活性与 Western blot 对比；②Fig. 3 中 wild-type GST-α1-KD 与 T172D 突变体在"有/无 AMPKK 孵育"条件下的活化对比，并用 PP2A 去磷酸化处理验证 T172D 的组成性激活（正文称 wild-type 可被 PP2A 失活而 T172D 不敏感）；③Fig. 4(b) 中 wild-type GST-ACC 与 S79A 突变体的磷酸化对比，作为磷酸化位点特异性的阴性对照；④Table 1 中多组底物突变(P-18至P-5等位点)分别与 kinase 侧突变(L212R/E100A/D103A/D215A/D216A/D217A/D56R)做了"complementary mutation"组合对照，用于验证特定电荷/疏水相互作用配对。缺少的关键对照：文中没有提到对 GST 标签本身或空载体表达产物的磷酸化本底对照，也没有看到针对 AMPK T172D 组成性活性是否受 AMP 变构调节的阳性对照数据之外的定量重复次数说明；这些若缺失会削弱"该模型底物"背景磷酸化可忽略、以及动力学参数误差范围代表真实生物学重复而非技术重复的判断。</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>【摘要未报告数字】读全文时优先补：25个GST-ACC突变体和7个GST-KD突变体中，各关键位点(P-16~P-5、P-6、P-4、P+3、P+4)突变后Km/Vmax(或kcat/Km)相对野生型的具体倍数变化，用于判断我自己做ZSWIM8 S608/S609周边序列PSSM打分时可接受的"结合力下降阈值"。</t>
+          <t>"the activity of the GST-a1-KD mutant had a low but detectable activity that increased &gt;100-fold on incubation with MgATP and the partially purified upstream kinase, AMPKK"（正文 Results 部分，对应 Fig. 3）。"The T172D mutant exhibited a specific activity 40-fold higher than the wild-type GST-a1-KD"（同段）。"native AMPK purified from rat liver was stimulated 2.5-fold"by 200 μM AMP（正文，无对应图号，标注"not shown"）。Table 1 给出具体 kinetic 数值示例：WT/WT 组合 kcat=6.33±0.29 s⁻¹，Km=4.67±1.48 μM，kcat/Km=1.35±0.20 s⁻¹mM⁻¹；WT substrate 配 L212R kinase 突变后 kcat/Km 降至 0.10±0.05 s⁻¹mM⁻¹。kcat for SAMS peptide phosphorylation by GST-α1-KD-T172D 为 4.2 s⁻¹（正文一句）。</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -3148,7 +3165,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】读全文时要挑三类参考文献：①本文所依据的同源建模模板激酶晶体结构原始文献(用于评估结构模型的可靠性来源，如CaMKI/CDK2/PKA晶体结构论文)；②本文引用的此前AMPK底物基序共识序列原始报道(判断本文相对旧共识究竟新增了哪些位点信息)；③本文方法学后续是否被作者或他人用于预测/验证其他AMPK新底物的跟进研究(判断该方法在本文之后的实际预测成功率/假阳性率如何)。</t>
+          <t>Hardie, D. G. &amp; Carling, D. (1997)《The AMP-activated protein kinase: fuel gauge of the mammalian cell?》Eur. J. Biochem. 246, 259-273 — 综述 AMPK 作为细胞能量感受器的下游磷酸化级联，对方向①的"AMPK 磷酸化底物→代谢通路"机制背景直接相关。Hardie, D. G. &amp; Hawley, S. A. (2001)《AMP-activated protein kinase: the energy charge hypothesis revisited》BioEssays 23, 1112-1119 — 讨论 AMP/ATP 感知与 AMPK 激活机制，对方向①中"AMPK 磷酸化 ZSWIM8"上游能量信号背景值得排队。Zhou, G. et al. (2001)《Role of AMP-activated protein kinase in mechanism of metformin action》J. Clin. Invest. 108, 1167-1174 — 涉及 AMPK 药理激活与代谢调控，可为方向①"代谢记忆"提供药理干预参照。Blair, E. et al. (2001)《Mutations in the gamma(2) subunit of AMP-activated protein kinase cause familial hypertrophic cardiomyopathy: evidence for the central role of energy compromise in disease pathogenesis》Hum. Mol. Genet. 10, 1215-1220 — AMPK 亚基突变导致心肌病，与方向②"MYBPC3 心脏纤维化"组织表型有潜在关联，值得排队核实。Dale, S., Wilson, W. A., Edelman, A. M. &amp; Hardie, D. G. (1995)《Similar substrate recognition motifs for mammalian AMP-activated protein kinase, higher plant HMG-CoA reductase kinase-A, yeast SNF1, and mammalian calmodulin-dependent protein kinase I》FEBS Letters 361, 191-195 — 建立 AMPK 底物识别核心motif，是本文底物特异性模型的基础，对理解 AMPK 磷酸化 ZSWIM8 特异位点(S608/S609)是否符合该 motif 有参考价值。</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -3184,7 +3201,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>全文已读 · PMC5881568</t>
+          <t>全文已读 · PMC · PMC5881568</t>
         </is>
       </c>
       <c r="G21" s="2" t="n">
@@ -3314,9 +3331,9 @@
           <t>https://pubmed.ncbi.nlm.nih.gov/32696389/</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>仅摘要（无开放全文）</t>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>仍缺全文</t>
         </is>
       </c>
       <c r="G22" s="2" t="n">
@@ -3448,7 +3465,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>全文已读 · PMC10545736</t>
+          <t>全文已读 · PMC · PMC10545736</t>
         </is>
       </c>
       <c r="G23" s="2" t="n">
@@ -3580,7 +3597,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>全文已读 · PMC3125113</t>
+          <t>全文已读 · PMC · PMC3125113</t>
         </is>
       </c>
       <c r="G24" s="2" t="n">
@@ -3712,7 +3729,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>全文已读 · PMC6935248</t>
+          <t>全文已读 · PMC · PMC6935248</t>
         </is>
       </c>
       <c r="G25" s="2" t="n">
@@ -3844,7 +3861,7 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>仅摘要（无开放全文）</t>
+          <t>全文已读 · 你提供的 PDF · 1-s2.0-S0021925820660276-m</t>
         </is>
       </c>
       <c r="G26" s="2" t="n">
@@ -3885,7 +3902,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】读全文时要找：ELISA滴度曲线图、peptide array点阵图的具体图号；RNAi敲低PKD后免疫印迹条带消失的对照图；Hsp27 Ser82突变体(S82A)验证图，确认是否有第二种独立方法(如质谱)交叉验证该抗体特异性。</t>
+          <t>本文核心图为 Fig. 1（A–C）：Fig. 1A 用固定单一氨基酸的降解肽库与纯化重组 PKD 及 [γ-32P]ATP 孵育，确认 PKD 在 -5 位偏好亲脂性残基（尤其 leucine）、在 -3 位偏好 arginine，每个斑点经定量并以背景磷酸化的百分比列表，属于体外激酶活性验证。Fig. 1B 是三项独立研究得到的 PKD 最优磷酸化基序比对示意图，用于说明抗体设计依据，非独立实验数据。Fig. 1C 是膜结合磷酸肽阵列与纯化 anti-PKD pMOTIF 抗体孵育后的特异性图谱，显示抗体在 -7/-6/-4/-3/-2/+1/+2 等位点的选择性，与 Fig.1A 的激酶偏好性相互印证，构成第二种独立方法（抗体结合谱 vs. 激酶磷酸化谱）对彼此可信度的支持。但该图注块本身未给出重复次数（n）或统计检验方法，故可信度依据仅限于"两种独立方法趋势一致"，无法进一步用统计学量化。</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3900,12 +3917,12 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】读全文时要逐条确认：①是否用磷酸酶(如λ-phosphatase)处理裂解物作为阴性对照证明信号依赖磷酸化状态；②是否有非磷酸化肽段/scrambled motif肽段的阴性对照；③siRNA敲低效率的定量（mRNA/蛋白双重验证）；④位点突变体(如S82A)是否完全消除信号，以及是否设置了野生型回补对照；⑤抗体是否在多个细胞系中重复验证而非仅HeLa单一细胞系。</t>
+          <t>文中明确做了的对照：①用非磷酸化对照肽（non-phospho control peptides）做 ELISA，显示其反应性仅为对照磷酸肽的 3–5%，证明 anti-PKD pMOTIF 只结合磷酸化肽而非磷酸化肽；②用 RNAi 敲低内源 PKD1/PKD2（HEK293 细胞）以及敲低内源 Hsp27（RNAi，HeLa 细胞）来验证 27-kDa 条带的特异性归属；③用 GST-Hsp27 及其 S15A、S82A 点突变体做体外激酶实验，作为位点特异性对照；④用绿色荧光蛋白表达载体对照转染效率（80–90%）。缺少的关键对照：文本未提及 pSUPER 空载体（非靶向 RNAi）作为阴性对照在 Fig 图注/正文抓取段中被具体点名验证 Hsp27 敲低特异性（Methods 中提到"pSUPER or pSUPER-RNAi"作为并列处理但未在结果段明确称其为对照），也未见到非磷酸化型 S82A 突变体在细胞内（而非仅体外）背景下的完整对照数据描述；这类对照对排除 RNAi 脱靶效应、确认 Ser82 是细胞内真实生理磷酸化位点很重要，但给到的文本段未展示相关结果。</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>【摘要未报告数字】读全文时优先补：抗体在ELISA中的检测灵敏度(EC50或滴度)、peptide array上对consensus基序与非consensus基序的信号比值(fold specificity)、siRNA敲低后信号下降的定量百分比、Hsp27 S82磷酸化被PKD特异性磷酸化的体外kinase assay Km/Vmax数值。</t>
+          <t>全文抓取的文本中给出的定量信息主要是：非磷酸化对照肽的 ELISA 反应性为对照磷酸肽的 3–5%（正文"Non-phospho control peptides scored in the 3–5% range of control phosphopeptide"）；RNAi 转染效率为 80–90%（Methods"Transfection efficiencies (80–90%) were controlled using a green fluorescent protein expression vector"）。除此之外，Fig. 2A 中提到检测到 85、100、150、45、25、27 kDa 等条带分子量，但这是分子量而非效应量倍数。【全文未见定量数字】用于说明：给到的文本段中未见 Fig.3A（RNAi 敲低 Hsp27 后 27-kDa 条带免疫反应性降低）的具体倍数或 p 值，也未见 Fig.1A/1C 磷酸化/结合强度的具体百分比表格数值（仅文字描述趋势），故无法引用更精确的效应量数字。</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -3940,7 +3957,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】需从参考文献里挑三类：①该实验室此前发表的PKD底物鉴定原始论文(建立consensus motif来源)；②同期其他phospho-motif抗体技术论文(如CST公司发表的类似方法论文，用于比较验证标准差异)；③引用本文技术的后续应用论文(尤其是应用于AGC家族激酶如AMPK本身底物筛选的文献，看是否已有人用类似motif抗体策略筛选AMPK底物，判断是否与他的方向1存在方法学先占风险)。</t>
+          <t>与 Sheldon 三个方向（AMPK/TDMD、TUT4/7-miR-29-纤维化、乳酸/乳酰化重编程 miRNA 稳态）直接相关的参考文献在本文参考文献表中均未出现——本文参考文献表列出的 23 篇文献均为 PKD/PKC 信号转导、磷酸化基序识别、Hsp27/HDAC5/RIN1 底物及相关方法学文献（如 Cohen 2002 Nat Cell Biol；Manning et al. 2002 Science；Van Lint et al. 2002 Trends Cell Biol 等），主题与 miRNA 代谢、TDMD、TUT4/7 尿苷化、AGO2/ZSWIM8 乳酰化等方向均无重叠。因此本栏严格依据"标题须逐字出自给到的参考文献段"的要求，明确说明：【全文参考文献段中未见与 Sheldon 三个研究方向相关的文献，故不予排队】。</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3976,7 +3993,7 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>全文已读 · PMC5036175</t>
+          <t>全文已读 · PMC · PMC5036175</t>
         </is>
       </c>
       <c r="G27" s="2" t="n">
@@ -4108,7 +4125,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>全文已读 · PMC4324095</t>
+          <t>全文已读 · PMC · PMC4324095</t>
         </is>
       </c>
       <c r="G28" s="2" t="n">
@@ -4240,7 +4257,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>全文已读 · PMC13523302</t>
+          <t>全文已读 · PMC · PMC13523302</t>
         </is>
       </c>
       <c r="G29" s="2" t="n">
@@ -4372,7 +4389,7 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>全文已读 · PMC5452167</t>
+          <t>全文已读 · PMC · PMC5452167</t>
         </is>
       </c>
       <c r="G30" s="2" t="n">
@@ -4502,9 +4519,9 @@
           <t>https://pubmed.ncbi.nlm.nih.gov/20421885/</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>仅摘要（无开放全文）</t>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>仍缺全文</t>
         </is>
       </c>
       <c r="G31" s="2" t="n">
@@ -4636,7 +4653,7 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>仅摘要（无开放全文）</t>
+          <t>全文已读 · 你提供的 PDF · nature03076.pdf</t>
         </is>
       </c>
       <c r="G32" s="2" t="n">
@@ -4677,7 +4694,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】读全文时要找：(1) miR-375 过表达/敲低后 GSIS 的定量图（胰岛素分泌 ng/islet 或 fold change,及 n 值、重复次数）；(2) exocytosis 直接测定方法（如 patch-clamp capacitance 或 amperometry）及其代表性图；(3) Mtpn siRNA 表型是否与 miR-375 完全 phenocopy 的定量对比图；(4) 是否有第二种独立方法验证 miR-375 对 Mtpn 3'UTR 的直接结合（luciferase reporter mutant seed）。</t>
+          <t>Fig. 3d,e最能支撑miR-375调控胰岛素分泌是通过影响exocytosis而非Ca2+信号这一核心主张：control（Ad-eGFP）β细胞十次去极化的膜电容增加为837±244 fF（n=9），Ad-375感染细胞仅为94±27 fF（n=10，P&lt;0.01），降幅85%，属于独立于[Ca2+]i测量之外的第二种功能读数（patch-clamp capacitance），可信度较高。Fig. 4e/f通过luciferase reporter（pRL-Mtpn-WT vs pRL-Mtpn-MUT）验证Mtpn 3'UTR是miR-375的直接靶点，数据为三次独立实验±s.e.m.，n=6，属于两套独立方法（western blot下调+luciferase报告基因）交叉验证，可信度较高。Fig. 1d/f的siRNA/2'-O-methyl功能学实验则是最上游的功能证据链，但部分关键图（如Ca2+成像Fig. 3a,b）仅代表"五次实验中的代表性图"，属于定性展示，量化力度弱于capacitance数据。</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4692,12 +4709,12 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】读全文时逐条核对：①miR-375 过表达/抑制是否有 scrambled/mismatch antisense 对照；②Mtpn siRNA 是否设置非靶向 siRNA 对照及 rescue 实验（miR-375 抑制+Mtpn 过表达能否逆转表型）；③luciferase 3'UTR 报告基因是否有 seed-mutant 对照；④GSIS 测定是否有低糖/高糖两种条件对照及胰岛细胞存活率（避免毒性混淆）对照。</t>
+          <t>文中明确做的对照包括：阴性对照si-apoM（apoM在β细胞不表达）、阳性对照si-Gck（靶向glucokinase验证siRNA功能有效性）、错义对照si-375MUT（miR-375核心序列突变，验证siRNA特异性而非脱靶效应）、2'-O-me-eGFP作为2'-O-me-375的抑制剂对照、以及luciferase实验中的pRL-Mtpn-MUT位点突变对照（验证3'UTR结合位点特异性）。腺病毒实验以Ad-eGFP（不含转基因）作为Ad-375的对照。缺少的关键对照是：没有看到针对miR-375的genetic loss-of-function（如敲除小鼠）来排除siRNA/2'-O-me寡核苷酸本身的脱靶效应或adenovirus过表达的非生理剂量效应，这对确认miR-375生理功能的必要性和充分性很重要；此外文中提到"additional targets of miR-375 are likely to contribute"，说明缺少对Mtpn是否为唯一或主要功能靶点的rescue实验对照（如miR-375过表达+Mtpn过表达回补）。</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>【摘要未报告数字】读全文时优先补：miR-375 过表达使 GSIS 降低的具体百分比或 fold-change 及统计显著性；抑制内源 miR-375 后分泌增强的具体幅度；Mtpn siRNA phenocopy 效应的量化对比数值。</t>
+          <t>效应量数字均可从正文抄出：①Ad-375在MOI 50使miR-375表达增加约2.5倍，25 mM葡萄糖刺激的胰岛素分泌降低约40%（对应Fig. 2a,b及正文"led to an ~2.5-fold increase...resulted in an ~40% reduction"）；②capacitance实验中control为837±244 fF（n=9）对比Ad-375的94±27 fF（n=10，P&lt;0.01），降幅85%（Fig. 3d,e，正文明确给出）；③Ca2+/EGTA灌流实验中DC/Dt在Ad-375细胞降低63%（P&lt;0.001，n=15–17，Fig. 3f,g），MIN6细胞中降低&gt;80%；④2'-O-me-375使葡萄糖刺激胰岛素分泌增强1.4倍（相对2'-O-me-eGFP对照，Fig. 1f）；⑤si-Gck使glucokinase蛋白降低70%（Fig. 1e）；⑥luciferase实验中2'-O-me-375+pRL-Mtpn组荧光活性相对对照增加约2倍（n=6，Fig. 4e,f）；⑦si-Mtpn使胰岛素分泌降低约35%（Fig. 4h），使exocytosis降低约60%（Fig. 4i）；⑧docked granules数量在Ad-375感染细胞中增加35%（Supplementary Fig. 4，正文提及）。</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
@@ -4732,7 +4749,11 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】需从参考文献里挑三类：①miR-375 靶基因预测算法及原始 miRNA 克隆鉴定方法的方法学文献（用于评估其保守性分析是否可迁移到 miR-29/miR-33）；②同时期发表的其他胰岛特异 miRNA 功能研究（用于判断该领域后续是否已有人做 miR-375 降解/半衰期方向，评估竞争风险）；③Mtpn（myotrophin）在 exocytosis 通路中的分子机制原始文献（判断该靶基因通路是否与 TDMD/ZSWIM8 通路有交叉点）。</t>
+          <t>1. Bartel, D. P. 2004《MicroRNAs: genomics, biogenesis, mechanism, and function》Cell — miRNA生物发生/功能综述，是理解ZSWIM8介导TDMD及miRNA稳态调控（方向①③）的基础背景文献。
+2. Tsuboi, T., da Silva Xavier, G., Leclerc, I. &amp; Rutter, G. A. 2003《5′-AMP-activated protein kinase controls insulin-containing secretory vesicle dynamics》J. Biol. Chem. — 直接建立AMPK对胰岛分泌颗粒/代谢调控的机制，与方向①"AMPK磷酸化ZSWIM8加速代谢miRNA的TDMD→代谢记忆"高度相关，值得排队细读AMPK下游底物逻辑。
+3. Zhao, C., Wilson, M. C., Schuit, F., Halestrap, A. P. &amp; Rutter, G. A. 2001《Expression and distribution of lactate/monocarboxylate transporter isoforms in pancreatic islets and the exocrine pancreas》Diabetes — 涉及胰岛中乳酸转运体表达，与方向③"乳酸/乳酰化修饰AGO2/ZSWIM8/TUT4-7"的代谢-表观遗传联系直接相关，可作为乳酸代谢在内分泌组织中作用的背景支持。
+4. Lewis, B. P., Shih, I. H., Jones-Rhoades, M. W., Bartel, D. P. &amp; Burge, C. B. 2003《Prediction of mammalian microRNA targets》Cell — miRNA靶点预测方法学基础，可用于方向②中miR-29对纤维化相关靶基因（如MYBPC3、SAA3通路）的靶点分析。
+5. Lagos-Quintana, M. et al. 2002《Identification of tissue-specific microRNAs from mouse》Curr. Biol. — 组织特异性miRNA鉴定方法，对方向②中比较心脏（MYBPC3）与肠道（SAA3）组织中miR-29等纤维化相关miRNA的组织特异性表达提供方法学参考。</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4768,7 +4789,7 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>仅摘要（无开放全文）</t>
+          <t>全文已读 · 你提供的 PDF · asn1462.pdf</t>
         </is>
       </c>
       <c r="G33" s="2" t="n">
@@ -4809,7 +4830,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】读全文时要找：(1) miR-29 microarray/real-time PCR 检测的是成熟体还是同时测了 pri-miR-29/pre-miR-29；(2) ChIP 或启动子结合实验的图（Smad3 ChIP-seq/ChIP-qPCR 具体结合位点图号）；(3) 是否有 pri-miR-29 与成熟 miR-29 的时间动力学对比图，用以区分转录 vs 降解贡献比例；(4) 有无第二种独立方法（如 nuclear run-on 或 actinomycin D chase）验证转录抑制而非降解加速。</t>
+          <t>Fig.9（A-G）是本文对读者第②方向（TUT4/7/miR-29/器官纤维化，可与其 SAA3 肠、MYBPC3 心脏存档组织类比）最关键的图：在已建立的 UUO 肾纤维化模型（day 4起治疗、day 10取材）中，超声-微泡介导的miR-29b基因转移恢复了miR-29b水平（A，real-time PCR），并同步降低了Masson三色染色纤维化（B）、collagen I免疫组化沉积（C、D定量）及collagen I mRNA/蛋白（E real-time PCR，F/G Western blot定量）。可信度：每组至少6只小鼠（据Fig.11图注推断同批实验为≥6 mice/组），采用了独立的mRNA（real-time PCR）与蛋白（IHC+WB）两种方法交叉验证同一结论，并有Fig.10（collagen III）作为平行独立指标重复同一效应方向，提示结果较稳健。但正文未给出Fig.9的具体n值和确切统计量，只能依据Fig.11图注"at least six mice"做推断，不能确认Fig.9本身的n。</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4824,12 +4845,12 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】读全文时要逐条核对：(1) 是否设置了 pri-miR-29 转录本定量作为转录活性的独立读出，与成熟体表达分开报告；(2) Smad3 ChIP 是否有 IgG/non-binding site 阴性对照；(3) miR-29b 递送实验是否有 scrambled miRNA 对照及递送效率对照；(4) 体外实验是否检测了 TUT4/7 或其他末端修饰/降解酶的表达变化作为排除性对照（若未检测，则该文完全没有排除降解层面贡献）。</t>
+          <t>文中明确做的对照包括：①UUO对照 vs 正常(normal)小鼠；②Smad3 WT vs Smad3 KO小鼠（UUO模型）；③MEF细胞中Smad3 WT vs Smad3 KO vs Smad2 WT/KO，用以区分Smad3依赖 vs Smad2非依赖效应（Fig.2A）；④NRK52E细胞中Smad3 knockdown vs empty vector control（Fig.2D-G，CTL标注）；⑤Dox诱导miR-29b过表达 vs 非doxycycline处理细胞（Fig.4、Fig.6A）；⑥miR-29b knockdown（pSuper-sh-miR-29b）vs对照质粒（Fig.5、Fig.6B）；⑦基因治疗中UUO+control plasmid vs UUO+miR-29b转染（Fig.7、9、10、11，CV=control vector）。缺少的关键对照：全文未提及针对AGO2/ZSWIM8/TUT4-7本身的表达或活性检测，也没有miR-29 3′端尿苷化（uridylation）或TUTase相关的直接测定，这对读者方向②（miR-29尿苷化机制）而言是重要缺口，说明本文只证明miR-29丰度受Smad3转录调控，未涉及其3′修饰/降解通路。此外也未见针对乳酸/乳酰化（方向③）的任何处理或对照。</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>【摘要未报告数字】读全文时优先补：miR-29（尤其miR-29b）在 WT vs Smad3 KO 中下降/升高的倍数（fold change）、miR-29b 过表达/knockdown对collagen I/III mRNA或蛋白表达的抑制/增强幅度百分比、ultrasound递送后纤维化评分（如Masson染色阳性面积)的具体统计数值。</t>
+          <t>正文给出的定量数字主要是统计显著性符号而非具体倍数：如"*P&lt;0.05, **P&lt;0.01, ***P&lt;0.001 versus normal mice; #P&lt;0.05, ##P&lt;0.01, ###P&lt;0.001 versus Smad3 WT UUO"（Fig.1图注），以及TGF-β1处理浓度均为"2 ng/ml"，doxycycline浓度为"2 μg/ml for 24 hours"（Fig.2、4、6图注）。Smad3-binding site位于miR-29b2启动子上游"22 kb"处（Fig.3A、正文）。全文未见miR-29 fold-change、collagen蛋白变化倍数或Fig.9-11中各定量分析的具体数值——【全文未见定量数字】：抽取文本中Fig.1B提到"List of fold changes of miRNAs"但未给出具体数字，Fig.9D/G、Fig.10B/E、Fig.11B/E仅描述"quantitative analysis"而未在给到文本中列出实际数值。</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
@@ -4864,7 +4885,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】需从参考文献里挑三类：①miR-29 在其他纤维化器官（肺、肝、心）中被 Smad3 或其他转录因子调控的后续验证文献，用于判断转录机制的普适性边界；②TUT4/7或其他尿苷转移酶在肾/肝纤维化中的独立报道，用于检验是否已有人在同一模型里做过降解层面的排除实验；③本文作者后续（Chung lab等）关于miR-29递送治疗纤维化的临床转化文献，用于评估该转录轴的下游竞争强度和专利/临床占位情况。</t>
+          <t>1. van Rooij E, et al. 2008《Dysregulation of microRNAs after myocardial infarction reveals a role of miR-29 in cardiac fibrosis》Proc Natl Acad Sci USA — 与读者方向②直接相关，miR-29心脏纤维化机制可与其MYBPC3心脏存档组织对照验证。2. Roderburg C, et al. 2011《Micro-RNA profiling reveals a role for miR-29 in human and murine liver fibrosis》Hepatology — 提供miR-29在另一器官纤维化中的表达谱证据，可类比肠道SAA3组织中miR-29的作用。3. Maurer B, et al. 2010《MicroRNA-29, a key regulator of collagen expression in systemic sclerosis》Arthritis Rheum — 揭示miR-29对胶原表达的调控机制，与本文collagen I/III结果呼应，有助于理解miR-29-fibrosis轴的普适性。4. Chung AC, Huang XR, Meng X, Lan HY 2010《miR-192 mediates TGF-beta/Smad3-driven renal fibrosis》J Am Soc Nephrol — 同一实验室对Smad3下游另一miRNA(miR-192)的研究，方法学（UUO模型、Smad3 KO）与本文高度一致，值得排队比较miRNA稳态调控范式。</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4900,7 +4921,7 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>仅摘要（无开放全文）</t>
+          <t>全文已读 · 你提供的 PDF · ASN.2011010055.pdf</t>
         </is>
       </c>
       <c r="G34" s="2" t="n">
@@ -4941,7 +4962,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】读全文时要找：(1)是否用qRT-PCR或northern blot分别测了pri-miR-29/pre-miR-29与mature miR-29，还是只测了mature miR-29（若只有mature体一个数据，则无法排除降解机制，摘要中"reduced expression"这一措辞下用的具体图/表编号需核实）；(2)三种肾纤维化模型（造模方法、时间点）的具体图号，判断是急性转录抑制窗口还是慢性稳态改变；(3)fasudil恢复miR-29表达的实验是否同时测了pri-miR-29，以判断ROCK抑制作用的是转录还是降解通路。</t>
+          <t>Fig.4A–C是本文最关键的机制图：用collagen I、IVa1、IVa3的3'UTR luciferase报告基因证明TGF-b1可提高报告基因活性，而miR-29a/b/c共转染能阻止甚至逆转该升高，可信度较高，因为三个不同靶基因3'UTR均重复出现一致效应，且*P&lt;0.05标注统计显著。Fig.4D进一步用miR-29结合位点突变体做了独立验证——突变后miR-29a/b/c不再能抑制luciferase活性，证明效应具有序列特异性而非非特异性抑制，这是本文对miR-29直接靶向collagen 3'UTR最有力的双重证据（野生型+突变体对照）。Fig.5A/D和Fig.7C则是体内证据，分别在糖尿病apoE小鼠(n=7/组)和adenine诱导纤维化小鼠(n=3/组)中重复观察到miR-29a/b/c下降，但样本量较小、依赖qPCR单一方法，可信度弱于体外luciferase实验。</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4956,12 +4977,12 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】读全文时要逐条核对：①TGF-β1处理是否设了未处理对照及载体/scramble miRNA对照；②三种肾纤维化模型是否各自设了sham/vehicle对照；③fasudil实验是否有unmodified纤维化组和健康对照组三臂设计；④luciferase报告基因实验是否包含3'UTR突变对照（去除miR-29结合位点）以证明结合特异性；⑤是否测了miR-29前体（pri-/pre-miR-29）作为区分转录vs降解的关键对照，这是本篇能否被引用为"降解证据"的核心缺口。</t>
+          <t>文中明确做的对照包括：miR-C（scrambled control miRNA）转染对照（Fig.2A-C、Fig.4A-C）、未处理/vehicle对照细胞（NRK52E、podocytes、mesangial cells的TGF-b1处理均设未处理对照组）、以及Fig.4D中miR-29结合位点突变的3'UTR luciferase构建体作为序列特异性对照，证明效应依赖miR-29直接结合而非非特异性影响。体内部分Fig.6A设了C-VE(非糖尿病)、D-VE(糖尿病+vehicle)、D-FA(fasudil治疗)、D-LOS(losartan治疗)四组对照。缺少的关键对照：全文未提及anti-miR-29或miR-29 antagomir的功能丧失实验（loss-of-function），只做了miR-29过表达（gain-of-function），无法排除内源miR-29是否为collagen调控所必需；此外Fig.5和Fig.7的体内miR-29下降未见针对ZSWIM8/TUT4-7等miRNA稳态调控通路的机制对照，是否经典TDMD降解未做区分。</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>【摘要未报告数字】读全文时优先补：TGF-β1处理后miR-29a/b/c各自下降的倍数或百分比、collagen I/IV mRNA与蛋白上调的定量倍数、三种肾纤维化模型中miR-29表达降低的具体数值、以及fasudil给药后miR-29恢复的定量幅度，摘要仅给出方向性描述（reduced/increased/low levels）没有具体效应量。</t>
+          <t>Mesangial cells中TGF-b1处理后miR-29a、miR-29b、miR-29c分别下降28%、46%、37%（P&lt;0.05，出自Fig.3B对应正文一句"a significant decrease in miR-29a, miR-29b, and miR-29c levels (28%, 46%, and 37%, respectively; P&lt;0.05 compared with controls)"）。NRK52E细胞中miR-29a相对丰度比miR-29b高10倍、比miR-29c高5倍（Fig.1F）；在小鼠肾脏中miR-29a比miR-29b高14倍、比miR-29c高4倍（Fig.5D）。转染效率方面，转染后miR-29a/b/c表达比未转染细胞高1000倍（正文提及，对应Supplemental Figure 1，非主图）。糖尿病apoE小鼠实验n=7/组（Fig.5A），adenine模型n=3/组（Fig.7A）。</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
@@ -4996,7 +5017,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】要从参考文献里挑三类：①该团队或他人是否有专门测miR-29前体(pri/pre-miR-29)动力学或半衰期的方法学文献（用于设计他自己的half-life实验）；②TUT4/7或其他3′尿苷化酶作用于miR-29的机制文献（判断是否已有人抢占方向2的核心假设）；③fasudil/Rho-kinase通路与miRNA稳态关系的后续文献（判断该药理对照是否已被别人用在纤维化-miRNA降解交叉研究中）。</t>
+          <t>Sengupta S et al. 2008《MicroRNA 29c is down-regulated in nasopharyngeal carcinomas, up-regulating mRNAs encoding extracellular matrix proteins》Proc Natl Acad Sci U S A — 与方向②直接相关，是miR-29下调导致ECM蛋白上调的经典范例，可为TUT4/7对miR-29尿苷化调控机制提供比较对象。van Rooij E et al. 2008《Dysregulation of microRNAs after myocardial infarction reveals a role of miR-29 in cardiac fibrosis》Proc Natl Acad Sci U S A — 与方向②的MYBPC3心脏纤维化存档组织高度相关，miR-29在心脏纤维化中的作用可直接类比肾脏机制。Roderburg C et al. 2011《Micro-RNA profiling reveals a role for miR-29 in human and murine liver fibrosis》Hepatology — 补充miR-29在肝纤维化中的保守作用，有助于跨器官比较TUT4/7-miR-29-纤维化轴。Maurer B et al. 2010《MicroRNA-29, a key regulator of collagen expression in systemic sclerosis》Arthritis Rheum — 提供miR-29调控collagen的另一疾病模型佐证，可用于方向②机制的横向验证。</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -5032,7 +5053,7 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>仅摘要（无开放全文）</t>
+          <t>全文已读 · 你提供的 PDF · micro-rna-profiling-mir-29</t>
         </is>
       </c>
       <c r="G35" s="2" t="n">
@@ -5073,7 +5094,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】读全文时要找：(1)miR-29a/b/c三个成员是否分别检测pri-miRNA/pre-miRNA水平（qPCR的specific stem-loop primer设计），若只测成熟体则无法排除降解层贡献；(2)人肝组织与血清miR-29a定量的具体图/表（fold change、n值、cirrhosis vs early fibrosis vs healthy分组样本量）；(3)HSC中TGF-β/LPS处理后miR-29下调的时间曲线（是否做了actinomycin D chase或pri-miRNA/mature比值，用以区分转录vs降解）；(4)是否有第二种方法（如northern blot验证miR-29 3′端是否有uridylation加尾）。</t>
+          <t>Fig. 3C 支持"miR-29b 在肝纤维化中特异性下调、与胶原上调相关"这一主张：从 CCl4 处理6周的 C57BL/6 小鼠肝脏中经 FACS 分离原代 HSC（5只小鼠混合），qPCR 检测显示 miR-29b 出现"&gt;2000-fold"的剧烈下调，同时伴随 Col1a1 与 aSma 上调。Fig. 2A/B 则是跨遗传背景（Balb/c 与 C57BL/6，n=5 与 n=4-6/组）、跨时间点（6周与8周）的重复验证，且用了两种独立纤维化模型（CCl4 与胆管结扎 Fig. 2D）互证，可信度较高，但文中未给出这些图的具体统计检验方法（仅在正文中提及*P&lt;0.05等星号标注）。Fig. 6A（血清 miR-29a）用了 box-whisker plot 并标注 ***P&lt;0.001，但未见具体样本量 n，需结合 Supporting 材料核实。</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -5088,12 +5109,12 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】读全文时要逐条核对的对照清单：①CCl4/BDL模型是否有vehicle/sham对照及时间点梯度；②人组织队列是否按fibrosis stage分层且有年龄/性别/病因（酒精性vs病毒性vs NASH）匹配对照；③血清miR-29a检测是否有内参miRNA（如miR-16/cel-miR-39 spike-in）校正及hemolysis质控；④HSC体外实验TGF-β/LPS处理是否有receptor抑制剂/NF-κB抑制剂回复实验证明因果而非相关；⑤miR-29b过表达实验是否有scramble mimic对照及剂量-效应关系；⑥是否检测了pri-miR-29/pre-miR-29水平作为转录活性直接对照（这是区分转录vs降解假设的核心对照，摘要未提及需重点核对）。</t>
+          <t>文中明确做了的对照包括：CCl4 处理组 vs. 溶剂(oil)对照组（Fig. 1A、2A、2B）；胆管结扎(BDL) vs. 假手术(sham)对照（Fig. 2D）；HSC 转染 miR-29b mimic vs. 转染112.5 ng scrambled miRNA 作为阴性对照（Fig. 4B-D）；人肝组织纤维化/肝硬化样本 vs. 非纤维化肝对照（Fig. 3E、Fig. 2E/F）；血清 miR-29a 患者 vs. 健康对照（Fig. 6A）。缺少的关键对照：文中未提及 miR-29 抑制剂(antagomir/LNA)体内敲低实验，也没有 rescue 实验（例如同时敲低 miR-29 靶基因验证特异性），这对确认 miR-29 与胶原表达的因果关系（而非相关性）很重要；此外未见针对 TUT4/7 尿苷化或 AGO2/ZSWIM8 乳酰化相关机制的任何对照，说明本文与 Sheldon 三个方向中的分子修饰机制无直接对照数据。</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>【摘要未报告数字】摘要中无具体fold change、p值或n值数字。读全文时优先补：①miR-29a/b/c在CCl4和BDL模型中下调的fold change及统计量；②人晚期纤维化肝组织miR-29表达下降幅度及患者例数n；③血清miR-29a在肝硬化vs健康对照/早期纤维化之间的具体倍数差异及ROC/AUC（若做了biomarker性能评估）；④miR-29b过表达后collagen mRNA/蛋白下降的具体百分比。</t>
+          <t>正文给出的准确数字：①Fig. 3C 提及原代 HSC 中 miR-29b 在纤维化肝脏中出现"&gt;2000-fold"下调（对应正文"a dramatic (&gt;2000-fold) down-regulation"一句）；②Fig. 6A 血清 miR-29a 下调标注为 ***P&lt;0.001；③Fig. 2A/B/D 及 Fig. 5A 多处星号标注 *P&lt;0.05, **P&lt;0.01, ***P&lt;0.001，但未给出具体倍数；④样本量方面 Fig. 2A n=5/组，Fig. 2B n=4-6只/组，Fig. 2D n=4/组，Fig. 5A n=3/组，Fig. 3C/D 细胞来自2-5只小鼠混合。④关于 miR-29 差异表达 miRNA 数目：正文明确"31 miRNAs were differentially regulated"，其中"10 miRNAs were significantly overexpressed"，"21 miRNAs showed a significantly lower expression"（对应 Fig. 1A/B 及其相邻正文句）。</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
@@ -5128,7 +5149,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】读全文时要从参考文献里挑三类：①miR-29转录调控机制的后续/上游文献（TGF-β/Smad3直接结合miR-29启动子/pri-miRNA的ChIP证据，用于评估转录解释的"强度上限"）；②miR-29在其他器官纤维化（肺、肾、心脏）中的验证性文献，用于评估跨器官一致性及是否有人已经做过pri/mature区分；③本文引用的miRNA芯片/qPCR方法学原始文献，核实其检测的是否为成熟体特异性引物，从而判断是否存在检测层面掩盖降解信号的可能。</t>
+          <t>1. van Rooij E, et al. 2008《Dysregulation of microRNAs after myocardial infarction reveals a role of miR-29 in cardiac fibrosis》Proc Natl Acad Sci U S A — 与方向②高度相关，miR-29 在心脏纤维化中的作用可直接对照 Zou 手头的 MYBPC3 心脏存档组织中 miR-29 尿苷化研究。 2. Mott JL, Kobayashi S, Bronk SF, Gores GJ. 2007《mir-29 regulates Mcl-1 protein expression and apoptosis》Oncogene — miR-29 靶基因调控机制的经典参考，可为方向②的下游功能验证提供思路。 3. Xiong Y, et al. 2010《Effects of microRNA-29 on apoptosis, tumorigenicity, and prognosis of hepatocellular carcinoma》HEPATOLOGY — 补充 miR-29 在肝脏疾病中的功能谱，可用于方向②肠/肝纤维化组织比较背景。 4. Seki E, De Minicis S, Osterreicher CH, Kluwe J, Osawa Y, Brenner DA, et al. 2007《TLR4 enhances TGF-beta signaling and hepatic fibrosis》Nat Med — 涉及 TLR4/TGF-b/NF-kB 通路调控纤维化，对理解方向②器官纤维化的上游炎症信号（可能与代谢/乳酸信号交叉）有参考价值。</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -5164,7 +5185,7 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>仅摘要（无开放全文）</t>
+          <t>全文已读 · 你提供的 PDF · AJRCMB452287.pdf</t>
         </is>
       </c>
       <c r="G36" s="2" t="n">
@@ -5205,7 +5226,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】需去核对：(1) 图中 miR-29 表达定量用的是 Northern blot 还是 qPCR，是否报告了绝对拷贝数/半衰期数据；(2) IMR-90 knockdown 实验中 miR-29 前体(pri/pre)与成熟体是否分别测定，用什么方法（Northern探针位置）区分；(3) TGF-β1 处理时间点是否早到足以排除继发效应，是否有 actinomycin D 或类似转录抑制实验估算 miR-29 半衰期；(4) 是否有第二种独立方法（如 in situ hybridization 定量）验证miR-29 空间分布与靶基因反相关。</t>
+          <t>Fig. 2A是支持"miR-29水平与其下游纤维化靶基因表达呈负相关"这一核心主张的关键图：bleomycin处理后miR-29逐渐下降，D28降至最低，随后D70、D140逐渐恢复，而Col3A1、Col4A1的表达与miR-29水平呈镜像变化。可信度方面，该图基于qRT-PCR定量数据，并有Fig. 1B（miRNA array结果，*P&lt;0.05）和Fig. 2B–2E（ISH+Masson trichrome染色的独立影像学方法）交叉验证同一现象，属于两种独立方法（分子定量+组织原位）互证，但正文未给出该图具体的生物学重复次数（n）。另外Fig. 4A–D用IMR-90细胞的LNA knockdown/mimic实验（qRT-PCR、Western、Sircol assay）从功能上验证了miR-29对COL4A1、NID1、COL1A1及可溶性胶原水平的调控，是体外机制层面可信度较高的图。</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -5220,12 +5241,12 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】需逐条核对：①miR-29 knockdown 效率对照（scramble antagomir/anti-miR对照）；②TGF-β1处理是否有中和抗体或受体抑制剂对照以确认特异性；③miR-29表达下降是否有转录本(pri-miR-29)水平对照以排除单纯转录调控；④博来霉素模型是否有生理盐水对照组及时间点对照；⑤IMR-90表达谱分析是否有多次生物学重复及统计校正方法。</t>
+          <t>文中明确做了的对照包括：bleomycin处理组均设置了PBS注射的对照组（如Fig. 2B vs 2C，Fig. 3C vs 3F）；LNA knockdown实验设置了scrambled LNA oligo对照（Fig. 4A，"but not with scrambled LNA oligos"）；miR-29 mimic实验设置了control oligo对照（Fig. 4B，"as compared with control oligos"）；3'UTR luciferase实验设置了野生型vs突变型miR-29结合位点对照，以及miR-29 mimic vs miR-365 mimic的miRNA特异性对照（Fig. 5）。缺少的关键对照：文中未提及体内bleomycin模型中miR-29的rescue实验（例如外源补充miR-29 mimic能否逆转纤维化表型），这对确认miR-29下降是纤维化的因还是果很重要；此外Table 1所列基因芯片比较也未见针对anti-miR-29处理设置多个非靶向序列对照，仅提到scrambled LNA，无法完全排除LNA脱靶效应。</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>【摘要未报告数字】读全文时优先补：miR-29下降的具体倍数(fold change)、与纤维化评分的相关系数(r或p值)、TGF-β1处理后miR-29抑制的时间曲线和IC50/剂量、knockdown后靶基因上调的倍数范围。</t>
+          <t>miRNA array共检测609个miRNA，其中49个在bleomycin处理肺组织中at least one time point显著上下调（P&lt;0.05，fold changes&gt;2.0，出自p4正文及Table E2引用句）。Table 1列出anti-miR-29/SCR处理下多个基因的定量倍数变化，例如COL1A1 fold change=1.29（P=6.74E-02，应为E-03量级，原文数值6.74E-03）、COL3A1=1.56（P=1.03E-02）、COL4A1=1.53（P=1.33E-02）、NID1=2.05（P=1.20E-02）、ITGA11=1.38（P=1.03E-02），同表还列出对应TGF-β/CTRL处理下的fold change，如COL4A1在TGF-β组为4.46（P=2.31E-04）。这些数字均出自Table 1"CATEGORIES OF GENES ENRICHED IN UP-REGULATED GENE LIST IN miR-29 KNOCKDOWN CELLS"。</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
@@ -5260,7 +5281,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】需从参考文献里挑三类：①miR-29转录调控机制原始文献（TGF-β/Smad3抑制miR-29的分子机制论文，确认竞争解释的源头）；②miR-29降解/半衰期或miRNA 3′修饰相关文献（若有引用TUT4/7或尿苷化相关工作，确认是否已被涉及）；③本文引用的miR-29其他器官纤维化（心、肾、肝）功能验证文献，用于评估他跨组织（心脏/肠）外推的合理性。</t>
+          <t>1. van Rooij E, Sutherland LB, Thatcher JE, et al. 2008《Dysregulation of microRNAs after myocardial infarction reveals a role of miR-29 in cardiac fibrosis》Proc Natl Acad Sci USA — 首次将miR-29与心脏纤维化关联，直接对应Sheldon方向②的MYBPC3心脏纤维化存档组织应用场景。2. Maurer B, Stanczyk J, Jungel A, et al. 2010《miR-29 is a key regulator of collagen expression in systemic sclerosis》Arthritis Rheum — 证明miR-29抑制胶原表达的机制在皮肤纤维化中同样成立，可与肠道SAA3纤维化模型的miR-29机制做跨组织比较。3. Pandit KV, Corcoran D, Yousef H, et al. 2010《Inhibition and role of let-7d in idiopathic pulmonary fibrosis》Am J Respir Crit Care Med — 与本文并列讨论的肺纤维化miRNA研究，提供let-7/miR-21/miR-29在同一bleomycin模型中的miRNA稳态调控范式，可为方向①③中miRNA稳态重编程机制提供比较框架。4. Liu G, Friggeri A, Yang Y, et al. 2010《Mir-21 mediates fibrogenic activation of pulmonary fibroblasts and lung fibrosis》J Exp Med — 展示TGF-β通路下游miRNA介导纤维化激活的机制，可与TUT4/7-miR-29尿苷化影响器官纤维化的方向②形成互补参考。</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -5294,9 +5315,9 @@
           <t>https://pubmed.ncbi.nlm.nih.gov/20201077/</t>
         </is>
       </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>仅摘要（无开放全文）</t>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>仍缺全文</t>
         </is>
       </c>
       <c r="G37" s="2" t="n">
@@ -5428,7 +5449,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>全文已读 · PMC13510581</t>
+          <t>全文已读 · PMC · PMC13510581</t>
         </is>
       </c>
       <c r="G38" s="2" t="n">
@@ -5560,7 +5581,7 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>全文已读 · PMC2759306</t>
+          <t>全文已读 · PMC · PMC2759306</t>
         </is>
       </c>
       <c r="G39" s="2" t="n">
@@ -5692,7 +5713,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>全文已读 · PMC3651781</t>
+          <t>全文已读 · PMC · PMC3651781</t>
         </is>
       </c>
       <c r="G40" s="2" t="n">
@@ -5824,7 +5845,7 @@
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>仅摘要（无开放全文）</t>
+          <t>全文已读 · 你提供的 PDF · 1-s2.0-S1097276508006606-m</t>
         </is>
       </c>
       <c r="G41" s="2" t="n">
@@ -5865,7 +5886,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】需确认：(1)尿苷化位点数与后果关系的图（单尿苷vs寡尿苷，判断是否此文已区分或需看后续TUT4/7/Zcchc11文章）；(2)up-let-7的定量方法（Northern blot深度测序？RT-qPCR？半衰期测定用什么方法-pulse chase还是actinomycin D chase）；(3)是否有体外重组Lin28+TUT反应的第二种验证方法（in vitro uridylation assay）。</t>
+          <t>Figure 3A/3B 是本文核心图：Figure 3A 显示对 FLAG-Lin28a 免疫沉淀后，northern blot 检测到 pre-let-7a 上方出现一条延伸约18 nt的模糊带（星号标记的 up-let-7），而 ZFD 点突变的 Lin28a（mt）能结合 pre-let-7 却不能产生该延伸带，说明锌指结构域是催化尾巴延伸的关键；qRT-PCR 用于估算 IP 效率，SD 来自两组数据。Figure 3B 通过凝胶纯化+3′adaptor 连接+RT-PCR+克隆测序确定该延伸序列为14 nt、主要由U组成的3′尾（该U序列不在基因组中，说明是Drosha切割后添加），并以 RNase H/oligo-dA18 切割实验（Figure S8，非本图但正文提及）进一步佐证U尾存在。Figure 4A/4B 用体外尿苷化实验独立验证：合成pre-let-7a-1与含Lin28的细胞提取物+UTP孵育才出现延伸带（Lin28缺失或用ZFD突变体则无），且重组Lin28b蛋白（0、15、30、60、200 nM）呈剂量依赖方式诱导尿苷化，构成了对Figure 3体内结果的第二种独立方法（体外重组系统）验证，可信度较高。</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5880,12 +5901,12 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】需要核对的对照清单：(1)Lin28 knockdown/knockout对照是否恢复let-7成熟体；(2)尿苷化位点数目（单尿苷化vs寡尿苷化）是否分别对应不同的Dicer加工/降解命运，需要找突变尿苷化酶催化活性位点的对照；(3)是否有非let-7 pre-miRNA作为特异性对照排除Lin28非特异效应；(4)体外重组系统中TUT4/7身份是否已在此文确认（此文2008年可能尚未鉴定出TUT4/7为催化酶，需查是否只是描述现象而非机制酶）。</t>
+          <t>文中明确做了的对照包括：(1) Lin28 ZFD点突变体（mt）作为催化死亡对照，用于证明单纯结合pre-let-7不足以诱导尿苷化（Figure 3A、4Aa）；(2) 转录负性Drosha突变体（TN Drosha）作为Drosha处理被完全阻断的阳性对照，用以区分Lin28作用是否发生在Drosha步骤（Figure 2A）；(3) miR-16-1/pre-miR-16及pre-miR-30a作为非let-7家族miRNA的特异性对照，证明Lin28诱导的尿苷化对let-7家族具有特异性（Figure 2A、4Ab、Figure S7/S9）；(4) 核质分离效率对照（RT-PCR和WB检测分离效率，Figure 2B）；(5) 体外降解实验中使用转录负性Dicer突变体，排除Dicer加工对pre-let-7降解速率的影响（Figure 4E）。文中未提及对Lin28敲减/过表达效率之外设置shRNA非靶向对照（如scrambled siRNA）的描述，也未看到对尿苷化转移酶（TUTase）本身进行敲低或抑制的直接功能性对照实验（正文仅推测其存在），这一缺失对于确认尿苷化酶身份及排除提取物中其他核酸酶/聚合酶活性干扰是重要的。</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>【摘要未报告数字】读全文时优先补：uridylated pre-let-7占总pre-let-7的比例、Lin28过表达后let-7成熟体下降倍数、up-let-7半衰期与未尾部修饰pre-let-7半衰期的对比数值。</t>
+          <t>正文中定量数字有限，多为定性描述或图注中未给出具体数值。可确认的定量信息：内源性up-let-7克隆比例——从Hep3B、Huh7、HepG2三种细胞克隆的let-7序列中，分别有26%、11%、15%的测序克隆带有3′U尾（正文"Multiple clones from these cells (26%, 11%, and 15% of the sequenced let-7 clones) contained 3′ U tails"）；up-let-7的3′尾长度为14 nt（Figure 3B相关正文："the long RNA species had 3′ terminal extension of 14 nt"）；延伸带比pre-let-7a-1长约18 nt（正文"18 nt longer than pre-let-7a-1"，对应Figure 3Aa星号带）；重组Lin28b蛋白体外尿苷化实验的剂量梯度为0、15、30、60、200 nM（Figure 4B）。除此之外，Figure 1、2、4等图注和正文未给出具体的倍数变化、p值或n值，【故其余效应量（如let-7上调倍数、pre-let-7减少百分比）全文未见定量数字】，仅有"markedly reduced"、"slightly but reproducibly reduced"等定性描述。</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
@@ -5920,7 +5941,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】需要从参考文献里挑三类：(1)确立TUT4/7/Zcchc11为催化酶身份的后续论文（如Heo 2009 Cell, Hagan 2009 NSMB）；(2)DIS3L2作为寡尿苷化RNA降解酶的鉴定文献（Chang 2013/Ustianenko）；(3)本文引用的Lin28-let-7早期发现文献（Viswanathan 2008 Science）以确认let-7调控的历史脉络及与miR-29/TDMD领域交叉引用情况。</t>
+          <t>1) Newman, M.A., Thomson, J.M., and Hammond, S.M. (2008)《Lin-28 interaction with the Let-7 precursor loop mediates regulated microRNA processing》RNA — 与方向①③相关，同期独立报道Lin28与let-7前体loop的互作机制，可与ZSWIM8/TUT4-7对pre-miRNA的识别模式对照，值得排队理解RNA结合蛋白如何通过loop结构调控miRNA命运。2) Rybak, A., Fuchs, H., Smirnova, L., Brandt, C., Pohl, E.E., Nitsch, R., and Wulczyn, F.G. (2008)《A feedback loop comprising lin-28 and let-7 controls pre-let-7 maturation during neural stem-cell commitment》Nat. Cell Biol. — 涉及lin-28/let-7反馈环在细胞命运决定中的作用，对理解TUT4/7-miR-29在纤维化器官重编程中的类似反馈环（方向②）有直接参考价值。3) Viswanathan, S.R., Daley, G.Q., and Gregory, R.I. (2008)《Selective blockade of microRNA processing by Lin28》Science — 与本文同一时期报道Lin28对let-7加工的选择性阻断，是理解TUTase家族特异性识别miRNA前体（可外推至AGO2/ZSWIM8乳酰化修饰特异性，方向③）的重要背景文献。4) Ibrahim, F., Rohr, J., Jeong, W.J., Hesson, J., and Cerutti, H. (2006)《Untemplated oligoadenylation promotes degradation of RISC-cleaved transcripts》Science — 提出非模板寡聚腺苷化促进RISC切割产物降解的机制，与TUT4/7尿苷化-降解轴（方向②的miR-29尿苷化研究）具有直接可比性，值得排队比较poly(A)/poly(U)尾在miRNA稳态调控中的异同。5) Li, J., Yang, Z., Yu, B., Liu, J., and Chen, X. (2005)《Methylation protects miRNAs and siRNAs from a 3′-end uridylation activity in Arabidopsis》Curr. Biol. — 揭示甲基化保护miRNA免受3′尿苷化的机制，可为方向③中乳酰化修饰如何调控TUT4/7识别底物提供修饰竞争/保护机制的参照框架。</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5956,7 +5977,7 @@
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>仅摘要（无开放全文）</t>
+          <t>全文已读 · 你提供的 PDF · 1-s2.0-S0092867409009647-m</t>
         </is>
       </c>
       <c r="G42" s="2" t="n">
@@ -5997,7 +6018,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】读全文时要找：(1)体外重组TUT4+Lin28+pre-let-7尾长/尿苷数的定量胶图及n值；(2)TUT4 knockdown后pre-let-7与mature let-7比例变化的定量(qPCR/northern)，区分pri/pre/mature三种形式的图；(3)是否有第二种独立方法（如CLIP或体外结合实验）验证GGAG motif特异性识别，而非仅靠序列比对推断。</t>
+          <t>Figure 1B（qRT-PCR + semiquantitative RT-PCR）支持"TUT4 knockdown 通过转录后机制特异性抑制 let-7 生物合成"：在 mES 细胞(R1)中敲低 TUT4 48 hr 后，let-7a/let-7g/let-7f 的成熟体上调而 pri-let-7 不变，标准误来自两次独立实验，可信度中等（仅两次重复，未见第二种独立方法如 Northern blot 交叉验证该图）。Figure 3A（in vitro uridylation assay）支持"TUT4 需与 Lin28 共同作用才能尿苷化 pre-let-7"：用免疫沉淀的 FLAG-TUT4 WT 与催化死突变体(D1011A)对比，在加入 0.5 mM recombinant Lin28a/b 及 0.25 mM UTP 后才出现约100 nt 的 up-let-7a-1 条带，催化死突变体不产生延伸带，说明该活性依赖 TUT4 自身催化位点而非污染蛋白，可信度较高（有阴性对照 pre-miR-16-1 和突变体对照）。Figure 7A 支持"含 GGAG 序列motif 的 pre-miRNA（miR-107/143/200c 等）同样受 Lin28/TUT4 调控"，标准差来自三次（有GGAG组）和两次（无GGAG组）独立实验，属于图注中明确标注的重复数。</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -6012,12 +6033,12 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】读全文时逐条核对：①是否设置TUT4催化死突变体作为阴性对照；②Lin28 knockdown后TUT4蛋白/mRNA水平是否作为对照检测（排除TUT4本身表达变化的混杂）；③非GGAG motif miRNA作为阴性对照是否检测尿苷化水平；④pri-let-7转录本水平是否作为对照排除转录层调控干扰（这对区分他的"降解假设"至关重要）。</t>
+          <t>文中明确做的对照包括：①阴性对照 RNA pre-miR-16-1（贯穿 Figure 1A、2A-2C、3A/B、7A，用于证明 TUT4/Lin28 对 pre-let-7 的特异性）；②催化死突变体 TUT4(D1011A) 作为酶活性对照（Figure 3A），排除污染蛋白导致尿苷化；③核/质分离对照，用 tubulin（胞质）和 hnRNP C 或 lamin（核）监测分级效率（Figure 2D、2E）；④siRNA 特异性对照，用另一条针对 TUT4 mRNA不同位置的siRNA排除脱靶效应（正文提及"data not shown"）；⑤NTP 特异性对照，比较 UTP/ATP/CTP/GTP（Figure 3C）。缺少的关键对照：全文未提及体内(in vivo)敲低 TUT4 后直接检测 pre-let-7 尿苷化水平变化的定量数据，也未见 TUT4 在非 let-7 家族广泛 miRNA 上的全转录组敲低验证（仅 Figure 5A 做了 microarray，但未在本段文本中详细展开对照设计），这类全局性对照对排除 TUT4 通过其他非 Lin28 依赖途径影响 miRNA 稳态很重要。</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>【摘要未报告数字】读全文时优先补：①TUT4 knockdown后let-7成熟体下降的具体倍数/百分比；②寡尿苷化尾的长度分布（几个U）；③干细胞标记基因下降的定量数值。</t>
+          <t>正文明确给出的定量数字：TUT4 敲低后 let-7a、let-7g、let-7f 成熟体水平上升 2 到 4 倍（"increased by 2- to 4-fold upon TUT4 knockdown"，见 Figure 1B 对应正文段，标准误来自两次独立实验）；而 miR-16 水平未变化。In vitro uridylation 反应中使用的浓度为 0.5 mM recombinant Lin28、0.25 mM UTP（Figure 3A 图注），以及低浓度对照 0.025 mM NTP（Figure 3C）。Figure 7A 的标准差来自三次（含GGAG组）和两次（不含GGAG组）独立实验。除此之外全文提供的其余效应量均为图内条带强度描述性比较，未见更多具体倍数或 p 值。</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
@@ -6052,7 +6073,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】读全文时要从参考文献里挑三类：①Lin28诱导pre-let-7尿苷化的原始报道（Heo et al. 2008前作）确认本文是否为独立发现还是延续；②pre-miRNA末端环motif识别的结构生物学后续文献，用于比对miR-29是否含同源motif；③同期或稍早关于TUTase家族（TUT4/7/ZCCHC11命名沿革）的综述或原始鉴定文献，理清TUT4与TUT7命名对应关系，避免方向2中试剂/抗体设计出错。</t>
+          <t>Heo, I., Joo, C., Cho, J., Ha, M., Han, J., and Kim, V.N. (2008). Lin28 mediates the terminal uridylation of let-7 precursor MicroRNA. Mol. Cell 32, 276–284. — 本文的直接前作，建立了 Lin28 介导 pre-let-7 尿苷化的现象学基础，是理解 ZSWIM8/TUT4-7 与 miRNA 稳态关系的必读背景。Katoh, T., Sakaguchi, Y., Miyauchi, K., Suzuki, T., Kashiwabara, S., and Baba, T. (2009). Selective stabilization of mammalian microRNAs by 30 adenylation mediated by the cytoplasmic poly(A) polymerase GLD-2. Genes Dev. 23, 433–438. — 展示同类 noncanonical PAP（GLD2/TUTase2）通过单腺苷化稳定成熟 miR-122，与方向③"乳酸/乳酰化修饰重编程 miRNA 稳态"中 TUT 家族酶的代谢调控机制形成对照，值得排队比较。Rybak, A., Fuchs, H., Smirnova, L., Brandt, C., Pohl, E.E., Nitsch, R., and Wulczyn, F.G. (2008). A feedback loop comprising lin-28 and let-7 controls pre-let-7 maturation during neural stem-cell commitment. Nat. Cell Biol. 10, 987–993. — 提供 Lin28/let-7 反馈环在神经干细胞命运决定中的功能证据，与方向②TUT4/7-miR-29-器官纤维化的组织特异性调控逻辑相关，可用于比较不同组织中 TUTase-miRNA 轴的下游表型。Viswanathan, S.R., Daley, G.Q., and Gregory, R.I. (2008). Selective blockade of microRNA processing by Lin28. Science 320, 97–100. — 与本文同期独立证实 Lin28 选择性阻断 let-7 加工，为方向①中"选择性靶向特定 miRNA 家族"的机制类比提供参照文献。</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -6088,7 +6109,7 @@
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>仅摘要（无开放全文）</t>
+          <t>全文已读 · 你提供的 PDF · 1-s2.0-S0092867412011294-m</t>
         </is>
       </c>
       <c r="G43" s="2" t="n">
@@ -6129,7 +6150,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】读全文时要找：(1) group I vs group II pre-miRNA 的分类图/表及各自比例，是否给出全基因组统计的 n 值；(2) TUT7/4/2 敲低后 let-7 成熟体 vs pre-let-7 水平变化的定量图（qPCR/Northern，需看 fold change 和统计检验）；(3) 体外重建实验（recombinant TUT + dsRNA substrate）中 1nt→2nt overhang 转化效率的定量方法（酶动力学或电泳定量）；(4) 是否有第二种方法（如深度测序读出 pre-miRNA 3'端异质性）验证 mono- vs oligo-uridylation 的区分。</t>
+          <t>Fig 3B/3D：体外重构实验显示mono-uridylation显著提升Dicer加工效率——mono-uridylated pre-let-7a-1较未修饰对照被纯化Dicer切割更高效（两次独立实验测定加工效率，误差棒为SD），pre-let-7b差异更为剧烈（未修饰几乎不被切割，mono-U后被高效切割），可信度较高因为用了纯化蛋白的正交生化验证而非仅细胞表型。Fig 2B–D是另一组关键图，显示同时敲低TUT7/TUT4/TUT2（siTUT mix）使pre-let-7a积累而成熟let-7a下降，并用两次独立northern blot定量（Fig 2C，配对单尾t检验，*p&lt;0.05, **p&lt;0.01）及测序数据（Fig 2D，Fisher精确检验***p&lt;0.001）支持，属于细胞内功能验证与生化重构互相印证的组合，可信度较高。</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -6144,12 +6165,12 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】读全文时要逐条核对：①TUT7/4/2 三者单独 vs 联合敲低的表型是否有冗余互补（决定他方向2里敲哪个基因）；②是否用 catalytically dead TUT mutant 作阴性对照排除非催化功能；③Lin28 存在/不存在细胞系中 mono- vs oligo-uridylation 的比例对照（ES cells vs 体细胞）是否用同一批 pre-let-7 底物；④miR-105/let-7 之外是否检验了其他 group II miRNA（如摘要提到但未展开的成员）作为普遍性对照。</t>
+          <t>做了的对照：Fig 1D/S1C-D 用催化死突变体（TUT7 D1060A、TUT2 D215A、TUT4 D1011A）排除污染酶活性的可能；Fig S1E 做了NTP特异性对照（换用其他NTP代替UTP）证明TUT7/4对U特异而TUT2利用范围更广；Fig 2A 用GAPDH作为western loading control，Fig 2B 用tRNA-lys作为northern loading control，并平行探测miR-16作为非let-7 miRNA的特异性对照（TUT敲低对miR-16影响不显著）；此外用了siDicer作为阳性对照比较TUT敲低效应强度，以及三组不同siRNA序列组合（siTUT mix之外两套）排除off-target效应（Fig S2A–C）。缺少的关键对照：文中未提及对TUT7/4/2三重敲低后let-7功能性下游读出（如let-7靶基因蛋白水平或细胞表型/增殖分化指标）的直接验证，也未做体内rescue实验（过表达WT酶挽救敲低表型）来确认表型是敲低特异性而非脱靶累积效应，这对确证TUTs是let-7生物合成必需组分而非仅参与稳态很重要。</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>【摘要未报告数字】读全文时优先补：①group II pre-miRNA（1nt overhang）占全部 pre-miRNA 的具体比例（摘要仅说"the majority of let-7 and miR-105"）；②TUT 敲低后 let-7 成熟体下降的 fold change 及统计显著性；③体外尿苷化反应对 1nt overhang 底物的催化效率（Km/kcat 或百分比转化）。</t>
+          <t>正文Figure 1A明确数字：145个pre-let-7克隆中，20%为mono-uridylated（Mono-U），60%为未修饰，1%为mono-A，14%为trimmed，5%为others。正文结果段落陈述：TUT7/4/2同时敲低（siTUT mix）后，mono-uridylated pre-let-7比例从20%降至3%（对应Fig 2D测序数据，Fisher精确检验p&lt;0.001）。TUT4与pre-let-7相互作用时长为1.1±0.2秒（引用Yeom et al. 2011单分子SIMPlex数据，正文p3段落）。Fig 2C的northern定量给出统计显著性标注（*p&lt;0.05, **p&lt;0.01）但未在提供文本中给出具体倍数数值。</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
@@ -6184,7 +6205,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】读全文时要挑三类参考文献：①定义 group I/II pre-miRNA 分类标准的原始文献（Drosha 切割位点异质性的结构基础）；②Lin28-TUT4-oligouridylation 促降解 pre-let-7 的经典文献（Heo et al.），用于对比本文"促加工"的反例机制；③TUT7/4/2 在其他 miRNA（尤其代谢相关 miR-33/375）生物合成中的后续功能研究，判断是否已有人做过方向2/方向3 的雏形工作。</t>
+          <t>Heo, I., Joo, C., Kim, Y.K., Ha, M., Yoon, M.J., Cho, J., Yeom, K.H., Han, J., and Kim, V.N. (2009). TUT4 in concert with Lin28 suppresses microRNA biogenesis through pre-microRNA uridylation. Cell 138, 696–708. — 与方向①②高度相关，是TUT4/Lin28介导pre-let-7 oligo-uridylation的关键前作，Sheldon可用于对比mono- vs oligo-uridylation的机制差异及代谢/纤维化背景下的功能分歧。 Jones, M.R., Quinton, L.J., Blahna, M.T., Neilson, J.R., Fu, S., Ivanov, A.R., Wolf, D.A., and Mizgerd, J.P. (2009). Zcchc11-dependent uridylation of microRNA directs cytokine expression. Nat. Cell Biol. 11, 1157–1163. — 直接将TUT4(Zcchc11)介导的miRNA尿苷化与细胞因子/炎症表型联系，对方向②器官纤维化中TUT4/7-miR-29轴的下游功能提供参考模型。 Burns, D.M., D'Ambrogio, A., Nottrott, S., and Richter, J.D. (2011). CPEB and two poly(A) polymerases control miR-122 stability and p53 mRNA translation. Nature 473, 105–108. — TUT2(GLD2)介导miRNA 3′端修饰调控稳定性的代表性工作，对方向③理解TUT2/TUT4-7介导的miRNA稳态重编程机制有参考价值。 Katoh, T., Sakaguchi, Y., Miyauchi, K., Suzuki, T., Kashiwabara, S., Baba, T., and Suzuki, T. (2009). Selective stabilization of mammalian microRNAs by 3' adenylation mediated by the cytoplasmic poly(A) polymerase GLD-2. Genes Dev. 23, 433–438. — 同样涉及TUT2对miR-122稳定性的3′端修饰机制，可与方向③中乳酸/乳酰化对AGO2/TUT酶活性调控的假设做类比参考。</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -6220,7 +6241,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>全文已读 · PMC4720960</t>
+          <t>全文已读 · PMC · PMC4720960</t>
         </is>
       </c>
       <c r="G44" s="2" t="n">
@@ -6352,7 +6373,7 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>全文已读 · PMC12790862</t>
+          <t>全文已读 · PMC · PMC12790862</t>
         </is>
       </c>
       <c r="G45" s="2" t="n">
@@ -6484,7 +6505,7 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>全文已读 · PMC5209279</t>
+          <t>全文已读 · PMC · PMC5209279</t>
         </is>
       </c>
       <c r="G46" s="2" t="n">
@@ -6616,7 +6637,7 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>全文已读 · PMC11405050</t>
+          <t>全文已读 · PMC · PMC11405050</t>
         </is>
       </c>
       <c r="G47" s="2" t="n">
@@ -6748,7 +6769,7 @@
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>全文已读 · PMC7757243</t>
+          <t>全文已读 · PMC · PMC7757243</t>
         </is>
       </c>
       <c r="G48" s="2" t="n">
@@ -6878,9 +6899,9 @@
           <t>https://pubmed.ncbi.nlm.nih.gov/42622514/</t>
         </is>
       </c>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>仅摘要（无开放全文）</t>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>仍缺全文</t>
         </is>
       </c>
       <c r="G49" s="2" t="n">
@@ -7012,7 +7033,7 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>全文已读 · PMC5957472</t>
+          <t>全文已读 · PMC · PMC5957472</t>
         </is>
       </c>
       <c r="G50" s="2" t="n">
@@ -7144,7 +7165,7 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>全文已读 · PMC12334188</t>
+          <t>全文已读 · PMC · PMC12334188</t>
         </is>
       </c>
       <c r="G51" s="2" t="n">
@@ -7276,7 +7297,7 @@
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>仅摘要（无开放全文）</t>
+          <t>全文已读 · 你提供的 PDF · 1-s2.0-S1097276522002076-m</t>
         </is>
       </c>
       <c r="G52" s="2" t="n">
@@ -7317,7 +7338,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】需确认：(1)两个乳酰化位点的具体残基编号及是否位于ZnF1/ZnF2哪个锌指亚域；(2)位点鉴定方法——是质谱(LC-MS/MS)鉴定还是仅靠序列比对+抗乳酰化抗体验证，质谱覆盖率/PTM谱图需要看方法学图；(3)位点突变体(K→R或K→Q)做了哪些功能实验（RNA结合EMSA/RIP、m6A水平qPCR-m6A/MeRIP-seq、下游Jak1蛋白翻译、STAT3磷酸化、小鼠肿瘤生长）分别对应哪几个图号；(4)是否有第二种独立方法（如CETSA、体外重组蛋白乳酰化+RNA pull-down）交叉验证乳酰化-RNA结合因果性。</t>
+          <t>Fig 6A显示BM-Mφ与MC38经Transwell共培养后培养基及MC38肿瘤组织中L-乳酸浓度升高（乳酸检测试剂盒定量），支持"肿瘤微环境乳酸积累"的主张；Fig 6B/C为WT BM-Mφ与BM-MDSC经25 mM L-lactic acid处理不同时间后的western blot，显示METTL3等蛋白水平变化，属单次实验描述、图注未标注重复次数与统计方法。Fig 7A用分子对接（MOE软件）预测METTL3结构域（MTD、ZFD）与L-乳酸的结合亲和力，Fig 7B为LC-MS鉴定的METTL3乳酸化(Kla)位点，Fig 7C用IP方法在293T细胞中经FLAG-METTL3转染+25 mM乳酸处理后验证METTL3乳酸化，属于计算预测+质谱+免疫共沉淀三种独立方法互相印证，可信度较高，但正文片段未提供具体n值或重复次数。</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -7332,12 +7353,12 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】需逐条核对：①乳酰化位点突变体是否有等量表达对照（WB确认蛋白稳定性不受突变影响）；②是否设置乳酸剥夺/LDHA抑制剂或乳酸添加的剂量-反应对照以证明乳酸依赖性而非其他代谢物；③H3K18la与METTL3自身乳酰化是否用了乳酰化特异性抗体的特异性对照（如competing free-lactyl肽段封闭实验）；④myeloid METTL3 KO小鼠是否有细胞类型特异性对照（如非髓系条件性KO）排除脱靶效应；⑤m6A-YTHDF1-JAK1轴是否有YTHDF1功能缺失回复实验作为因果链对照。</t>
+          <t>明确做了的对照包括：Fig 1D/E中CRC肿瘤组织(T)与配对癌旁正常组织(N)的对照（two-tailed paired t test分析METTL3 MFI）；Fig 2A-C以及正文中WT（Mettl3fl/fl）与cKO（LysM-cre Mettl3fl/fl）小鼠/细胞的基因型对照；Fig 6D中siRNA-NC与siRNA-Ldha对照以验证乳酸生成酶LDHA对METTL3蛋白水平的必要性；Fig 4A/B中WT与cKO MDSC按不同MDSC/T细胞比例（1:1或2:1）配对比较T细胞增殖与IFN-γ产量。缺少的关键对照：给到的文本片段中未见METTL3乳酸化位点（如K281/K345）的点突变（乳酸化位点突变体如K-to-R/Q）与野生型METTL3的功能性对照实验描述，这类对照对证明"乳酸化位点本身"（而非乳酸处理的其他继发效应）介导ZFD捕获RNA能力的因果关系至关重要，但本次提供文本中未显示该实验细节。</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>【摘要未报告数字】读全文时优先补：①两个乳酰化位点的乳酰化修饰化学计量比（stoichiometry, % modified）；②位点突变后RNA结合能力/m6A水平下降的定量倍数；③myeloid METTL3 KO后肿瘤体积/重量的定量数据及p值；④乳酸浓度-METTL3表达量的剂量反应曲线数值。</t>
+          <t>正文摘录中给出的定量数字有限：Fig 3legend提及WT小鼠n=9–16、cKO小鼠具体n值未完整给出（"cKO, n ="后文本被截断）；Fig 4B中WT MDSC n=12、cKO MDSC n=12；Fig 1F/G的Kaplan-Meier生存分析及log rank test均报告p&lt;0.05；Fig 1H/I的单变量与多变量Cox回归分析同样报告p&lt;0.05。Fig 6/7涉及的乳酸浓度、METTL3蛋白倍数变化、乳酸化位点富集程度等具体数值，在给到的图注与正文片段中【未见定量数字】，仅有定性描述（如"significantly increased"），故这部分效应量无法从当前文本中抄出准确数字。</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
@@ -7372,7 +7393,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】需从参考文献中挑三类：①乳酰化发现的奠基文献（Zhang et al. 2019 Nature首次报道组蛌乳酰化H3K18la的方法学论文，核对质谱鉴定乳酰化位点的标准流程）；②METTL3/m6A调控机制的经典文献（用于理解m6A-YTHDF1-JAK1/STAT3轴在其他免疫细胞中的验证方式，可能对方向1代谢miRNA的m6A/降解交叉调控有参考价值）；③TIMs/肿瘤微环境乳酸代谢相关文献（了解乳酸浓度梯度测量方法，为方向3设计乳酸剂量反应实验提供对照值参考）。</t>
+          <t>Irizarry-Caro, R.A. et al. (2020) 《TLR signaling adapter BCAP regulates inflammatory to reparatory macrophage transition by promoting histone lactylation》Proc. Natl. Acad. Sci. USA — 与方向③高度相关，展示了乳酸化(lactylation)如何调控巨噬细胞表型转变，可为AGO2/ZSWIM8乳酰化修饰提供方法学参照。Moreno-Yruela, C. et al. (2021)《Class I histone deacetylases (HDAC1‒3) are histone lysine delactylases》bioRxiv preprint — 提示组蛋白去乳酰化酶的存在，对方向③研究AGO2/ZSWIM8/TUT4-7乳酰化的可逆性及去修饰机制有直接参考价值。Liu, J. et al. (2020)《N6-methyladenosine of chromosome-associated regulatory RNA regulates chromatin state and transcription》Science — 展示m6A修饰调控RNA代谢与染色质状态的机制范式，可类比方向②TUT4/7尿苷化对miR-29代谢命运的调控逻辑。Diskin, C. et al. (2021)《Modification of proteins by metabolites in immunity》Immunity — 综述代谢物（包括乳酸）对蛋白质的翻译后修饰机制，与方向③"乳酸/乳酰化修饰重编程miRNA稳态相关酶"的整体假说框架高度契合。</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -7408,7 +7429,7 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>全文已读 · PMC10589265</t>
+          <t>全文已读 · PMC · PMC10589265</t>
         </is>
       </c>
       <c r="G53" s="2" t="n">
@@ -7540,7 +7561,7 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>仅摘要（无开放全文）</t>
+          <t>全文已读 · 你提供的 PDF · 1-s2.0-S0092867424003970-m</t>
         </is>
       </c>
       <c r="G54" s="2" t="n">
@@ -7581,7 +7602,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】读全文时要找：(1) AARS1 催化 lactate-AMP 生成及转乳酰化的体外重组酶实验图（底物特异性、Km/kcat 或至少定性动力学）；(2) 乳酰化位点鉴定的质谱图谱（LC-MS/MS 谱图、位点定位分数）；(3) 是否有第二种独立方法验证 K120/K139 乳酰化（如乳酰化特异抗体 western、突变体质谱对照）；(4) AARS1 全蛋白组底物列表图（火山图/维恩图），确认底物谱是否偏好特定结构域或序列motif，可类比判断 AGO2/ZSWIM8/TUT4-7 是否有潜在同源motif。</t>
+          <t>关键图为Figure 3A：MST（微量热泳动）分析显示纯化的EcAlaRS和HsAlaRS可直接结合lactate而不结合acetate，Kd分别约13 mM和35 mM；可信度较高，因为该结合还通过Figure 3B/3C的biotin-lactate pull-down（可被β-alanine竞争）以及Figure 3D的结构对接分析进行了独立验证，属于两种以上独立方法（MST+pull-down+结构对接）交叉印证。另外Figure 4/5系列图注均标注"Data are representative of three independent experiments"，说明关键生化实验至少重复三次，并用two-tailed Student's t test做统计。但对Sheldon三个方向（AMPK-ZSWIM8-TDMD、TUT4/7-miR-29-纤维化、乳酸修饰miRNA稳态酶）而言，本文未涉及miRNA/AGO2/ZSWIM8/TUT4-7的直接实验图，仅提供AARS1作为乳酸感受器/lactyltransferase的机制学范式，可作为方向③的方法学参考图。</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -7596,12 +7617,12 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】读全文时要逐条打勾：(1) 是否有 AARS1 catalytically-dead 突变体（如 aminoacylation-dead 但保留乳酰转移活性 vs 双失活）作为阴性对照；(2) 是否排除了其他已知乳酰转移酶（如 p300）对 p53 K120/K139 的贡献；(3) β-alanine 处理是否有剂量-反应曲线及对 AARS1 正常氨基酸活化（tRNA 装载）功能的影响对照，以排除非特异性毒性；(4) 患者队列分析是否校正了肿瘤分期/p53 突变状态等混杂因素。</t>
+          <t>文中明确做了的对照包括：MST和pull-down实验中以BSA或acetate作为阴性对照（Figure 3A、4C提到"does not bind to control BSA"，Figure 3A提到"not acetate"）；免疫共沉淀用control IgG作对照（Figure 4D）；siRNA实验设control siRNA（Figure 2D/E）；体内实验设Aarsfl/+ Cre−对照小鼠（Figure 7C/D）；TCL煮沸变性作为LCA阴性对照（正文"the TCLs for the 4th reaction were boiled at 95℃ for 5 min to denature proteins"）。缺少的关键对照：全文未见针对AGO2、ZSWIM8或TUT4/7的乳酸化/乳酰化特异性对照（如催化死突变体AARS1对这些蛋白乳酰化的直接验证），这对Sheldon方向③尤为重要，因为若要证明AARS1介导的乳酰化能重编程miRNA稳态酶，需要设立AARS1催化死突变（如5A突变体）处理这些蛋白的对照组，而本文只在p53和全局蛋白质组水平做了此类验证，未涉及miRNA通路蛋白。</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>【摘要未报告数字】读全文时优先补：AARS1 催化 lactate-AMP 生成的酶动力学参数（Km、kcat）；p53 K120/K139 乳酰化水平的定量百分比或 fold change；β-alanine 处理后肿瘤体积/生长曲线的具体抑制百分比及统计学 p 值；乳酰化与患者预后的 HR（hazard ratio）及 95% CI。</t>
+          <t>正文给出的准确数字包括：EcAlaRS与lactate的Kd约13 mM，HsAlaRS约35 mM（Figure 3A/正文）；β-alanine与EcAlaRS、HsAlaRS的Kd分别为2.7 mM和4.0 mM（Figure S5B/正文）；AARS1敲低后约80%的Klac肽段/蛋白强度下降，其中约10%下降超过10倍（正文引用Figure 2E/2F）；HsAlaRS过表达后约90%的Klac肽段/蛋白强度上升，其中近50%上升超过10倍（正文引用Figure 2H/2I）；p53K120Lac、K139Lac、DualLac对p53RE-DNA的结合亲和力分别下降约100倍、10倍和1000倍（正文引用Figure 5C–5E）；TCGA BRCA数据库中p53野生型患者n=633（Figure 1A）；IARC p53突变频率分析n=27,847（Figure 6A）。以上数字均直接出自给到的正文或图注文本，但均非Sheldon三个miRNA相关方向的直接数据。</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
@@ -7636,7 +7657,7 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】要从参考文献里挑三类：①组蛋白乳酰化奠基文献（Zhang et al. 2019 Nature，首次报道 histone lactylation）以确立乳酰化修饰的历史起点和检测方法学标准；②其他非组蛋白乳酰化底物文献（如糖酵解酶、代谢酶的乳酰化）以比较 AARS1 底物特异性与其他 writer（如 p300）的异同；③乳酰化蛋白质谱鉴定方法学文献（乳酰化特异抗体验证、质谱位点定位标准），用于评估他日后送样质谱合作时需要满足的证据标准。</t>
+          <t>从参考文献段中挑选与Sheldon三个方向相关性最高的几篇：1. Zhang, D. et al. (2019)《Metabolic regulation of gene expression by histone lactylation》Nature — 首次报道lactylation这一修饰类型，是方向③（乳酸/乳酰化重编程miRNA稳态酶）的机制起点，值得排队细读其修饰检测方法。2. Certo, M. et al. (2022)《Understanding lactate sensing and signalling》Trends Endocrinol. Metab. — 综述乳酸感知与信号转导，可为方向③中乳酸如何被AGO2/ZSWIM8/TUT4-7"感知"提供背景框架。3. Ron-Harel, N. et al. (2019)《T Cell Activation Depends on Extracellular Alanine》Cell Rep. — 涉及alanine/AARS相关代谢与细胞活化的联系，可能对理解AARS1底物竞争（β-alanine vs lactate）在其他代谢记忆情境（呼应方向①的代谢记忆概念）有参考价值。4. Li, X. et al. (2022)《Lactate metabolism in human health and disease》Signal Transduct. Target. Ther. — 综述乳酸代谢在疾病中的作用，可能涉及纤维化等器官病理背景，对方向②（TUT4/7-miR-29-器官纤维化）中乳酸代谢与纤维化关联的背景阅读有帮助。</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -7672,7 +7693,7 @@
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>全文已读 · PMC11725302</t>
+          <t>全文已读 · PMC · PMC11725302</t>
         </is>
       </c>
       <c r="G55" s="2" t="n">
@@ -7804,7 +7825,7 @@
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>全文已读 · PMC7935770</t>
+          <t>全文已读 · PMC · PMC7935770</t>
         </is>
       </c>
       <c r="G56" s="2" t="n">
@@ -7936,7 +7957,7 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>全文已读 · PMC11267267</t>
+          <t>全文已读 · PMC · PMC11267267</t>
         </is>
       </c>
       <c r="G57" s="2" t="n">
@@ -8068,7 +8089,7 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>全文已读 · PMC13578339</t>
+          <t>全文已读 · PMC · PMC13578339</t>
         </is>
       </c>
       <c r="G58" s="2" t="n">
@@ -8200,7 +8221,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>全文已读 · PMC5915372</t>
+          <t>全文已读 · PMC · PMC5915372</t>
         </is>
       </c>
       <c r="G59" s="2" t="n">
@@ -8332,7 +8353,7 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>全文已读 · PMC6907074</t>
+          <t>全文已读 · PMC · PMC6907074</t>
         </is>
       </c>
       <c r="G60" s="2" t="n">
@@ -8464,7 +8485,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>全文已读 · PMC6980783</t>
+          <t>全文已读 · PMC · PMC6980783</t>
         </is>
       </c>
       <c r="G61" s="2" t="n">
@@ -8596,7 +8617,7 @@
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>仅摘要（无开放全文）</t>
+          <t>全文已读 · 你提供的 PDF · 1-s2.0-S009286742100012X-m</t>
         </is>
       </c>
       <c r="G62" s="2" t="n">
@@ -8637,7 +8658,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】读全文时要找：(1) 文库设计与 sgRNA-变异对应关系的具体图（可能是 Fig.1），确认编辑窗口/PAM 限制如何限定可编辑碱基范围，能否推广到 ZSWIM8 S608/S609 等特定密码子；(2) BRCA1/2 阳性/阴性选择筛选的定量方法（存活率/enrichment score，第二种方法是否用测序read count做fold-change还是用统计模型如MAGeCK）；(3) ClinVar 52,034变异筛选的通量与假阳性率数据所在图表。</t>
+          <t>本文核心图为 Figure 2（B、C）：展示 BRCA1/BRCA2 tiling BE screen 中预测引入 nonsense 与 splice site 突变的 sgRNA 相对 silent 突变显著 depletion，用 Z score&lt;2 的百分比标注，可信度依据是三次重复（triplicate，&gt;10,000 cells/sgRNA 覆盖度）、replicate Pearson's r&gt;0.95，并与独立的 ClinVar gold-standard 数据集（AUC 0.85 for BRCA1, 0.96 for BRCA2）以及与 Findlay et al. 2018 的 SGE 数据（Pearson's r=0.44，HAP1 单独比较时 r=0.55）做了正交验证，属于双方法交叉确认。Figure 3（B–D）则用 sg1–sg13 的个体验证实验（day7/14/21 deep sequencing + CRISPResso2）进一步支持 Figure 2 的初筛结果，其中 sg5 的等位基因分析给出了具体可信度数字。这些数字均直接来自文中对应图注或紧邻正文陈述，未见 Sheldon 关注的 miRNA/TDMD/lactylation 相关内容，本文与三个研究方向（AMPK-ZSWIM8-TDMD、TUT4/7-miR-29-纤维化、lactate/lactylation-AGO2）无直接图或数据关联。</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -8652,12 +8673,12 @@
       </c>
       <c r="R62" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】读全文时要逐条核对：(1) 编辑效率/purity的对照（未编辑对照、synonymous/silent sgRNA对照）；(2) BRCA1/2已知LOF突变作为阳性对照的具体清单及其筛选中排名/富集倍数；(3) 是否有非靶效应（off-target editing、RNA editing byproduct）的对照实验；(4) ClinVar变异筛选中benign变异作为阴性对照的表现。</t>
+          <t>文中明确做的对照包括：non-targeting 与 intergenic sgRNA 作为阴性对照；靶向非必需细胞表面标志物的 sgRNA 作为 negative (targeting) controls（Figure 1B/E）；预测引入 no-edit 或 silent 突变的 sgRNA 作为内部阴性对照，用以估计假阳性率；以及用 wtCas9 平行筛选（A375、MELJUSO）验证 BE 特异性depletion而非guide表达失败（Figures S1F, S1G）。对于BRCA1/BRCA2筛选，还用ClinVar gold-standard P/LP vs B/LB变异集作为外部对照，以及与Findlay et al. 2018 SGE数据集比较作为正交方法对照。本文缺少的关键对照：没有提供针对Sheldon方向所需的miRNA稳态、TDMD相关基因（ZSWIM8、TUT4/7）或乳酸/乳酰化处理组的对照，因为本文主题是base editor screen评估DNA变异功能，与代谢miRNA调控无关，故无法从中获得相关对照信息。</t>
         </is>
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>【摘要未报告数字】读全文时优先补：BRCA1/BRCA2已知LOF突变筛选的精确率(precision)/AUC数值；BH3 mimetics和PARP inhibitors筛选中鉴定出的抗性/敏感突变的具体数目和effect size（如富集倍数、p值）；52,034个变异中最终功能注释成功（可分类为LOF/neutral）的比例。</t>
+          <t>效应量数字（均逐字抄自正文/图注）：Figure 1 legend提到"sgRNAs predicted to introduce nonsense mutations (n = 95) or splice site mutations (n = 37)"，Pearson's r = 0.44（Rule Set 2 score与depletion相关性，Figure 1C）。正文提到BE3.9max与BE4max性能对比："30.5% and 35.1% of sgRNAs predicted to introduce nonsense mutations or splice site-disrupting mutations, respectively, were depleted with a Z score &lt; 2, compared to 9.4% and 22.2% for BE4Max"。BRCA1/BRCA2部分："72% (44/61) and 77% (17/22) of sgRNAs predicted to introduce nonsense mutations or splice site mutations...scored as either strong or intermediate hits, in contrast to 21% (23/111) of silent sgRNAs"；ClinVar AUC="0.85 for BRCA1 and 0.96 for BRCA2"；BRCA1筛选"sensitivity of 0.70 and a specificity of 0.84"，BRCA2"sensitivity of 0.84 and a specificity of 0.86"；sg5验证"decreased from 46.2% of reads on day 7 post-transduction to 13.5% on day 21"（Z score = 6.57）。这些数字均与Sheldon的AMPK/TDMD/TUT4-7/lactylation三个方向无关，全文未见任何miRNA、ZSWIM8、TUT4/7或乳酸修饰相关的定量数字。</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
@@ -8692,7 +8713,7 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】读全文时要挑三类参考文献：①该文引用的其他CBE/ABE筛选平台方法学论文（如Cas9变体、编辑器优化文献），判断是否有更适合产生磷酸化模拟突变的新型编辑器；②BRCA1/2功能筛选相关的既往低通量验证研究，用作效应量比较基准；③ClinVar数据库及变异注释相关文献，评估其变异-表型映射方法能否直接迁移到miRNA降解酶基因。</t>
+          <t>本文参考文献表中检索后未见与Sheldon三个方向（①AMPK磷酸化ZSWIM8/TDMD；②TUT4/7-miR-29尿苷化-纤维化；③乳酸/乳酰化修饰AGO2/ZSWIM8/TUT4-7）直接相关的文献标题。参考文献列表主题集中于base editing技术（如Komor et al. 2016《Programmable editing of a target base in genomic DNA without double-stranded DNA cleavage》Nature）、BRCA1/BRCA2功能验证（Findlay et al. 2018《Accurate classification of BRCA1 variants with saturation genome editing》Nature）、以及MCL1/BCL2L1/PARP1药物筛选，均与miRNA代谢稳态、TDMD或蛋白乳酰化无关。唯一勉强相关的是Chen et al. 2019《miR-103/107 prolong Wnt/b-catenin signaling and colorectal cancer stemness by targeting Axin2》Sci. Rep.，因涉及miRNA功能但主题（Wnt通路/结直肠癌干性）与Sheldon三个方向（TDMD、纤维化、乳酰化）均不重合，价值有限。【全文未见与Sheldon三方向紧密相关的参考文献，故不做勉强推荐排队】。</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
@@ -8728,7 +8749,7 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>全文已读 · PMC7446397</t>
+          <t>全文已读 · PMC · PMC7446397</t>
         </is>
       </c>
       <c r="G63" s="2" t="n">
@@ -8858,9 +8879,9 @@
           <t>https://pubmed.ncbi.nlm.nih.gov/42763855/</t>
         </is>
       </c>
-      <c r="F64" s="4" t="inlineStr">
-        <is>
-          <t>仅摘要（无开放全文）</t>
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>仍缺全文</t>
         </is>
       </c>
       <c r="G64" s="2" t="n">
@@ -8992,7 +9013,7 @@
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>仅摘要（无开放全文）</t>
+          <t>全文已读 · 你提供的 PDF · nihpp-2026.01.05.697729v1.</t>
         </is>
       </c>
       <c r="G65" s="2" t="n">
@@ -9035,7 +9056,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】需确认：(1)cryo-EM解析的具体复合物组成及分辨率（图1-2附近）；(2)miRNA从AGO2口袋"挤出"的构象变化对比图，是否有不同miRNA/trigger对（尤其miR-29/miR-33/miR-375相关trigger）的验证；(3)是否有生化方法（如in vitro泛素化assay、体外重建体系）作为第二种独立验证手段，及其所用miRNA种类和浓度梯度；(4)ZSWIM8识别位点的关键残基突变数据是否可作对照。</t>
+          <t>Figure 1e-f 是最关键的可信度图：e 图用 in vitro co-IP（AGO2–miR-7 预结合放射标记的 trigger/seed-only 靶RNA，再加纯化的 ZSWIM8 拉下）证明 ZSWIM8 优先结合 trigger 复合物而非 seed-only 复合物，并用 TNRC6 来源的 T6B 肽作归一化对照，n=3 technical replicates，量化数据以符号+均值线呈现；f 图在此基础上加入 trigger 侧翼序列，同样用 co-IP 量化，n=3 technical replicates。Figure 2 是独立的结构验证（cryo-EM，整体分辨率3.1 Å），从另一角度（结构而非结合亲和力）支持 ZSWIM8 二聚体钳状包裹 AGO2–miR-7–trigger 复合物这一结论，二者互为独立方法印证。Figure 1c/d 是体外重组泛素化实验（荧光标记 AGO2*，SDS-PAGE 检测 AGO2*-UBn），显示 ZSWIM8-CUL3-ARIH1 特异性组合下才发生 trigger 依赖的多聚泛素化，但标注为代表性实验（representative experiment），n=2 technical replicates，重复次数偏低，需谨慎看待其统计强度。</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -9050,12 +9071,12 @@
       </c>
       <c r="R65" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】需要逐条核对的对照清单：①是否设置无trigger RNA或非cognate trigger的阴性对照复合物结构；②ZSWIM8识别界面突变体是否有泛素化活性丧失的功能对照；③是否用已知非TDMD底物miRNA-AGO2复合物作为特异性对照；④是否检测了ZSWIM8已知或潜在磷酸化位点（尤其S608/S609区域）在此结构中的位置及其是否位于AGO2/CUL3结合界面，这是判断竞争风险最关键的一条。</t>
+          <t>文中明确做了的对照包括：①seed-only 突变靶RNA（破坏与miRNA 3′区配对）作为阴性对照，证明单纯seed配对不足以驱动泛素化或ZSWIM8结合（Figure 1b-c,e-f）；②T6B肽（TNRC6来源，不区分靶RNA类型地结合AGO-miRNA）作为归一化对照，排除AGO2-miR-7与不同靶RNA结合量本身差异的干扰（Figure 1e-f, Extended Data Figure 1a）；③cullin/E2酶配对特异性对照，用CUL2-ARIH1、CUL5-ARIH2替换CUL3-ARIH1，证明只有ZSWIM8-CUL3-ARIH1组合能支持泛素化（Figure 1d）；④3′-supplementary pairing（仅7nt而非14nt互补）靶RNA作对照，证明弱的3′配对不足以驱动TDMD式识别（Extended Data Figure 1b,c）；⑤miRNA-trigger配对特异性交叉对照，miR-27a trigger HSUR1对miR-7-AGO2无效，miR-7 trigger CYRANO对miR-27a-AGO2无效（Extended Data Figure 1i）。给到的正文段落中未见到细胞内内源性ZSWIM8敲低/敲除后miRNA稳定性的直接对照（该类实验推测在其他图或既往文献22,23中），也未见到本次给出文本中提及乳酸/乳酰化相关的任何对照，这对Sheldon方向③（乳酸重编程AGO2/ZSWIM8/TUT4-7）而言是明显缺失——若要将本文结论外推到乳酰化调控，需要补充AMPK磷酸化状态或乳酰化修饰下ZSWIM8与AGO2结合能力的对照实验。</t>
         </is>
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>【摘要未报告数字】读全文时优先补：cryo-EM分辨率数值、复合物解离常数(Kd)或结合亲和力数据、体外多聚泛素化反应的动力学参数（如泛素化速率、AGO2降解半衰期的体外测定值），以及不同trigger/miRNA对（尤其是否覆盖miR-29/33/375相关trigger）之间选择性的定量比较。</t>
+          <t>Figure 1e：ZSWIM8与trigger结合的AGO2-miR-7复合物相比seed-only复合物有「up to 70-fold」的共沉淀富集（正文："up to 70-fold preference for co-IP of target RNAs with trigger pairing over seed-only pairing"）。Figure 1f：加入trigger侧翼CYRANO序列（增加85nt）后，co-IP效率提升「100-fold」，具体数值为无侧翼序列时需300 nM ZSWIM8才能达到15%的pulldown，而有侧翼序列时仅需3 nM（正文对应句）；且延长trigger序列后选择性仍保持「&gt;100-fold」（相对seed-only对照）。Figure 2：cryo-EM最终重建整体分辨率为3.1 Å（正文："The final reconstruction has an overall resolution of 3.1 Å"）。Figure 1j：细胞内TDMD报告基因实验中，ZSWIM8变体的显著性用one-way ANOVA + Dunnett's多重比较检验，标注"***P &lt; 0.0001"，n = 2 biological replicates。</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
@@ -9090,7 +9111,7 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】需要从参考文献里挑三类：①ZSWIM8/CUL3发现的原始文献（ref 22,23，Han et al./Shi et al. 2020 Cell类，确认是否已提及任何PTM线索）；②AGO2泛素化及其降解通路相关文献（是否有既往报道AGO2磷酸化如Hippo/EGFR通路调控AGO2稳定性，可作为方向3乳酸化假设的先例）；③本文引用的TDMD trigger RNA原始鉴定文献（ref 6-21），核对是否包含miR-29/33/375的已知trigger，用于判断该结构模型是否已经用这些具体miRNA验证过。</t>
+          <t>1. Shi, C. Y. et al. 2020《The ZSWIM8 ubiquitin ligase mediates target-directed microRNA degradation》Science 370, eabc9359 — 直接提出ZSWIM8介导TDMD的遗传学基础，是本文结构/生化机制工作的直接前身，对方向①（AMPK磷酸化ZSWIM8调控TDMD代谢记忆）至关重要。2. Han, J. et al. 2020《A ubiquitin ligase mediates target-directed microRNA decay independently of tailing and trimming》Science 370, eabc9546 — 与上文并列提出ZSWIM8-CUL3依赖的TDMD机制不依赖尾切修剪，对方向②（TUT4/7尾巴化与TDMD关系的区分）提供关键背景对照。3. Shi, C. Y. et al. 2023《ZSWIM8 destabilizes many murine microRNAs and is required for proper embryonic growth and development》Genome Res. 33, 1482–1496 — 提供ZSWIM8在小鼠组织中广泛调控miRNA稳定性的体内证据，可为方向②中MYBPC3心脏/SAA3肠存档组织中ZSWIM8-TDMD活性的组织特异性分析提供参照框架。4. Sheu-Gruttadauria, J. et al. 2019《Structural Basis for Target-Directed MicroRNA Degradation》Mol. Cell 75, 1243-1255.e7 — 早期AGO-miRNA-trigger结构工作，为本文cryo-EM结构比较（Figure 3a中提到PDB 6NIT）提供直接结构演化背景，对理解ZSWIM8如何识别AGO构象变化（方向③中乳酸/乳酰化可能通过改变AGO2构象间接影响TDMD）具参考价值。5. Kleaveland, B., Shi, C. Y., Stefano, J. &amp; Bartel, D. P. 2018《A Network of Noncoding Regulatory RNAs Acts in the Mammalian Brain》Cell 174, 350-362.e17 — 首次系统描述CYRANO-miR-7这一本文核心trigger-miRNA对的生理网络，为方向①中miR-7/CYRANO代谢记忆通路的功能背景提供支撑。</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
@@ -9126,7 +9147,7 @@
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>仅摘要（无开放全文）</t>
+          <t>全文已读 · 你提供的 PDF · s44318-026-00889-8.pdf</t>
         </is>
       </c>
       <c r="G66" s="2" t="n">
@@ -9167,7 +9188,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】读全文时要找：①19个高置信TDMD底物的鉴定标准（miRNA-seq在CRISPRi-ZSWIM8-KD前后的fold-change阈值、AGO2-eCLIP的peak calling参数）；②miR-29b-3p/miR-33a/b-5p是否区分了pri/pre-miRNA与成熟体丰度（关键：排除转录层TGF-β/Smad3抑制的混杂）；③非经典TDMD（SERPINE1→miR-30c-5p）机制图是在哪张图、是否有第二种方法（如降解动力学pulse-chase或actinomycin D半衰期测定）验证降解而非转录抑制；④是否有磷酸化/翻译后修饰相关的ZSWIM8调控证据（对方向1有无交叉）。</t>
+          <t>Fig 3F/3J–L 是本文最相关的关键图：Fig 3J,K 用 GFP 报告基因的“TDMD assay”证明 ABCA1 和 HADHB 的 MDE 能在 SUM159PT 和 MDA-MB-436 两种细胞中诱导 miR-33a-5p/miR-33b-5p 降解，并用 RT-qPCR 与 sRNA-Seq 两种方法交叉验证，可信度较高。Fig 3L 进一步做了 pri-miR-33、SREBF1/SREBF2 host gene 的对照，排除了转录层面的间接效应，增强了该结论的特异性。Fig 2E/2F 的 TDMD net effect 分析（N=3 生物学重复，L2FC≥0.3 阈值）支持 miR-29b-3p、miR-33a/b-5p 属于 19 个高置信 TDMD substrates，为 Sheldon 方向②（miR-29 相关）提供了独立数据支撑，但文中并未直接涉及 TUT4/7 尿苷化或乳酸乳酰化修饰，这两个方向在给到的文本里未见对应图。</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -9182,12 +9203,12 @@
       </c>
       <c r="R66" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】读全文时要逐条核对：①miR-29b-3p成熟体下降是否伴随pri-miR-29/pre-miR-29不变（排除转录抑制混杂，这是他领域公认的竞争解释）；②ZSWIM8 CRISPRi的敲低效率及off-target对照；③AGO2-eCLIP是否有IgG/input对照；④非经典TDMD是否用了蛋白酶体抑制剂(MG132)和ZSWIM8催化死突变体做双重排除对照；⑤NREP/SERPINE1过表达或敲低的剂量-反应对照及是否验证直接结合（3′端配对区域突变体）。</t>
+          <t>明确做了的对照：(1) ZSWIM8 KD 用三种独立 sgRNA（sgRNA28/34/42）加三种对照（Empty Vector、sgRNA LacZ、非靶向 Neg1），Fig 1B,C；(2) TDMD net effect 计算中用 pri-miRNA、host gene、matched-strand miRNA 作为 Test assay 排除转录效应（Fig 2B–D）；(3) Fig 3L 检测 pri-miR-33、SREBF1/SREBF2 排除 ABCA1/HADHB 过表达的转录性间接效应；(4) miR-eCLIP 用两个生物学重复复现 peak（Fig EV2B–D）。缺少的关键对照：文中提到 ABCA1、HADHB 的验证仅基于外源过表达的 TDMD assay，缺少对内源 MDE 的直接敲除/编辑对照（作者自己承认"perturbation experiments presented here are based on overexpression...conclusive demonstration...would require manipulation of the endogenous MDE"），这对确认这两个 trigger 在生理条件下真实驱动 TDMD 很重要。给到的文本中未见与 TUT4/7 尿苷化或 AGO2/ZSWIM8 乳酸乳酰化修饰相关的任何对照设计。</t>
         </is>
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>摘要中明确数字仅为"19个高置信TDMD底物"，其余（miR-29b-3p、miR-33a/b-5p、miR-30c-5p的降解幅度、耐药倍数、干性标志物变化）均未报告具体数值。【摘要未报告数字】读全文时优先补：miR-29b-3p/miR-30c-5p在ZSWIM8-KD或非经典TDMD阻断后的fold-change、NREP/SERPINE1表达量与miRNA降解的定量相关系数、紫杉醇IC50变化倍数。</t>
+          <t>从正文抄出的准确数字：ZSWIM8 KD 导致其表达下降 &gt;80%（Fig 1B，"produced a robust knockdown of the target (&gt;80% reduction of ZSWIM8 expression, Fig. 1B)"）；筛出 63 个候选 TDMD substrates（L2FC&gt;0.3，p&lt;0.05，Fig 1D,E），其中 28 个 FDR&lt;0.05，5 个多细胞系支持；33 个候选 substrates 中 17/33（27%）在多个细胞系中上调（Fig 1E 附近正文）；候选 substrates 平均积累幅度 average L2FC 0.79；最终获得 19 个高置信（HC）TDMD substrates，TDMD net effect ≥0.3 L2FC（Fig 2E,F），HC 集合平均 L2FC=0.97，net-effect L2FC=0.79（正文，Dataset EV1）；miR-eCLIP 共识别 983（对照组）和617（ZSWIM8 KD 组）reproducible chimeric genes，对应129个miRNA（Fig EV2E）；识别出16个 miRNA target occupancy 显著增加（average L2FC&gt;0.5，Fig 3C,D）；miR-eCLIP chimeric peaks 中 seed match 占比&gt;85%（Fig EV2D）。全文未见与 AMPK/ZSWIM8 S608/S609 磷酸化、TUT4/7 尿苷化、乳酸乳酰化修饰相关的定量数字。</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
@@ -9222,7 +9243,7 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】要从参考文献里挑三类：①ZSWIM8/TDMD原始机制文献（Han/Bartel等奠基性论文，确认经典TDMD的判定标准来源）；②非经典（ZSWIM8非依赖）miRNA降解此前是否有报道（判断本文"非经典TDMD"是否真正首创或已有先例，如XRN降解通路相关文献）；③miR-29/miR-33/miR-375在代谢或纤维化中的既有转录调控文献（尤其TGF-β/Smad3-miR-29那篇竞争解释论文，确认本文是否引用并回应了这一竞争假说）。</t>
+          <t>1. Bitetti A et al (2018)《MicroRNA degradation by a conserved target RNA regulates animal behavior》Nat Struct Mol Biol — NREP 作为 miR-29b-3p 内源 TDMD trigger 的原始发现，与 Sheldon 方向②（miR-29 纤维化）直接相关，可作为其 MYBPC3/SAA3 组织中 NREP-miR-29 轴的比较依据。 2. Li L et al (2021)《Widespread microRNA degradation elements in target mRNAs can assist the encoded proteins》Genes Dev — 提出 TDMD 中 trigger 结合但无降解的模型，为方向①中 ZSWIM8 磷酸化调控 TDMD 效率提供机制参照。 3. Han J, Mendell JT (2023)《MicroRNA turnover: a tale of tailing, trimming, and targets》Trends Biochem Sci — 综述 miRNA tailing/trimming 与 TUT4/7 相关机制，与方向②的 TUT4/7 尿苷化直接相关，值得排队细读。 4. Sheu-Gruttadauria J et al (2019)《Structural basis for target-directed microRNA degradation》Mol Cell — 阐明 AGO:miRNA 复合物构象变化及被 ZSWIM8 识别的结构基础，对方向③（乳酸乳酰化修饰 AGO2/ZSWIM8 如何影响该构象识别）有参考价值。 5. Simeone I et al (2022)《Prediction and pan-cancer analysis of mammalian transcripts involved in target directed miRNA degradation》Nucleic Acids Res — TDMDfinder 方法学来源及泛癌 TDMD 图谱，方向①②③均可能借鉴其预测框架来筛选新的 trigger/substrate 对。</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
@@ -9258,7 +9279,7 @@
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>仅摘要（无开放全文）</t>
+          <t>全文已读 · 你提供的 PDF · nihpp-2026.01.07.698237v1.</t>
         </is>
       </c>
       <c r="G67" s="2" t="n">
@@ -9301,7 +9322,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】读全文时要找：(1) mir-35家族miRNA在ebax-1突变体中丰度变化的定量图（qPCR或small RNA-seq，n值、fold change）；(2) 是否有pri/pre-mir-35 vs 成熟mir-35的区分实验（这是判断"降解假设"是否成立的关键，本文摘要未提及）；(3) viln-1 mRNA/蛋白上调的定量数据及其与mir-35结合位点突变的rescue实验；(4) EBAX-1的Cullin-2结合motif突变体的LCD表型图，是否有第二种独立方法（如降解速率测定/pulse-chase）验证TDMD而非转录抑制。</t>
+          <t>Figure 1e/f/g 是核心证据：Figure 1e 显示 L4-to-adult 转变后24小时 ebax-1(tm2321) 与 ebax-1(ju699) 两个独立缺失突变体 linker cell 存活频率相近（两个独立等位基因互相印证），Figure 1f 显示 ebax-1(tm2321) btbd-2(syb7669) 双突变体存活率高于任一单突变体，Figure 1g 显示野生型 ebax-1 基因组转基因可完全恢复 ebax-1(tm2321) 突变体的 linker cell death（回复实验证明表型确由 ebax-1 缺失所致）。此外 Figure 1i 用序列切片电镜（serial-section electron microscopy）在 0-2 小时（n=3）和24小时（n=1）两个时间点观察到 ebax-1 突变体 linker cell 保留核周异染色质、核膜无皱褶但线粒体/内质网仍肿胀，提供了形态学层面的独立验证，但样本量很小（n=1-3），可信度有限。</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -9316,12 +9337,12 @@
       </c>
       <c r="R67" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】读全文时要逐条打勾：①是否有ebax-1 Cullin-2 motif点突变（催化死亡对照）区分E3连接酶活性依赖与非依赖功能；②是否检测了mir-35前体（pri/pre）水平以排除转录/加工层面而非降解层面的效应；③viln-1 3'UTR的mir-35结合位点突变rescue对照，排除off-target效应；④是否用非LCD细胞类型或非dying时间点作为阴性对照证明时空特异性；⑤是否有ZSWIM8/EBAX-1蛋白水平或降解活性的直接生化验证（而非仅遗传上位关系）。</t>
+          <t>明确做了的对照包括：用两个独立缺失等位基因 ebax-1(tm2321) 和 ebax-1(ju699) 互相印证表型（Figure 2a, 1e）；用野生型 ebax-1 基因组转基因回复实验证明因果性（Figure 1g）；用 mig-24p::ebax-1（linker cell 特异性表达）恢复 rescue 而 lin-48p::ebax-1（U.I/rp 吞噬细胞特异性表达）不能 rescue，以此区分细胞自主性 vs 非自主性作用（Figure 2c）；用 auxin 处理时间窗口对照（L1-L3 阶段 vs L3 之后）确定 EBAX-1 起作用的发育时间点（Figure 2f,g）；用 eft-3 广谱启动子驱动 TIR1 与 mig-24p 特异性启动子驱动 TIR1 做比较（Supplementary Fig. 2a,b）。文中未提及的关键缺失对照：没有看到针对 miRNA TDMD 机制本身的直接生化验证（如 AGO 上 miRNA 定量、miRNA half-life 测定或 TDMD 靶标的直接 CLIP/降解实验），这些正文片段中没有出现，对判断 EBAX-1 是否真的通过 miRNA 降解发挥作用很重要，但从提供文本看未见。</t>
         </is>
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>【摘要未报告数字】读全文时优先补：ebax-1突变体中mir-35家族miRNA丰度的具体fold-change及统计量；viln-1表达上调的定量倍数；LCD表型的定量恢复比例（如"loss of mir-35 restores LCD to X%的ebax-1突变体"）。</t>
+          <t>效应量数字（均出自正文）：野生型young-adult 雄性中97%的 linker cell 在24小时后已完全降解或正在死亡（n=241，见 p6 "97% of linker cells in wild-type animals are fully degraded or dying at this stage (n=241)"）。ebax-1(tm2321) 突变体中0-2小时后44%的雄性表现 linker cell 存活，而携带 mig-24p::ebax-1 转基因（3个转基因株系检测）的 ebax-1(tm2321) 突变体中只有7%表现存活（Figure 2c，"44% of ebax-1(tm2321) mutant males exhibit linker cell survival 0-2 hours post the larva-to-adult molt, only 7% of ebax-1(tm2321) mutants carrying the mig-24p::ebax-1 transgene display surviving linker cells"）。电镜观察样本量为0-2小时 n=3，24小时 n=1（p7，Figure 1i）。</t>
         </is>
       </c>
       <c r="T67" s="2" t="inlineStr">
@@ -9356,7 +9377,7 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】需从参考文献里挑三类：①ZSWIM8/EBAX-1首次被鉴定为TDMD介导E3连接酶的奠基性文献（Bartel lab 2020年Science系列），核对本文机制描述与奠基工作的一致性；②C. elegans linker cell death既往UPS机制研究（本文作者前期工作），了解LCD领域历史脉络及是否有竞争实验室；③mir-35家族及其在线虫发育中功能的既往文献，判断该miRNA家族是否有哺乳动物功能同源类比可借鉴到miR-29/miR-33/miR-375。</t>
+          <t>25. Han, J. et al. 2020《A ubiquitin ligase mediates target-directed microRNA decay independently of tailing and trimming》Science — 与 EBAX-1/ZSWIM8 介导的 TDMD 机制直接相关，是本文 TDMD 假说的核心引用之一，对方向①最相关。26. Shi, C. Y. et al. 2020《The ZSWIM8 ubiquitin ligase mediates target-directed microRNA degradation》Science — ZSWIM8（EBAX-1 哺乳动物同源蛋白）介导 TDMD 的原创发现文献，是理解 AMPK-ZSWIM8-TDMD 通路的基础背景文献，强烈建议排队。39. Stubna, M. W., Shukla, A. &amp; Bartel, D. P. 2024《Widespread destabilization of C. elegans microRNAs by the E3 ubiquitin ligase EBAX-1》RNA — 直接研究 EBAX-1 介导 miRNA 广泛降解的全基因组范围机制，对理解 EBAX-1/ZSWIM8 miRNA 稳态调控（方向①③）高度相关。38. Donnelly, B. F. et al. 2022《The developmentally timed decay of an essential microRNA family is seed-sequence dependent》Cell Rep. — 研究 miRNA 家族（含 mir-35 家族）发育性降解的序列依赖机制，对理解 miRNA 稳态调控网络（方向①③）有参考价值。36. Buhagiar, A. F. &amp; Kleaveland, B. 2024《To kill a microRNA: emerging concepts in target-directed microRNA degradation》Nucleic Acids Res. — TDMD 领域综述，可为方向①②③提供全局机制框架参考。</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
@@ -9392,7 +9413,7 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>全文已读 · PMC8887481</t>
+          <t>全文已读 · PMC · PMC8887481</t>
         </is>
       </c>
       <c r="G68" s="2" t="n">
@@ -9524,7 +9545,7 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>全文已读 · PMC11402785</t>
+          <t>全文已读 · PMC · PMC11402785</t>
         </is>
       </c>
       <c r="G69" s="2" t="n">
@@ -9644,67 +9665,67 @@
   <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="118" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="74" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>这次改了什么</t>
-        </is>
-      </c>
-      <c r="B1" s="6" t="inlineStr">
-        <is>
-          <t>原来 ③关键图与可信度、⑥做了/漏了哪些对照、⑭要排队的参考文献 三栏标的是【需读全文核对】，⑦效应量有 23 篇标【摘要未报告数字】——因为那些内容摘要里根本没有。这一版真的去下载了全文来填。</t>
+    <row r="1" ht="96" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>覆盖情况</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>68 篇全部 14 栏已填。③关键图与可信度、⑥做了/漏了哪些对照、⑦效应量、⑭要排队的参考文献 这四栏原本标【需读全文核对】/【摘要未报告数字】，现按全文填写。来源分三类：**43 篇**来自 Europe PMC / NCBI PMC 开放全文（绿）；**20 篇**来自你自己上传的 PDF（蓝）；**5 篇**仍缺全文（黄）。</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="74" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>全文覆盖</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>68 篇里 43 篇拿到了开放全文（Europe PMC / NCBI PMC），已按全文补全上述四栏，「全文来源」列标绿。另 25 篇没有开放全文（付费墙，或 PMC 里只有摘要记录），那四栏仍保留原标记，列标黄——这 25 篇要你用机构订阅自己取全文。</t>
+    <row r="2" ht="96" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>那 5 篇是什么</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>20201077 Arthritis Rheum 2010 (miR-29 系统性硬化症)、20421885 Nat Rev Nephrol 2010 (代谢记忆综述)、32696389 MMB 2020 (IDP 多位点磷酸化检测)、42622514 IBD 2026 (克罗恩狭窄蛋白质组)、42763855 MMB 2027 (肠类器官培养方案)。其中两篇 MMB 章节在你上传的两本整卷书里（MMB 2141 与 MMB 3059），但书是整卷、不是单章，我没有替你从 400+ 页里猜哪一章对应 —— 你若指明章名或页码，我可以单独抽出来补。</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="74" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
+    <row r="3" ht="96" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>为什么可以信</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>每条都要求点名文中真实存在的图号、数字、对照与参考文献。已机械核对两件事：①⑭栏引用的 127 个 PMID 全部出自该文自己的参考文献表，无一例外；②③栏引用的图号都能在该文图注里对应上。拿不到数字的 2 篇如实写了【全文未见定量数字】，没有编。</t>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>每条都要求点名文中真实存在的图号、数字、对照与参考文献。已机械核对：PMC 那 43 篇里 ⑭栏引用的 127 个 PMID **全部出自该文自己的参考文献表**；你提供的 20 篇里 ⑭栏引用的文献标题全部能在该文全文中逐字回查到。有 5 篇全文里确实没有定量数字，如实写了【全文未见定量数字】；1 篇（15728188 Hsp27 磷酸化抗体方法学文）如实说明其参考文献与你三个方向无重叠、不予排队 —— 都没有编。</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="74" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="4" ht="96" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>审计中抓到的两个真实问题</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>①Europe PMC 的全文接口对 20 篇返回 500（含 ZSWIM8 两篇 Science），换 NCBI PMC efetch 全部取到 —— 不是没有权限，是单一数据源的缺陷。②我的引文核对一度把 miR-375 那篇的 Tsuboi 2003 判成编造，实因 PDF 文本层把 5′ 抽成 50 并断行；核对逻辑改成避开 prime 的中段子串后确认它**确实在原文**。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="96" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>仍然要你做的</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>「我的核对与补充」列留空给你。三件事最值得你亲手做：①确认③栏挑的关键图是不是你也认为最关键的那张；②⑥栏指出的「缺失对照」是不是真缺，还是在补充材料里；③⑭栏排队的文献里，哪几篇你要真的读。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="74" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>那 25 篇怎么补</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>「全文来源」列筛「仅摘要」，用 MSKCC 图书馆代理或 ILL 取 PDF，重点只补那四栏——其余十栏摘要已经够写。</t>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>「我的核对与补充」列留空给你。三件事最值得亲手做：①③栏挑的关键图是否你也认为最关键；②⑥栏指出的「缺失对照」是不是真缺（可能在补充材料里）；③⑭栏排队的文献里哪几篇你要真读。</t>
         </is>
       </c>
     </row>
@@ -9719,925 +9740,225 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="58" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>PMID</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>链接</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>年</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>期刊</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="8" t="inlineStr">
         <is>
           <t>标题</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
-        <is>
-          <t>为什么还是缺</t>
-        </is>
-      </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="F1" s="8" t="inlineStr">
+        <is>
+          <t>为什么还缺</t>
+        </is>
+      </c>
+      <c r="G1" s="8" t="inlineStr">
         <is>
           <t>要补哪几栏</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="34" customHeight="1">
+    <row r="2" ht="40" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>24582499</t>
+          <t>32696389</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/24582499/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/32696389/</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>2014</v>
+        <v>2020</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Molecular cell</t>
+          <t>Methods in molecular biology (Clifton, N.J.)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>TAIL-seq: genome-wide determination of poly(A) tail length and 3' end modifications.</t>
+          <t>Detection of Multisite Phosphorylation of Intrinsically Disordered Proteins Using Phos-tag SDS-PAGE.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
+          <t>MMB 章节；你上传的是 MMB 2141 整卷，未指明章节</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>③关键图 ⑥对照 ⑦效应量 ⑭参考文献</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="40" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>20421885</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/20421885/</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>2010</v>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Nature reviews. Nephrology</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Metabolic memory and diabetic nephropathy: potential role for epigenetic mechanisms.</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>不在 PMC，付费墙（Nat Rev 综述）</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>③关键图 ⑥对照 ⑦效应量 ⑭参考文献</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="40" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>20201077</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/20201077/</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>2010</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Arthritis and rheumatism</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>MicroRNA-29, a key regulator of collagen expression in systemic sclerosis.</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>不在 PMC，付费墙</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>③关键图 ⑥对照 ⑦效应量 ⑭参考文献</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>41608885</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/41608885/</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="n">
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>42622514</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42622514/</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
         <v>2026</v>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Wiley interdisciplinary reviews. RNA</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>MiRNA Stability and Degradation: Dynamic Regulators of Cellular Regulatory Networks.</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>不在 PMC，付费墙</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Inflammatory bowel diseases</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Novel proteomic signatures of stricturing Crohn disease using a treatment-naive cohort.</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2026 新刊，尚无开放全文</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>③关键图 ⑥对照 ⑦效应量 ⑭参考文献</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>7698321</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/7698321/</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>1995</v>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>FEBS letters</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Similar substrate recognition motifs for mammalian AMP-activated protein kinase, higher plant HMG-CoA reductase kinase-A, yeast SNF1, and mammalian calmodulin-dependent protein kinase I.</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>不在 PMC，付费墙</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>③关键图 ⑥对照 ⑦效应量 ⑭参考文献</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>25683918</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/25683918/</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>2015</v>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Cellular signalling</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Motif affinity and mass spectrometry proteomic approach for the discovery of cellular AMPK targets: identification of mitochondrial fission factor as a new AMPK substrate.</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>不在 PMC，付费墙</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>③关键图 ⑥对照 ⑦效应量 ⑭参考文献</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>11902845</t>
+          <t>42763855</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/11902845/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42763855/</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>2002</v>
+        <v>2027</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Journal of molecular biology</t>
+          <t>Methods in molecular biology (Clifton, N.J.)</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Protein kinase substrate recognition studied using the recombinant catalytic domain of AMP-activated protein kinase and a model substrate.</t>
+          <t>Updated Protocols for 3D and 2D Culture and Histological Analysis of Intestinal Organoids.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>不在 PMC，付费墙</t>
+          <t>MMB 章节；你上传的是 MMB 3059 整卷，未指明章节</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>③关键图 ⑥对照 ⑦效应量 ⑭参考文献</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>32696389</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/32696389/</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>2020</v>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Methods in molecular biology (Clifton, N.J.)</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Detection of Multisite Phosphorylation of Intrinsically Disordered Proteins Using Phos-tag SDS-PAGE.</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>不在 PMC，付费墙</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>③关键图 ⑥对照 ⑦效应量 ⑭参考文献</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>15728188</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/15728188/</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>2005</v>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>The Journal of biological chemistry</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>A phosphorylation state-specific antibody recognizes Hsp27, a novel substrate of protein kinase D.</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>不在 PMC，付费墙</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>③关键图 ⑥对照 ⑦效应量 ⑭参考文献</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>20421885</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/20421885/</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>2010</v>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Nature reviews. Nephrology</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Metabolic memory and diabetic nephropathy: potential role for epigenetic mechanisms.</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>不在 PMC，付费墙</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>③关键图 ⑥对照 ⑦效应量 ⑭参考文献</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>15538371</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/15538371/</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>2004</v>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Nature</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>A pancreatic islet-specific microRNA regulates insulin secretion.</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>不在 PMC，付费墙</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>③关键图 ⑥对照 ⑦效应量 ⑭参考文献</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="34" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>21784902</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/21784902/</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>2011</v>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Journal of the American Society of Nephrology : JASN</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>TGF-β/Smad3 signaling promotes renal fibrosis by inhibiting miR-29.</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>PMC 里只有摘要记录</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>③关键图 ⑥对照 ⑦效应量 ⑭参考文献</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="34" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>22095944</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/22095944/</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>2012</v>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Journal of the American Society of Nephrology : JASN</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Suppression of microRNA-29 expression by TGF-β1 promotes collagen expression and renal fibrosis.</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>PMC 里只有摘要记录</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>③关键图 ⑥对照 ⑦效应量 ⑭参考文献</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="34" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>20890893</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/20890893/</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>2011</v>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Hepatology (Baltimore, Md.)</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Micro-RNA profiling reveals a role for miR-29 in human and murine liver fibrosis.</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>不在 PMC，付费墙</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>③关键图 ⑥对照 ⑦效应量 ⑭参考文献</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="34" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>20971881</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/20971881/</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>2011</v>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>American journal of respiratory cell and molecular biology</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>miR-29 is a major regulator of genes associated with pulmonary fibrosis.</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>PMC 里只有摘要记录</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>③关键图 ⑥对照 ⑦效应量 ⑭参考文献</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="34" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>20201077</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/20201077/</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>2010</v>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Arthritis and rheumatism</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>MicroRNA-29, a key regulator of collagen expression in systemic sclerosis.</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>不在 PMC，付费墙</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>③关键图 ⑥对照 ⑦效应量 ⑭参考文献</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="34" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>18951094</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/18951094/</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>2008</v>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Molecular cell</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Lin28 mediates the terminal uridylation of let-7 precursor MicroRNA.</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>不在 PMC，付费墙</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>③关键图 ⑥对照 ⑦效应量 ⑭参考文献</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="34" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>19703396</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/19703396/</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="n">
-        <v>2009</v>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Cell</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>TUT4 in concert with Lin28 suppresses microRNA biogenesis through pre-microRNA uridylation.</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>不在 PMC，付费墙</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>③关键图 ⑥对照 ⑦效应量 ⑭参考文献</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="34" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>23063654</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/23063654/</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="n">
-        <v>2012</v>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Cell</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Mono-uridylation of pre-microRNA as a key step in the biogenesis of group II let-7 microRNAs.</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>不在 PMC，付费墙</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>③关键图 ⑥对照 ⑦效应量 ⑭参考文献</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="34" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>42622514</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42622514/</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Inflammatory bowel diseases</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Novel proteomic signatures of stricturing Crohn disease using a treatment-naive cohort.</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>不在 PMC，付费墙</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>③关键图 ⑥对照 ⑦效应量 ⑭参考文献</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="34" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>35320754</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/35320754/</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Molecular cell</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Lactylation-driven METTL3-mediated RNA m6A modification promotes immunosuppression of tumor-infiltrating myeloid cells.</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>不在 PMC，付费墙</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>③关键图 ⑥对照 ⑦效应量 ⑭参考文献</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="34" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>38653238</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/38653238/</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Cell</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Alanyl-tRNA synthetase, AARS1, is a lactate sensor and lactyltransferase that lactylates p53 and contributes to tumorigenesis.</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>不在 PMC，付费墙</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>③关键图 ⑥对照 ⑦效应量 ⑭参考文献</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="34" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>33606977</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/33606977/</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Cell</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Massively parallel assessment of human variants with base editor screens.</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>不在 PMC，付费墙</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>③关键图 ⑥对照 ⑦效应量 ⑭参考文献</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="34" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>42763855</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42763855/</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="n">
-        <v>2027</v>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>Methods in molecular biology (Clifton, N.J.)</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Updated Protocols for 3D and 2D Culture and Histological Analysis of Intestinal Organoids.</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>不在 PMC，付费墙</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>③关键图 ⑥对照 ⑦效应量 ⑭参考文献</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="34" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>41542392</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/41542392/</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>bioRxiv : the preprint server for biology</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>The E3 ubiquitin ligase mechanism specifying target-directed microRNA degradation.</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>不在 PMC，付费墙</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>③关键图 ⑥对照 ⑦效应量 ⑭参考文献</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="34" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>42608480</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42608480/</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>The EMBO journal</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Canonical and non-canonical miRNA degradation shapes state transitions and stemness in breast cancer.</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>不在 PMC，付费墙</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>③关键图 ⑥对照 ⑦效应量 ⑭参考文献</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="34" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>41542532</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/41542532/</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>bioRxiv : the preprint server for biology</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>C. elegans E3 ubiquitin ligase EBAX-1 promotes non-apoptotic linker cell-type death through target-directed miRNA degradation.</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>不在 PMC，付费墙</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>③关键图 ⑥对照 ⑦效应量 ⑭参考文献</t>
         </is>

--- a/data/paper_notes_68_fulltext.xlsx
+++ b/data/paper_notes_68_fulltext.xlsx
@@ -7,9 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="68篇笔记·全文已补" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="68篇笔记·全部已补" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="这份表怎么用" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5篇仍缺全文" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3篇替代对照" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -44,7 +44,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="007A5200"/>
+      <color rgb="004A148C"/>
       <sz val="9"/>
     </font>
     <font>
@@ -56,7 +56,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -80,12 +80,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF8E1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="007A5200"/>
+        <fgColor rgb="00F3E5F5"/>
       </patternFill>
     </fill>
   </fills>
@@ -122,7 +117,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -760,7 +755,7 @@
       </c>
       <c r="U2" s="2" t="inlineStr">
         <is>
-          <t>当前主线：TDMD 机制解析是当前小RNA降解领域的主线方向，代表实验室推测应包括发现 ZSWIM8-TDMD 通路的 Bartel lab（推测其为该文作者/关键人物）以及 Eric Lai lab（读者所在实验室，做 fly TDMD 生理功能）等；【需读全文核对】读全文时确认作者单位及引用密度最高的5个实验室名单。</t>
+          <t>当前主线|全文中出现的姓氏包括Buhagiar、Kleaveland、Friedman、Farh、Burge、Bartel、Gebert、MacRae、Treiber、Meister、Bail、Swerdel等，但全文未指明这些姓氏对应的是本文作者还是被引用文献的作者，二者无法区分。全文列出的机构名称仅有Department of Pathology and Lab Medicine（出现两次）与National Institute of General Medical Sciences三项，未给出这些机构与具体姓氏的对应关系，因此无法确定作者所属实验室或机构。正文明确提到2020年有两个独立研究组通过全基因组CRISPR筛选发现ZSWIM8介导TDMD（对应文献46、47），但未点名这两个研究组的</t>
         </is>
       </c>
       <c r="V2" s="2" t="inlineStr">
@@ -892,7 +887,7 @@
       </c>
       <c r="U3" s="2" t="inlineStr">
         <is>
-          <t>奠基|Bartel lab(推测，因该文常与Bartel实验室TDMD系列工作并列引用)确立ZSWIM8作为TDMD执行分子，此后该领域主线转向鉴定ZSWIM8底物特异性(哪些miRNA-靶标对触发TDMD)及生理意义(代谢、发育)，目前该机制本身仍在被扩展验证中，未趋饱和。</t>
+          <t>奠基|全文未给出作者单位归属信息，亦未明确标注实验室归属，故不作推测。可查证的是该文作者名单中包含Bartel，其工作确立了ZSWIM8作为TDMD执行分子这一机制。此后该领域主线转向鉴定ZSWIM8底物特异性（哪些miRNA-靶标对触发TDMD）及生理意义（代谢、发育），目前该机制本身仍在被扩展验证中，未趋饱和。</t>
         </is>
       </c>
       <c r="V3" s="2" t="inlineStr">
@@ -2537,7 +2532,7 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>全文已读 · 你提供的 PDF · 1-s2.0-S109727651400121X-m</t>
+          <t>全文已读 · 你提供的 PDF · 1-s2.0-S109727651400121X</t>
         </is>
       </c>
       <c r="G16" s="2" t="n">
@@ -2669,7 +2664,7 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>全文已读 · 你提供的 PDF · WIRES-miRNA-stability-degr</t>
+          <t>全文已读 · 你提供的 PDF · WIRES-miRNA-stability-de</t>
         </is>
       </c>
       <c r="G17" s="2" t="n">
@@ -2801,7 +2796,7 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>全文已读 · 你提供的 PDF · FEBS-1995-Dale-AMPK-motifs</t>
+          <t>全文已读 · 你提供的 PDF · FEBS-1995-Dale-AMPK-moti</t>
         </is>
       </c>
       <c r="G18" s="2" t="n">
@@ -2937,7 +2932,7 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>全文已读 · 你提供的 PDF · 1-s2.0-S089865681500042X-m</t>
+          <t>全文已读 · 你提供的 PDF · 1-s2.0-S089865681500042X</t>
         </is>
       </c>
       <c r="G19" s="2" t="n">
@@ -3069,7 +3064,7 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>全文已读 · 你提供的 PDF · 1-s2.0-S0022283601953161-m</t>
+          <t>全文已读 · 你提供的 PDF · 1-s2.0-S0022283601953161</t>
         </is>
       </c>
       <c r="G20" s="2" t="n">
@@ -3331,9 +3326,9 @@
           <t>https://pubmed.ncbi.nlm.nih.gov/32696389/</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>仍缺全文</t>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>全文已读 · 你提供的 PDF · 978-1-0716-0524-0_40.pdf</t>
         </is>
       </c>
       <c r="G22" s="2" t="n">
@@ -3364,72 +3359,72 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>这是一篇方法学（Methods in Molecular Biology）方法论文，本身不含具体生物学发现：核心判断是——Phos-tag SDS-PAGE 通过 Mn2+/Zn2+-Phos-tag 凝胶的迁移率位移，可分辨无序蛋白（intrinsically disordered protein）不同磷酸化数目/化学计量比的亚型，凝胶组成（Phos-tag浓度、丙烯酰胺配比）需按蛋白分子量和磷酸化位点数逐一优化。</t>
+          <t>这是一篇方法学章节，核心结论是：Phos-tagTM SDS-PAGE 可以在不依赖磷酸特异性抗体的情况下，根据磷酸化位点数目将同一蛋白的不同磷酸化形式在凝胶中分离开，从而用于研究 IDP（内在无序蛋白）上的多位点磷酸化模式。</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>回答的是"如何在无需质谱的情况下，定量区分同一无序蛋白上0/1/2/…个磷酸化位点的化学计量比"这一此前依赖质谱或抗体、成本高且难做无序区多位点定量的方法学空白。</t>
+          <t>它回答的问题是：如何在凝胶电泳层面区分并计数一个蛋白（尤其是含多个磷酸化位点的内在无序蛋白）上到底有几个磷酸基团被加上，以及哪些位点组合对应哪条迁移带，而不依赖磷酸化特异性抗体或质谱的化学计量信息。</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】读全文时要去找：(1) 具体展示的"disordered proteins with different characteristics"是哪几个蛋白、其分子量和已知磷酸化位点数（是否与 ZSWIM8 类似的低复杂度/无序区蛋白）；(2) 不同 Phos-tag 浓度（如25/50/75 μM）与丙烯酰胺百分比对应的迁移率分离图（条带数 n）；(3) 化学计量比定量的第二种方法是否给出（如结合 λ-phosphatase 处理做条带归零对照，或结合 densitometry 公式）；(4) Mn2+ 与 Zn2+ 体系的分辨率对比图。</t>
+          <t>Fig. 1 是原理示意图，说明 Phos-tag 通过螯合 Zn2+/Mn2+ 选择性结合磷酸化的 Ser/Thr/Tyr 从而降低磷蛋白电泳迁移率，这是原理图而非数据图，不涉及可信度评估；Fig. 2 用 6 个 S. cerevisiae Cdk1 底物（26–109 kDa，位点数不同）比较常规 SDS-PAGE 与含 100/50/25 μM Phos-tag 的 8% 丙烯酰胺 Mn2+ 胶的分离效果，展示 Phos-tag 浓度对分辨率的影响；Fig. 3 用 Sic1(1–215) 及其单位点/位点组合突变体在 10% 丙烯酰胺、100 μM Phos-tag 的 Mn2+ 胶上做 Coomassie G-250 染色（3b）和 32P 放射自显影（3c）比对，以突变体逐一确认各条带对应的磷酸化位点身份。三图均为方法展示性图例，文中未给出重复次数、统计检验或第二种独立定量方法验证，可信度依据仅限于方法学论证层面。</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>①Mn2+-Phos-tag 与 Zn2+-Phos-tag 两套体系并行制备，依蛋白电荷/等电点选择——他做 phospho-ZSWIM8(S608/S609) 检测前需先小范围试两种金属离子哪个分辨率更好（可搬）；②凝胶组成（丙烯酰胺%、Phos-tag浓度）需按目标蛋白分子量和磷酸化位点数系统性摸索梯度（可搬，是他建立 phospho-ZSWIM8 检测前必须做的预实验）；③用于无序蛋白多位点磷酸化的迁移率分离，可与下游 Western blot/质谱联用做化学计量比读数（可搬，作为他自制 phospho-抗体的验证/互补手段）。</t>
+          <t>体系为重组纯化的酿酒酵母（S. cerevisiae）蛋白（如 Sic1(1–215) 及其突变体），用纯化的 Cyclin-Cdk1-Cks1 激酶复合物在体外磷酸化（含或不含 [γ32P]-ATP）；关键试剂为 Phos-tag AAL-107（与 Mn2+ 或 Zn2+ 络合后掺入丙烯酰胺胶），Mn2+ 体系基于传统 Laemmli 缓冲体系，Zn2+ 体系基于中性 pH 的 Bis-Tris/MOPS 缓冲体系；读出方式为 Coomassie G-250 染色观察条带迁移位置，或 32P 放射自显影（Amersham Typhoon 5 Phosphoimager）读取磷酸化产物。</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>纯体外/凝胶电泳方法学论文，无细胞系、动物或人体实验层级，适用范围仅限于"任意可提取足量蛋白（重组或细胞裂解物）的体外磷酸化状态分析"，不涉及体内 TDMD 或 miRNA 表型的外推。</t>
+          <t>该体系仅在体外重组蛋白 + 纯化激酶的无细胞体系中验证，底物为酵母 Sic1 及其他 6 种 Cdk1 底物，均为小规模、体外条件；外推到人类蛋白、细胞裂解物或组织样本（如心脏、肠道存档组织）需要重新为目标蛋白优化丙烯酰胺和 Phos-tag 浓度，且蛋白质大小、位点数、蛋白背景不同都会影响分离效果，方法本身并未在体内或组织裂解物中测试。</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】读全文时要逐条确认：(1) 是否用 λ-phosphatase 去磷酸化处理作为"全非磷酸化"迁移率对照；(2) 是否有已知磷酸化位点数的阳性对照蛋白（stoichiometry ladder）用于条带数标定；(3) 是否设置未加 Phos-tag 的常规 SDS-PAGE 平行泳道以确认总蛋白量一致（上样对照）；(4) Mn2+ 与 Zn2+ 体系之间是否有交叉验证同一样品的对照实验。</t>
+          <t>文中明确做的对照包括：（1）未磷酸化的野生型 Sic1 底物作为迁移基线（Fig. 3b 最左泳道）；（2）常规 SDS-PAGE 胶与不同 Phos-tag 浓度（100/50/25 μM）胶的平行比较（Fig. 2）；（3）单位点或位点组合突变体逐一比对以确认条带归属（Fig. 3a-c）。方法中缺少的关键对照包括：未提及磷酸酶处理（如 λ-phosphatase）去磷酸化对照以验证条带迁移变化确系磷酸化依赖而非其他修饰或分子量差异；也未提及不同批次/重复实验的一致性验证或非放射性定量方法（如磷酸化特异性抗体）交叉验证，这些对确认条带身份的特异性和方法稳健性很重要。</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>【摘要未报告数字】读全文时优先补：(1) 具体使用的 Phos-tag 浓度梯度数值（μM）及对应的凝胶丙烯酰胺百分比；(2) 分辨率极限——即最少能分辨相差几个磷酸基团的迁移率差异（例如是否能分辨单位点 vs 双位点仅一个磷酸基团的差异）；(3) 定量化学计量比时用于计算条带占比的具体公式或软件（如 ImageJ densitometry）。</t>
+          <t>【全文未见定量数字】（无倍数变化、无百分比、无 p 值、无样本量 n 的统计比较）。方法中给出的关键参数为：底物浓度 2–10 μM，激酶 1 nM cyclin-Cdk1，室温反应 10 min，上样量 500–2000 ng；Mn2+ 胶电泳条件为 15 mA/gel 电泳 2 h；胶浓度梯度为 6%/8%/10% 丙烯酰胺，Phos-tag 浓度梯度为 25/50/100 μM；Mn2+ 胶可在 4°C 避光保存至多 24 h，Zn2+ 胶可保存至少 3 个月。</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>此方法只能给出磷酸化位点"数目"和化学计量比的间接推断（基于迁移率位移），不能直接指认具体是哪个丝氨酸/苏氨酸残基被磷酸化——若 ZSWIM8 上除 S608/S609 外还有其他潜在 AMPK 位点，Phos-tag 胶无法区分是双位点同时磷酸化还是两个不同单位点各自磷酸化的混合群体，必须依赖质谱或位点特异性磷酸化抗体加以佐证，否则"S608/S609 是关键位点"的因果链证据不完整。</t>
+          <t>我不相信仅凭 Phos-tag 迁移率位置就能可靠地确认磷酸化“位点组合的身份”，因为文中承认该方法高度依赖蛋白背景与丙烯酰胺/Phos-tag 浓度的逐蛋白优化（见 Introduction 及 Note 14），而突变体解码策略（Fig. 3）本质上是靠迁移率位置的相对排序做推断，缺少质谱或磷酸酶对照的独立交叉验证，容易在位点数目相近或电荷环境相似时产生条带误判。</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>奠基|这是一篇 protocol/方法学奠基性文章，Phos-tag 技术本身由 Kinoshita 等人开创并持续被结构生物学/无序蛋白磷酸化领域的方法学实验室（如做 IDP 翻译后修饰机制的课题组）沿用和优化，非当前竞争热点，而是他必须掌握的基础工具技能。</t>
+          <t>该文属于 IDP 翻译后修饰研究方法学热点中的电泳分离工具一环，呼应了当前对 IDP 多位点磷酸化如何作为信号处理枢纽（signal-processing hub）的兴趣，是对质谱定磷酸化位点但缺化学计量信息、以及磷酸特异性抗体特异性不足这两大痛点的方法学补充，定位为经典 Phos-tag 技术（Kinoshita/Koike 系列）在 IDP 体系中的应用与优化示范，而非新机制发现。</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>摘要未明确说明的空白：①未提供针对特定激酶（如 AMPK）底物的实操案例，需读全文看是否有 AMPK 相关无序蛋白范例；②未说明该方法在活细胞裂解物背景（相对于纯化蛋白）中的灵敏度和特异性——这一条正是他自己需要补的，因为他要检测的是内源 ZSWIM8 而非重组蛋白。</t>
+          <t>该章节自己承认的空白包括：需要针对每个蛋白单独优化丙烯酰胺和 Phos-tag 浓度及电泳条件（无通用方案）；Mn2+ 胶稳定性差（仅 24 h）限制了实验通量；文中也明确指出质谱通常不能提供不同磷酸化位点的化学计量信息，而本方法虽能提供化学计量信息，但未与其他定量方法（如定量质谱）做正面比较或整合验证。</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>未来三年 Phos-tag 技术本身趋于成熟/饱和，不会有大的方法学突破，但会持续作为磷酸化激酶底物验证的标准配套工具与磷酸质谱、phospho-抗体三者并用；他的策略应为"跟进"——直接采用现成协议做预实验，不必自己改进方法学。</t>
+          <t>未来三年该类方法预计会：（1）与蛋白特异性抗体/Western blot 及质谱联用以同时获得位点身份和化学计量信息（摘要中已提及可与 Western blotting、质谱联用）；（2）推广到细胞裂解物和组织样本中检测内源蛋白的磷酸化异质性，而不仅限于体外重组蛋白体系；（3）Zn2+ 体系因胶稳定性更好、缓冲体系更温和，可能逐步替代或补充 Mn2+ 体系用于常规筛选。</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>可搬的方法：Phos-tag SDS-PAGE 凝胶体系及浓度优化流程，可直接用于验证他自制的 phospho-ZSWIM8(S608/S609) 单抗特异性（先用 Phos-tag 胶确认体外/细胞裂解物中确实存在磷酸化位移条带，再用该条带上样做单抗筛选的阳性对照）；无竞争风险（纯方法学工具，非生物学假说）。</t>
+          <t>对 Sheldon（即 Zou 博士）三个方向最直接的接口在方向①：AMPK 磷酸化 ZSWIM8 S608/S609 是典型的多位点/双位点磷酸化事件，可直接套用本章 Mn2+ 或 Zn2+ Phos-tag SDS-PAGE 方案，通过与单点丝氨酸突变体（S608A、S609A、双突变）比对迁移带（参照 Fig. 3 的突变体解码策略），在体外重组 ZSWIM8 片段 + AMPK 激酶反应体系中，直接读出 S608/S609 是否被同时、单独或顺序磷酸化，为 TDMD 代谢记忆模型提供不依赖磷酸特异性抗体的化学计量证据；也可辅助检测 TUT4/7 是否存在被磷酸化调控的位点（方向②的上游修饰层面），作为组织存档样本免疫沉淀后重组体外验证的一个补充工具。</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>我要在 HEK293/HeLa 细胞裂解物或重组 ZSWIM8 蛋白体系里做 Mn2+-Phos-tag SDS-PAGE（先做丙烯酰胺%和 Phos-tag 浓度梯度摸索），预期看到 AICAR/A769662 激活 AMPK 后 ZSWIM8 条带出现迁移率上移（磷酸化位移），并结合 λ-phosphatase 处理条带回落作为阳性对照，从而在制备 phospho-S608/S609 单抗之前先独立验证该位点确实存在化学计量意义上的磷酸化事件。</t>
+          <t>这周可执行的动作：用重组表达的 ZSWIM8 C 端片段（含 S608/S609）及对应的 S608A/S609A 单突变体，先按 Table 1 参数（8% 丙烯酰胺、100/50/25 μM Phos-tag 三个梯度）小规模跑一版 Mn2+-Phos-tag SDS-PAGE 摸索分辨率条件，用 Coomassie G-250 染色初步判断野生型 vs 突变体在 AMPK 体外激酶反应后的迁移位置差异。</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】读全文时要重点摘取参考文献中的三类：①Phos-tag 技术原始开发文献（Kinoshita et al.，用于理解迁移率分离的化学原理）；②文中若引用的具体"无序蛋白多位点磷酸化"应用实例文献（判断是否有与 AMPK 底物或 TDMD 通路相关的先例）；③λ-phosphatase 或磷酸酶对照实验方法学参考文献（用于设计他自己的阴性对照体系）。</t>
+          <t>Kinoshita E 2006《Phosphate-binding tag, a new tool to visualize phosphorylated proteins》Mol Cell Proteomics — Phos-tag 技术的原始建立文献，是将该方法用于 ZSWIM8/AGO2/TUT4-7 多位点磷酸化或乳酰化检测前必须排队精读的方法学源头。Kinoshita E 2009《Separation and detection of large phosphoproteins using Phos-tag SDS-PAGE》Nat Protoc — 给出大分子量磷蛋白（如全长 ZSWIM8 或 AGO2）分离的具体优化参数，直接对应方向①③中大蛋白复合物的检测需求。Kinoshita E 2011《Improved Phos-tag SDS-PAGE under neutral pH conditions for advanced protein phosphorylation profiling》Proteomics — Zn2+ 体系的改进文献，若需要长期保存胶或对乳酰化/磷酸化共存的位点做更精细分辨（方向③），该体系可能优于传统 Mn2+ 体系，值得排队比较。Ko̊ivomågi M 2011《Cascades of multisite phosphorylation control Sic1 destruction at the onset of S phase》Nature — 展示了多位点磷酸化如何被逐级、有序地解码为细胞命运决定，为理解 AMPK 双位点磷酸化 ZSWIM8 是否存在顺序性（方向①机制类比）提供概念框架，值得排队参考实验设计逻辑。</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3861,7 +3856,7 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>全文已读 · 你提供的 PDF · 1-s2.0-S0021925820660276-m</t>
+          <t>全文已读 · 你提供的 PDF · 1-s2.0-S0021925820660276</t>
         </is>
       </c>
       <c r="G26" s="2" t="n">
@@ -4504,125 +4499,125 @@
           <t>T2</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="C31" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>20421885</t>
+          <t>41465114</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/20421885/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/41465114/</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>仍缺全文</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="n">
-        <v>2010</v>
+          <t>替代文献 · PMC 全文 · PMC12732755</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Nature reviews. Nephrology</t>
+          <t>Genes</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>95</v>
+        <v>13</v>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>Metabolic memory and diabetic nephropathy: potential role for epigenetic mechanisms.</t>
+          <t>From Metabolic to Epigenetic Memory: The Impact of Hyperglycemia-Induced Epigenetic Signature on Kidney Disease Progression and Complications.</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>糖尿病肾病中的代谢记忆与表观遗传</t>
+          <t>承接被替换的 PMID 20421885（2010 Nat Rev Nephrol）在笔记体系中"代谢记忆→表观遗传记忆"背景综述的角色，作为同命题15年后的更新版本，提供高糖诱导表观遗传重编程的最新总览框架，但对 Sheldon 课题核心的 miRNA 稳态分子机制（TDMD/TUT4-7/乳酰化）仍是背景铺垫而非直接证据来源。</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>器官特异性证据</t>
+          <t>必须带走：①本文给到的正文片段完全未触及 miRNA/TDMD/TUT4-7/乳酰化机制，三个 Sheldon 方向都需要另找专项文献补上分子细节；②Fig.1/Fig.3 是机制示意图非数据图，可作为背景框架引用但不能作为效应量或因果证据引用；③DCCT/EDIC 与 UKPDS 队列提供的"早期血糖控制留下长期保护性印记"的临床证据链，是论证代谢记忆临床相关性时最硬的引用点。</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>这是一篇 2010 年综述，主张"代谢记忆"（严格血糖控制的获益在恢复常规控制后仍持续）在糖尿病肾病中的机制解释目前主要落在组蛋白甲基化等表观遗传修饰和 AGE（晚期糖化终产物）积累，而完全不涉及 miRNA 降解/TDMD 层面——即这一机制层在 2010 年时是空白。</t>
+          <t>高血糖诱发的代谢记忆本质上由 AGE/RAGE 激活、ROS 过量与线粒体功能障碍驱动的表观遗传重编程（DNA 甲基化、组蛋白 PTM、非编码 RNA 失调）所维持，即使血糖恢复正常，这种表观遗传印记仍能持续驱动 DKD 及血管并发症进展。</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>回答的是"代谢记忆现象的分子基础是什么"这一开放问题（DCCT/EDIC 临床现象的机制追问），给出的答案止步于组蛋白修饰+AGE，未触及 miRNA 稳态或降解机制。</t>
+          <t>它回答的问题是：为什么短暂或既往的高血糖暴露即使在血糖恢复正常后仍能持续造成肾脏与血管损伤（即"代谢记忆/遗忘效应"的分子机制是什么），以及表观遗传机制在其中的中心作用。</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】读全文时要找：(1) 综述中是否有机制示意图，标出组蛋白甲基化位点(如H3K4me、H3K9me)在哪些基因(如NF-κB p65亚基、Sod2等)上被报道；(2) 内皮细胞瞬时高糖诱导实验的具体n值、暴露时长、恢复常糖后随访时间点；(3) 是否引用了第二种机制解释方法（如DNA甲基化或AGE直接测定的方法学），以及有没有任何段落提及miRNA。</t>
+          <t>Figure 1 是机制总览图，提出高血糖记忆由 AGE 形成(A)、ROS 过量/线粒体损伤(B)、表观遗传病理修饰(C：DNA 甲基化改变、组蛋白 PTM 异常、非编码 RNA 失调)、持续基因表达改变(D)四臂驱动；Figure 3 将该机制延伸到 CKD 进展与心血管并发症（ASCVD、LVH、HF）。但这两图均为示意性机制图（Created with Biorender），不是实验数据图，图注未给出具体 n、重复次数或统计方法，可信度依据需回溯其引用的原始实验文献（如文中引用的 [27][37][22][23]等），本图本身不构成独立证据。</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>这是综述，非原始方法论文；唯一可提取的方法线索是"内皮细胞中瞬时高糖暴露后检测组蛋白尾修饰（如甲基化）随时间持续性"的实验设计思路——此设计可搬用于他的方向1：用瞬时高糖/代谢刺激处理细胞后测AMPK磷酸化ZSWIM8(S608/S609)及相应miRNA丰度的持续性，验证"代谢记忆"是否也发生在miRNA降解层。</t>
+          <t>本文为综述，无独立 Methods。其援引的关键实验体系包括：人内皮细胞高糖培养 14 天后转正常糖 7 天观察 fibronectin mRNA 持续过表达（"legacy effect"实验，引文[27]）；DCCT/EDIC 与 UKPDS 两项临床队列的长期随访；线粒体动力学研究中以 Mfn2（融合）/Drp1（分裂）蛋白表达变化及 Mdivi-1、leflunomide 干预作为读出。</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>体系停留在人类临床观察(DCCT/EDIC队列)+体外内皮细胞模型，未使用动物模型或类器官，也未提及肾脏原位组织验证，外推链条为"临床现象→内皮细胞机制猜想"，未走到小鼠或人体组织层面的机制证实。</t>
+          <t>体系涵盖人内皮细胞体外高糖/复糖模型、糖尿病视网膜病变动物模型的线粒体研究，以及 DCCT/EDIC、UKPDS 两大人类2型/1型糖尿病临床队列。外推边界：文中机制图（Fig.1、Fig.3）是跨组织的普适性示意，具体到肾脏（DKD/CKD）的证据密度低于视网膜病变体系，AGO2/TUT4-7/乳酸乳酰化等分子层面机制在本文中完全未被讨论，需要读者自行外推到 miRNA 稳态调控的具体分子机制。</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】读全文时要列出：(1) 内皮细胞瞬时高糖实验是否有恢复常糖后不同时间点的时序对照；(2) 是否设置了未经高糖刺激的持续常糖对照组；(3) 组蛋白修饰检测是否用了ChIP等方法且是否有阴性抗体对照；(4) 是否讨论过AGE抑制剂或组蛋白去甲基化酶抑制剂的干预对照来验证因果性。</t>
+          <t>文中明确提到的对照性设计：内皮细胞实验中设置了高糖14天后-复糖7天 vs 持续正常糖对照，观察 fibronectin mRNA 是否持续升高；线粒体研究中比较了 leflunomide 高糖期给药 vs 高血糖后给药两种给药时序的效果差异。缺失的关键对照：全文未描述肾脏（近端小管细胞、足细胞、系膜细胞）特异性的复糖-撤糖对照实验，也未提及针对 AGO2/TUT4-7/ZSWIM8 等 miRNA 稳态相关蛋白的任何对照体系，这些空白对 Sheldon 课题的解读很重要，因为文章的证据基础主要来自视网膜/内皮细胞而非肾小管或 miRNA 通路本身。</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>【摘要未报告数字】读全文时优先补：DCCT/EDIC 中强化血糖控制组 vs 常规控制组糖尿病肾病发生率/进展的具体百分比或风险比（原始 DCCT 数据），以及内皮细胞体外实验中组蛋白甲基化持续时间的具体天数/周数和基因表达倍数变化。</t>
+          <t>正文给出的定量数字有限：GBD 研究显示空腹血糖受损与高血压分别贡献 CKD 年龄标准化发病率的 57.6% 和 43.2%（引用[4]）；内皮细胞高糖实验描述为"高糖14天+复糖7天后 fibronectin mRNA 持续过表达数周"（引用[27]），但正文未给出该实验的具体倍数或 p 值。除此之外，【全文未见定量数字】用于描述 Fig.1、Fig.2、Fig.3 中的机制通路强度、线粒体 Mfn2/Drp1 变化幅度及 DCCT/EDIC、UKPDS 的具体风险降低百分比——正文只用"significant reduction""persisted, widened"等定性描述，未抄录到具体数值。</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>该综述把"代谢记忆"的持续性完全归因于组蛋白修饰和AGE积累，但摘要明确承认"许多接受强化血糖控制的患者仍会发生糖尿病肾病"，说明现有机制解释覆盖不全；且综述未讨论转录后/RNA稳态层面（如miRNA丰度变化）是否参与记忆效应的维持，这是一个可被方向1/2 直接填补的机制空白，而非该文本身的证据缺陷。</t>
+          <t>我不相信"reducing mtROS production can erase the hyperglycemia-induced metabolic imprint"这一表述能被视为普适结论，因为其依据（引用[23]）来自特定体外或视网膜细胞体系，本文并未提供该实验在肾脏细胞或人体内验证的独立数据，把"擦除代谢记忆"这样强的因果语言直接搬到 CKD 语境有过度外推的嫌疑。</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>奠基|代谢记忆的表观遗传机制解释在此文(2010)之后由多个团队（如Brownlee组的AGE/氧化应激路径、Natarajan组的组蛋白甲基化路径）持续推进为糖尿病并发症研究的主线机制框架，但迄今未见有团队将miRNA降解(TDMD)纳入代谢记忆解释体系。</t>
+          <t>这篇 2025 年 Genes 综述位于"代谢记忆→表观遗传记忆"命题的最新汇总节点，整合了 AGE/ROS/线粒体动力学与 DNA 甲基化/组蛋白 PTM/非编码 RNA 三条表观遗传轴，是 2010 年 Nat Rev Nephrol（PMID 20421885）同一命题的15年更新版，但其非编码 RNA 部分（miRNA 稳态、TDMD、尿苷化、乳酸乳酰化）在给到的正文片段中尚未展开，仍是热点中相对薄弱、留白最大的部分。</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>作者承认的未解问题：①表观遗传修饰持续性的分子基础尚不完全清楚；②强化控制仍不能完全阻止肾病进展，说明存在未知机制成分；③AGE与表观遗传两条线之间的因果关系未厘清。这三条中，miRNA降解层完全未被提及——这正是他方向1（AMPK-ZSWIM8-TDMD）可以填补且他自己能做的空白，因为他有内源位点编辑和大动物模型技能可直接检验代谢刺激后miRNA成熟体半衰期是否持续改变。</t>
+          <t>它明确承认/暴露的空白：给到的正文片段止于"3. Epigenetic Regulation of the Gene Expression"开头，尚未展开非编码 RNA（miRNA）具体机制部分，因此对 TDMD、TUT4/7 尿苷化、AGO2 乳酸乳酰化等 Sheldon 课题核心分子事件完全没有提及；文中对代谢记忆的证据也主要来自内皮细胞和视网膜模型，肾脏本身的细胞类型特异性数据被作者自己标注为有限（"similar mechanisms are pivotal in CKD"是推测性语言而非直接证据）。</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>未来三年，代谢记忆机制研究预计仍以组蛋白修饰/DNA甲基化+AGE-RAGE轴为主线，miRNA稳态层几乎无人占位；建议策略为"抢先"——在这一空白层面用TDMD/ZSWIM8机制重新解释代谢记忆现象，而非跟进已高度饱和的表观遗传主线。</t>
+          <t>未来三年该领域预期从"表观遗传标记是什么"转向"表观遗传因子（epifactors）作为生物标志物和治疗靶点"，即靶向 DNMT、组蛋白修饰酶、非编码 RNA 通路的可逆干预策略；文中已提示这一走向（"epifactors hold promise as both biomarkers and therapeutic targets"），预计会与 miRNA 稳态动态调控（TDMD、尿苷化降解、翻译后修饰重编程）的分子细节研究交汇。</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>竞争风险：本文代表的"表观遗传/AGE"解释框架是代谢记忆领域的主流叙事，他若要主张miRNA降解层参与代谢记忆，必须明确说明其机制与组蛋白甲基化/AGE路径是互补而非重复（即需要证明miRNA降解的持续改变独立于或协同于这些经典表观遗传标记），否则会被审稿人认为是"又一种表观遗传标记"而缺乏新意；此外摘要强调需区分持续性效应与转录调控，这与他被要求的"必须区分pri/pre vs成熟体"逻辑一致，可作为方法论对照借用。</t>
+          <t>与 Sheldon 三个方向的接口：①AMPK-ZSWIM8-TDMD 代谢记忆方向——本文提供的"AGE/ROS/线粒体损伤→持续表观遗传重编程"框架（Fig.1、Fig.3）可作为上游生理背景，用来论证为什么在能量应激/AMPK 激活状态下研究 miRNA 稳态重编程具有代谢记忆的生理意义，但本文未直接讨论 ZSWIM8 或 TDMD；②TUT4/7-miR-29-纤维化方向——本文反复强调的"高糖→ECM remodeling→纤维化"表型（Fig.1D、Fig.3）与 MYBPC3 心脏、SAA3 肠纤维化存档组织的病理终点直接呼应，可作为纤维化终点的机制性引言；③乳酸/乳酰化方向——本文完全未涉及乳酸代谢或乳酰化修饰，无直接接口，但其"氧化应激驱动持续性蛋白修饰"的整体框架（AGE 非酶糖化蛋白）可类比性地为乳酰化这一类似的代谢-蛋白修饰机制提供背景论证思路。</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>我要在原代内皮细胞或他已有的心脏/肠道存档组织衍生细胞体系中，做"瞬时高糖/棕榈酸刺激后测AMPK磷酸化ZSWIM8(S608/S609)水平及miR-33/miR-375成熟体丰度随时间(0/24/72h/7d恢复常糖)变化"的实验，预期发现即使代谢刺激撤除后，磷酸化ZSWIM8驱动的miRNA降解仍持续偏离基线，从而在miRNA降解层证实"代谢记忆"存在独立于组蛋白修饰的第二条机制。</t>
+          <t>这周可执行的具体动作：将本文 Fig.1 和 Fig.3 的机制框架图整理进 introduction slide，标注"此图未涉及 miRNA 分子机制（TDMD/尿苷化/乳酰化）"，并据此列出一份仅有3-4条的缺口清单，去 PubMed 用"ZSWIM8 metabolic memory" "TUT4 fibrosis hyperglycemia" "AGO2 lactylation"三组关键词各搜一次，确认本文参考文献表之外是否已有人做过这个交叉。</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】读全文时要挑三类参考文献：①DCCT/EDIC原始临床试验及后续机制随访文献（获取具体肾病发生率数字）；②El-Osta/Brownlee组关于内皮细胞组蛋白甲基化与代谢记忆的原始实验论文（获取实验设计与时序对照细节）；③任何早期（2010年前）关于糖尿病/高糖环境下miRNA表达谱变化的文献（哪怕未被此综述引用，也要通过引文网络回溯确认miRNA降解层确实是空白，而非被忽略引用）。</t>
+          <t>Kim J, et al. 2019《Epigenetics and epigenomics in diabetic kidney disease and metabolic memory》Nat. Rev. Nephrol. — 与本文同题材的姊妹综述，比 2010 版新且比本文早，可用来交叉核对表观遗传机制部分是否引用了 miRNA 相关工作；el-Osta A, et al. 2008《Transient high glucose causes persistent epigenetic changes and altered gene expression during subsequent normoglycemia》J. Exp. Med. — 是"代谢记忆"表观遗传证据链的原始实验论文，值得排队核实其是否检测了 miRNA 层面变化；Testa R, et al. 2024《An update on chronic complications of diabetes mellitus: From molecular mechanisms to therapeutic strategies with a focus on metabolic memory》Mol. Med. — 2024年最新更新综述，可能已纳入非编码RNA/miRNA更细的机制，值得核对是否提及 TUT4/7 或 TDMD；Testa R, et al. 2017《The "Metabolic Memory" Theory and the Early Treatment of Hyperglycemia in Prevention of Diabetic Complications》Nutrients — 补充早期干预证据链，可用于②纤维化方向中论证"早期糖控制窗口"对 MYBPC3/SAA3 纤维化终点的意义。</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>同意，T2合理——本文仅作背景性机制综述，用于确立"代谢记忆现有解释未覆盖miRNA降解层"这一空白论证，无需精读实验细节，符合第6周"疾病叙事与已有机制解释"梳理性质的阅读需求。</t>
+          <t>【替代】原 PMID 20421885（Metabolic memory and diabetic nephropathy: pot…）无开放全文，换成本篇。理由：同为综述、同一命题（高糖诱导的代谢记忆→表观遗传记忆），2025 年版本比 2010 年 Nat Rev Nephrol 更新 15 年文献。</t>
         </is>
       </c>
       <c r="AB31" s="2" t="n"/>
@@ -5053,7 +5048,7 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>全文已读 · 你提供的 PDF · micro-rna-profiling-mir-29</t>
+          <t>全文已读 · 你提供的 PDF · micro-rna-profiling-mir-</t>
         </is>
       </c>
       <c r="G35" s="2" t="n">
@@ -5297,128 +5292,128 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>20201077</t>
+          <t>40124162</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/20201077/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/40124162/</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>仍缺全文</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="n">
-        <v>2010</v>
+          <t>替代文献 · PMC 全文 · PMC11930095</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Arthritis and rheumatism</t>
+          <t>Molecular therapy. Nucleic acids</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>428</v>
+        <v>4</v>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>MicroRNA-29, a key regulator of collagen expression in systemic sclerosis.</t>
+          <t>Ratio of miRNA-29 to miRNA-199 expression coordinates mesenchymal stem cell repair of bleomycin-induced pulmonary injury.</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>系统性硬化中 miR-29 作为胶原关键调控者</t>
+          <t>此文承接被替换文献PMID20201077(皮肤系统性硬化中miR-29调控collagen)在笔记体系中的角色——即"miR-29/miR-199比值协调MSC抗纤维化修复、原发研究且有collagen读出"这一功能位置，但将验证组织从皮肤换成肺，与他已有的 20971881（miR-29 是肺纤维化相关基因的主要调控者，Am J Respir Cell Mol Biol 2011）在组织层面重叠，为方向②TUT4/7-miR-29-纤维化提供跨器官（肺vs心脏MYBPC3/肠SAA3）的表型对照案例。</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>人源样本证据</t>
+          <t>必须带走：(1) miR-29a与miR-199a呈相反方向变化，其比值是本文核心读出，但因果验证仅用双转染而非单变量干预，存在混淆风险；(2) ASC在day12（纤维化已建立后）给药仍有效，区别于预防性给药范式，具有治疗窗口意义；(3) 全文完全没有涉及RNA修饰/降解机制层面(TDMD、尿苷化、乳酰化)，是纯表达水平和下游靶点(MMP-2/CAV-1)的功能性研究，需要另外文献补充机制层。</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>miR-29a 在 SSc（系统性硬化）皮肤与纤维化模型中下调，且该下调由 TGFβ/PDGF-B/IL-4 信号驱动、可被 imatinib 逆转；论文将其解释为"上游信号抑制 miR-29a 表达"而非降解通路的作用——这是本周要对比的转录层解释的典型代表。</t>
+          <t>在博来霉素(BLM)诱导的老年小鼠肺纤维化模型中，day 12 静脉输注脂肪来源间充质干细胞(ASC)能显著上调抗纤维化 miR-29a、下调促纤维化 miR-199a，使 miR-29:miR-199 比值升高，同时降低 Ashcroft 评分、肺胶原含量与 MMP-2 活性、升高 CAV-1 表达，从而减轻已建立的肺纤维化。</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>回答了"miR-29a 下降是否能解释 SSc 中 I/III 型胶原升高"，并把机制锁定在 TGFβ/PDGF-B→miR-29a 表达下降→collagen 去抑制这一转录/信号轴，而完全没有涉及成熟miRNA的降解速率或TUT4/7尿苷化通路。</t>
+          <t>它回答的问题是：在纤维化已经建立之后（而非预防性给药）才输注 ASC，是否仍能通过调节 miR-29/miR-199 比值及其下游靶点(MMP-2、CAV-1)逆转/减轻博来霉素诱导的肺纤维化，并恢复AECI/AECII标志物表达。</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】需要找：(1) TaqMan qPCR的图是否区分了pri-miR-29/pre-miR-29 vs 成熟miR-29a的丰度（摘要只提"miR-29 levels”，不确定是否做了转录本层区分）；(2) 时间序列图——TGFβ刺激后miR-29a下降的动力学(几小时vs几天)，用以判断是转录抑制还是降解加速；(3) 是否有actinomycin D或类似转录阻断实验测定miR-29a半衰期；(4) 图中n值和统计方法，剂量反应曲线是否存在。</t>
+          <t>Fig 1F/1G 显示 ASC 输注后 Ashcroft 评分与羟脯氨酸胶原含量均较 BLM 组下降（n=6–10/组，*p&lt;0.05至***p&lt;0.001，个体生物学重复点图），但图注未提及是否有第二种独立方法交叉验证胶原沉积（如 qPCR 之外的蛋白定量）。Fig 3A–C 显示 miR-29a 升高、miR-199a 降低、二者比值升高（RT-PCR，U6为内参，n=6–8或3–6/组），Fig 3D 为 miRNAscope 代表性图像做定性支持，Fig 4 用体外双转染(29KI/199KO)人IPF肌成纤维细胞及3D ex vivo肺explant模型独立验证了miR-29/199对MMP-2和CAV-1的调控，属于跨体系（in vivo+in vitro+ex vivo）的独立验证，可信度较高。</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>方法要点：①in silico预测miRNA-靶基因(collagen)；②TaqMan real-time PCR定量miR-29a（他缺smallRNA-seq但qPCR他可用）；③pre-miRNA/anti-miRNA转染(Lipofectamine)做功能验证——这一条可直接搬用于他自己的miR-29 in vitro功能验证；④luciferase reporter验证直接靶向；⑤bleomycin诱导小鼠皮肤纤维化模型——可作为纤维化体系的备选对照模型；⑥imatinib药理阻断PDGF-B/TGFβ通路观察miR-29a恢复。他能搬的是③和⑥（药理阻断+miRNA功能转染），⑤可作为纤维化模型的补充。</t>
+          <t>体系为22月龄老年C57BL/6小鼠气管内注射BLM(2.0 U/kg)造模，day12尾静脉输注4月龄年轻供体来源ASC(5×10^5细胞)，day21取材；关键读出包括μCT、Masson三色染色+Ashcroft评分、羟脯氨酸胶原测定、western blot(pAKT/AKT、CAV-1)、RT-PCR(miR-29a、miR-199a，U6内参)、miRNAscope FISH、MMP-2 zymography、免疫荧光(AQP5/SPC/α-SMA)；体外补充实验用IPF患者肌成纤维细胞进行miR-29 mimic+miR-199 inhibitor双转染(29KI/199KO)及小鼠肺3D ex vivo explant模型。</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>体系边界：人SSc患者皮肤活检+原代皮肤纤维化细胞（人源，已到患者组织层级）+ bleomycin小鼠皮肤纤维化模型（体内验证）+细胞转染/luciferase（体外机制）。未涉及心脏或肠道纤维化，也未涉及TUT4/7或尿苷化机制，外推到他的MYBPC3心脏/SAA3肠道体系需要谨慎，组织特异性未知。</t>
+          <t>结论成立于博来霉素诱导的小鼠肺纤维化体系（老年C57BL/6小鼠）及体外/ex vivo人IPF肌成纤维细胞和小鼠肺explant模型中；外推到人体临床纤维化的限制在于：BLM造模是急性化学损伤模型，其时间线和纤维化机制与人类IPF慢性渐进性病程存在本质差异，且ASC来源为异种（人/小鼠混用）或同种年轻供体，未在人体中验证同等给药方案的安全性和有效性。</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】需要核对的对照清单：①健康对照皮肤/纤维化细胞的样本量、性别年龄匹配；②scramble/anti-miR对照转染是否设置；③imatinib是否有溶剂对照及剂量梯度；④bleomycin模型是否有PBS-only对照组；⑤luciferase实验是否用mutant 3'UTR seed-site对照排除非特异效应；⑥qPCR是否用snRNA/U6等内参并说明其在纤维化组织中的稳定性。</t>
+          <t>文中明确做了的对照：saline对照组（无BLM）、BLM-only组（无ASC）、体外用scrambled质粒转染对照("C"组)、3D explant用control scrambled质粒注射对照。缺少的关键对照：未见针对miR-29或miR-199单独敲低/过表达（非双转染）以区分二者独立贡献的对照，也未提及ASC来源（人vs小鼠）对结果一致性的种属对照，这对判断miR-29:miR-199比值机制的特异性很重要，因为双转染(29KI/199KO)无法排除两个miRNA变化各自的独立效应大小。</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>【摘要未报告数字】读全文时优先补：miR-29a在SSc皮肤/纤维化细胞中下调的确切fold-change或Ct差值；imatinib处理后miR-29a恢复的定量倍数；collagen mRNA/蛋白变化的定量百分比；luciferase活性下降的具体百分比数值。</t>
+          <t>Table1：BLM组day21体重变化−27.3%±3.7%(n=6) vs BLM+ASC组−15.0%±2.6%(n=6, p&lt;0.05 vs BLM)；Table2：BLM+ASC组collagen type1α1降至33±15.2%（vs BLM组116±35%，p&lt;0.01）；Fig1H显示pAKT/AKT比值BLM组升高、ASC组下降(p&lt;0.05)；Fig3A/B显示miR-29a、miR-199a变化(p&lt;0.05, p&lt;0.01)；Fig4E显示3D explant Ashcroft评分差异p&lt;0.002至p&lt;0.0001。全文未见miR-29或miR-199表达变化的具体倍数值（如fold change数字），仅有相对百分比和统计显著性标注。</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>该文完全未测miR-29a的稳定性/半衰期或pri-/pre-体丰度，因此"miR-29a下降"的数据实际上无法区分是转录抑制还是降解加速——它把TGFβ处理后miR-29a降低直接归为转录调控的推断缺乏机制层证据；此外imatinib恢复miR-29a的机制可能只是阻断了上游信号通路转录抑制，并不能排除同时发生的降解通路变化，论文没有做任何实验来排除后者，这正是"降解假设还剩多少空间"的关键漏洞——摘要没有提供任何区分转录vs降解的实验，其结论"posttranscriptional regulation of collagens by miR-29a"其实说的是miR-29a对collagen的posttranscriptional调控，而非miR-29a本身受posttranscriptional(降解)机制调控，容易被误读为支持降解假设。</t>
+          <t>我不相信"miR-29:miR-199比值"是驱动疗效的因果机制这一表述的严格性，因为体外/ex vivo验证实验用的是miR-29 mimic加miR-199 inhibitor的联合双转染(29KI/199KO)，而没有单独miR-29或单独miR-199的干预组作对照，因此无法确定该比值本身有独立生物学意义，还是仅是miR-29效应主导、miR-199变化只是伴随现象。</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>当前主线：miR-29/TGFβ-Smad3转录抑制轴在纤维化领域已是被广泛引用(428次被引)的经典范式，Maurer/Jüngel等纤维化风湿病学者持续在推进miR-29-based治疗靶点研究，是转录层解释的奠基性文献之一。</t>
+          <t>该文处于"MSC治疗纤维化的miRNA机制"这一持续熱点位置，聚焦于治疗性（而非预防性）给药窗口和miRNA比值调控这一相对小众但正在被关注的角度，衔接了miR-29抗纤维化这一经典热点（已有大量文献如PMID20971881），同时呼应当前对AKT信号通路、AECI/AECII细胞群体恢复在IPF衰老模型中的作用的研究趋势。</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>作者自己承认/隐含的未解问题：①未测miR-29a降解速率或3'端修饰状态（他可以做，用他熟悉的TUT4/7尿苷化+3'端测序补齐，但3'末端测序他也缺技能，需合作）；②未区分pri/pre vs成熟体丰度变化（他可以用现有qPCR探针体系或与合作方补做）；③未在人体系中验证TUT4/7是否参与miR-29a降解（这正是他方向2的空白，他能做）。</t>
+          <t>它明确暴露的空白：全文未提供miR-29/miR-199上游是如何被ASC旁分泌信号调控的分子机制（如是否通过exosome miRNA转移或旁分泌因子诱导内源转录），也未检测ZSWIM8、TUT4/7、TDMD或任何miRNA降解通路相关分子，对miRNA稳态调控的分子机制层面完全缺失，仅停留在表达水平的现象观察。</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>未来三年走向：转录调控(TGFβ-Smad3-miR-29)范式已趋饱和，被广泛引用但机制层面少有新突破；降解层面(TUT4/7尿苷化、ZSWIM8-TDMD)是上升中但几乎空白的方向。建议策略：绕开转录层证据的重复验证，直接抢先做"降解层面是否独立于/叠加于转录抑制"的实验，用他的心脏/肠道存档组织快速切入方向2。</t>
+          <t>未来三年，该领域可能走向：(1)明确ASC旁分泌因子如何在体内重编程受体细胞miRNA稳态（是否涉及TDMD或RNA修饰机制）；(2)将miR-29/miR-199比值作为IPF治疗反应的生物标志物推向临床；(3)结合单细胞或空间转录组解析ASC输注后AECI/AECII及肌成纤维细胞群体中miRNA调控网络的时空动态。</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>与方向2（TUT4/7-miR-29-纤维化）直接相关：属于**竞争风险**——这篇论文已经用"TGFβ/PDGF-B转录抑制miR-29a"完整解释了SSc皮肤纤维化中miR-29a下降+collagen升高的现象链条，且被引428次是该领域公认机制；他若只重复"miR-29a下降→纤维化"这条表型链，会直接撞上这篇奠基性转录解释论文，必须明确证明TUT4/7尿苷化介导的降解是独立/叠加机制，而非重复发现transcriptional down-regulation。可用的对照值：imatinib恢复miR-29a水平可作为他判断"转录抑制是否被阻断后miR-29a仍持续降解"的阳性对照药理工具。</t>
+          <t>此文可为方向②(TUT4/7对miR-29 3′尿苷化→器官纤维化)提供直接的体内表型和组织资源接口：其博来霉素肺纤维化模型及miR-29a表达下调/ASC回补上调的现象，为检验TUT4/7介导的miR-29尿苷化是否在肺纤维化中同样发生（对照他已有的MYBPC3心脏与SAA3肠存档组织）提供了一个可平行验证的呼吸系统纤维化体系；具体可在下一步中用这批BLM肺组织（如可获取）做miR-29 3′端尿苷化程度的TAIL-seq或分层qPCR，检验是否与心脏/肠道纤维化中的TUT4/7-miR-29通路一致。</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>我要在他自己存档的MYBPC3心脏纤维化和SAA3肠道纤维化组织中，先用actinomycin D转录阻断+qPCR测定miR-29a半衰期（区分pri/pre vs mature），再检测TUT4/7介导的3'尿苷化标记物丰度，预期若TUT4/7降解通路独立于TGFβ转录抑制起作用，则imatinib阻断TGFβ信号后miR-29a半衰期仍应显著低于健康对照，从而在这篇论文的转录解释之外找到降解层面的独立证据空间。</t>
+          <t>这周可执行的具体动作：联系原作者或检索是否可获取/申请该研究中day21 BLM及BLM+ASC组的存档肺组织RNA，设计一组miR-29a 3′端尾部尿苷化特异性qPCR或TAIL-seq引物，用于检测TUT4/7活性在BLM肺纤维化及ASC回补后是否伴随miR-29尿苷化水平的相应变化。</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】需要从参考文献里挑三类：①miR-29家族在其他纤维化器官（肺、肾、心脏）中的调控证据，判断组织特异性；②TUT4/7或其他尿苷化/降解机制在miRNA稳态中的早期文献，看这篇2010年论文是否已引用过降解假说但未验证；③TGFβ-Smad3直接结合miR-29启动子的ChIP或转录起始位点证据文献，用以判断转录抑制机制本身的证据强度是否足够排他性。</t>
+          <t>由于本文提供的材料中【参考文献表】标注为"未提供参考文献表"，无法从段外文献列表中逐字摘取标题，因此本栏无法按要求列出3–5篇参考文献；仅正文中提及的编号引用（如ref17自身既往ASC预防性给药研究、ref39/40关于miR-29抗纤维化、ref41关于miR-199上调于纤维化、ref22/42关于CAV-1被miR-199调控）缺乏完整标题信息，不能编造标题列出，故留空并明确说明原因。</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>同意，T1合理——该文是竞争性转录解释的关键人源证据来源，需精读但非直接决定他Aim成败的核心方法学文献。</t>
+          <t>【替代】原 PMID 20201077（MicroRNA-29, a key regulator of collagen expre…）无开放全文，换成本篇。理由：miR-29 机制主体保留（miR-29/miR-199 比值协调 MSC 抗纤维化修复），原发研究、有 collagen 读出；代价是组织从皮肤换成肺（你已有 20971881 肺）。备选 40021656 正好是硬化症皮肤但机制是 TGF-β1/Smad3、miR-29 零提及，故未选。</t>
         </is>
       </c>
       <c r="AB37" s="2" t="n"/>
@@ -5845,7 +5840,7 @@
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>全文已读 · 你提供的 PDF · 1-s2.0-S1097276508006606-m</t>
+          <t>全文已读 · 你提供的 PDF · 1-s2.0-S1097276508006606</t>
         </is>
       </c>
       <c r="G41" s="2" t="n">
@@ -5977,7 +5972,7 @@
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>全文已读 · 你提供的 PDF · 1-s2.0-S0092867409009647-m</t>
+          <t>全文已读 · 你提供的 PDF · 1-s2.0-S0092867409009647</t>
         </is>
       </c>
       <c r="G42" s="2" t="n">
@@ -6109,7 +6104,7 @@
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>全文已读 · 你提供的 PDF · 1-s2.0-S0092867412011294-m</t>
+          <t>全文已读 · 你提供的 PDF · 1-s2.0-S0092867412011294</t>
         </is>
       </c>
       <c r="G43" s="2" t="n">
@@ -6881,31 +6876,31 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>42622514</t>
+          <t>39977234</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42622514/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/39977234/</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>仍缺全文</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="n">
-        <v>2026</v>
+          <t>替代文献 · PMC 全文 · PMC12166298</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -6913,96 +6908,96 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>Novel proteomic signatures of stricturing Crohn disease using a treatment-naive cohort.</t>
+          <t>Novel Transcriptomic Signatures in Fibrostenotic Crohn's Disease: Dysregulated Pathways, Promising Biomarkers, and Putative Therapeutic Targets.</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>2026 年狭窄型克罗恩病的蛋白组学特征</t>
+          <t>这篇承接的是被替换的PMID 42622514（同刊、同病、同问题的蛋白质组学研究）留下的"分子标志物"角色，但把检测层从蛋白质组换成转录组，提供了与蛋白质组平行、互补的DEG/通路/细胞类型定位证据，用于在阅读计划里比较蛋白与mRNA两层证据是否指向同一批狭窄特异基因（如GREM1/SERPINE1），并为方向②的ECM靶基因筛选提供转录组层面的候选清单。</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>可作为人源验证的分子标记</t>
+          <t>必须带走：①81个DEG中GREM1、SERPINE1、LY96等8个基因是狭窄特异候选标志，且GREM1经scRNA-seq确认特异于成纤维细胞；②样本量极小（9例bulk、3例单细胞）、缺健康对照、Fig4功效分析基于合成数据而非真实前瞻队列，证据强度有限，不能当作已验证的biomarker；③全文未涉及miRNA或RNA修饰层面数据，与Sheldon课题的连接需要研究者自己做DEG-miR-29靶点交集这一步。</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>血清蛋白组学+机器学习筛选出与克罗恩病肠狭窄相关的诊断/预测模型，GPC6是核心候选标志物，其在纤维化肠黏膜/黏膜下层的成纤维细胞中特异性高表达，提示GPC6可能是狭窄型CD纤维化成纤维细胞亚群的标记物而非全身炎症标志物。</t>
+          <t>在9例纤维狭窄型CD患者的手术切除标本中，狭窄段相对于非狭窄近端/远端边缘存在81个重叠DEGs（64上调、17下调），其中LY96、AKAP11、SRM、GREM1、EHD2、SERPINE1、HDAC1、FGF2这8个基因对狭窄具有高特异性，并被scRNA-seq定位到特定细胞类型（如GREM1特异于成纤维细胞）。</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>回答了"狭窄型（B2）与非狭窄非穿透型（B1）CD患者能否通过血清蛋白组学区分、能否预测B1向狭窄进展"这一此前缺乏系统蛋白组学证据的问题；也部分回答了"肠道纤维化在单细胞层面哪类细胞高表达候选标志物"。</t>
+          <t>它回答的问题是：在无活动性炎症（RHI≤3）的终末期纤维化狭窄组织中，哪些转录本/通路能把狭窄段与同一患者的非狭窄近端、远端边缘区分开，并且这些差异基因分别来自哪类细胞。</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】需要找：①诊断模型5个蛋白具体身份及其与GPC6的关系图；②单细胞转录组分析中成纤维细胞亚群的分群图（UMAP/tSNE）及GPC6在各亚群中的表达小提琴图/热图，明确是哪一类成纤维细胞亚群（如炎性成纤维细胞、肌成纤维细胞）；③免疫荧光双染GPC6与成纤维细胞标志物(如PDGFRA/ACTA2)的共定位图及n值；④RISK队列中GPC6 mRNA/蛋白与狭窄进展时间的关联图。</t>
+          <t>Fig 1D/E显示将狭窄、近端、远端三组联合分析时，狭窄样本在无监督PCA与有监督PLS-DA中均形成独立聚类，而近端与远端重叠，提示狭窄转录组特征稳定；Fig 1F/G给出81个DEG的重叠与上下调方向（64上/17下），但文中未说明PCA/PLS-DA重复次数，仅为9例患者的单次队列分析；Fig 3C与Fig5B用AUC评估8个基因个体及联合诊断效能并给出置信区间，属于同一批患者内部交叉验证，Fig4通过合成数据的功效分析估计GREM1、LY96、SERPINE1在n=20时功效≥75%，这是模拟推算而非独立重复实验；Fig6用3例患者、31195个细胞的scRNA-seq对候选基因做细胞类型定位，属于第二种独立方法（转录组测序层级不同、细胞分辨率更高）的验证，但样本量同样很小。</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>①血清+配对肠组织蛋白质组学发现队列(n=62)，机器学习特征选择建立诊断模型(AUC 0.754)和进展预测模型(AUC 0.947)——此机器学习+多队列外部验证的建模思路本身不可直接搬用（依赖蛋白组学平台），但外部ELISA验证+多中心队列+RISK公共队列联合验证的**验证策略可搬用**于他自己的候选分子（如miR-29/TUT4-7蛋白）人源样本验证；②单细胞转录组+免疫荧光验证候选分子细胞来源——此**方法可直接搬用**到他的肠道类器官/存档组织，用于定位TUT4/7或pri-miR-29表达细胞亚群。</t>
+          <t>体系为9例（qPCR验证扩至14例）人纤维狭窄型CD手术切除肠段，取狭窄、非狭窄近端、非狭窄远端三个部位新鲜组织；关键方法为QIAseq UPX 3′ transcriptome kit建库+Miseq/Nextseq测序（1-3百万reads/样本）、limma做DEG（adj.P&lt;.05，fold change 2）、PLS-DA/VIP选基因、Random Forest AUC分类、EnrichR做通路富集；读出方式包括bulk RNA-seq、TaqMan qPCR（2-ΔΔCt）、公共数据集GSE192786验证、以及10x Chromium scRNA-seq（Seurat v3.2.2, UMAP聚类）。</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
         <is>
-          <t>人体系：treatment-naive CD患者血清+肠道组织(发现队列62例)，外部验证队列(FAH-SYSU+SRRSH, n=62)，RISK公共队列(n=237)，未涉及细胞系或动物模型；结论外推止步于"标志物关联"层面，未做因果机制（如GPC6敲低/过表达验证其致纤维化作用）。</t>
+          <t>体系严格限定在人纤维狭窄型CD（Montreal B2、L1为主）手术切除的末端回肠组织，且经RHI≤3筛选排除活动性炎症，即代表"终末期、无炎症"的纯纤维化状态；外推边界很窄：样本量仅9例（bulk）/3例（scRNA-seq），单中心（英国伯明翰），3′-based UPX测序深度仅1-3M reads/样本，属于浅层转录组，且未在动物模型或体外功能实验中验证因果关系，无法外推到其他肠段（如结肠L2）或早期/活动性炎症阶段的纤维化。</t>
         </is>
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】需要核对：①诊断/预测模型是否对年龄、病程、用药（生物制剂/免疫抑制剂使用史）做了协变量校正；②B1 nonprogressor对照组的定义与随访时长是否与progressor组匹配；③ELISA验证中是否设置了健康对照及UC(溃疡性结肠炎)患者作为疾病特异性对照；④单细胞分析中狭窄组织与非狭窄组织（或非IBD对照肠组织）是否配对比较。</t>
+          <t>文中明确做的对照包括：以非狭窄近端与非狭窄远端两个部位作为狭窄的内部对照（同一患者三点取材，配对设计）；RHI≤3排除混杂的活动性炎症；qPCR以β-actin作为housekeeping基因归一化；用独立公共数据集GSE192786（19纤维化vs21非纤维化）做外部验证。缺少的关键对照：未见健康对照（非CD）肠组织的比较，因此无法判断这些DEG是CD特异还是狭窄特异；也未做功能学验证（如基因敲低/过表达的成纤维细胞或类器官实验）来确认因果性，这些基因目前仅是关联性标志物。</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>诊断模型（5蛋白，区分B1 n=30 vs B2 n=20）AUC=0.754；预测模型（另5蛋白，10例B1 progressors）内部AUC=0.947；外部ELISA验证队列n=62，RISK队列n=237；GPC6在B2组血清及进展组肠组织中"升高/趋势一致"，但摘要未报告具体倍数变化、p值或ELISA的AUC/敏感性特异性——读全文时优先补：GPC6单独作为标志物的AUC、倍数变化(fold change)、统计学p值。</t>
+          <t>狭窄vs近端边缘303个DEGs，狭窄vs远端边缘224个DEGs，近端vs远端91个DEGs（正文Results段），三者重叠得到81个DEGs（64上调/17下调，Fig 1F/G）；DEG阈值为adj. P&lt;.05且fold change=2（Methods）；Fig4功效分析显示GREM1、LY96、SERPINE1在样本量n=20时诊断功效≥75%；qPCR验证用9+5=14例患者，Fig5B的AUC及Fig3C的AUC均给出置信区间但正文摘录片段未列出具体AUC数值。</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>摘要未说明GPC6升高是狭窄的原因还是纤维化后的继发表现（无功能学验证，如GPC6 knockdown对成纤维细胞胶原分泌的影响），且预测模型仅基于10例B1 progressors样本量极小、内部AUC=0.947很可能存在过拟合，需外部前瞻性队列证实其预测效力而非诊断队列的回顾性关联；此外GPC6作为蛋白多糖类分子，其升高可能反映细胞外基质重塑的下游共同通路（而非miRNA降解特异性机制），不能直接说明其与miR-29/TUT4-7轴的因果关系。</t>
+          <t>我不相信仅凭AUC/功效分析就能称这8个基因为"biomarkers"：这些数值来自极小样本（9-14例患者）内部的机器学习交叉验证与合成数据模拟（Fig4的"validation"实际是log-normal分布生成的合成数据推算所需样本量，并非真实独立队列的前瞻验证），且缺乏健康对照，所以特异性声称（"high specificity for strictures"）证据强度有限，需要独立、更大样本、含健康对照的队列重复才能确认。</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>上升中：CD肠道纤维化的蛋白组学/单细胞标志物发现是当前IBD转化医学的热点方向，中山一院/邵逸夫医院团队及RISK队列（美国CD儿童队列联盟）等多个多中心团队在推动血清标志物向临床诊断工具转化。</t>
+          <t>该文处于IBD纤维化研究从"炎症驱动"转向"细胞类型特异性/多组学驱动"的热点位置：与2023-2024年发表的Mukherjee等（PMID 37507073）和Zhang等（PMID 39024569/39286981）的CD狭窄scRNA-seq成纤维细胞异质性研究呼应，但本文的独特定位是聚焦"无活动性炎症的终末期纯纤维化"组织并用bulk+scRNA-seq联合筛选可诊断的转录标志物，试图弥补此前研究偏重成纤维细胞异质性、未分期取材的空白。</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>作者未解决的问题：①GPC6升高的上游调控机制未知（摘要未提miRNA/TGF-β等调控层面，他可以做——检测GPC6 mRNA是否受miR-29或TUT4/7介导的降解调控）；②GPC6在成纤维细胞中促纤维化的功能机制未验证（他可以做——用其肠类器官/成纤维细胞系做GPC6 knockdown后测胶原表达）；③诊断/预测模型未做前瞻性多中心大样本验证（他可能无法独立完成，需要临床协作网络）。</t>
+          <t>它自己承认的空白包括：目前尚无生物标志物或抗纤维化疗法进入临床实践（Introduction开篇即指出）；本研究未纳入结肠型（L2）狭窄，仅限末端回肠；scRNA-seq队列仅3例，HDAC1、AKAP11、SERPINE1在所有细胞亚群中表达量低，机制解释力有限；文中也未提供miRNA或RNA修饰层面的任何数据，转录组层面止步于mRNA差异表达和通路富集。</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>未来3年方向predicted为：①GPC6及类似蛋白多糖标志物会被整合进多标志物panel用于CD狭窄早期预测临床试验；②单细胞+空间转录组会进一步细分致纤维化成纤维细胞亚群及其miRNA调控网络。建议采取"跟进"策略——将GPC6纳入他自己肠道纤维化(SAA3肠存档组织)模型的候选读出指标之一，而非直接竞争蛋白组学标志物发现赛道。</t>
+          <t>未来三年该方向可能走向：（1）在更大规模、多中心队列中验证LY96/GREM1/SERPINE1等标志物的诊断效能并纳入健康对照；（2）结合功能学模型（类器官、成纤维细胞敲低）确认因果性并筛选抗纤维化靶点；（3）与单细胞多组学（如空间转录组）结合，进一步解析狭窄区域内成纤维细胞、内皮细胞与免疫细胞的相互作用网络，逐步把GREM1、TWIST1+FAP+成纤维细胞等信号节点推向药物靶点开发（呼应参考文献中TWIST1抑制剂的小鼠实验）。</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>可用的对照值：GPC6在纤维化黏膜/黏膜下层成纤维细胞中高表达可作为他SAA3肠纤维化存档组织的人源阳性对照/验证靶点，用于比对其miR-29-TUT4/7轴致纤维化模型中成纤维细胞的分子特征是否与人源狭窄CD一致；竞争风险：若他计划以"血清标志物预测肠狭窄进展"为切入点会与本文及RISK队列团队直接竞争，应避开，转而聚焦机制层面（miR-29降解如何解除对胶原/GPC6上游通路的抑制）作为差异化定位。</t>
+          <t>与Sheldon课题的接口主要在方向②（TUT4/7-miR-29-器官纤维化）：本文提供的GREM1、SERPINE1、COL1A1等ECM重塑基因和上调的纤维化通路清单，可以作为在他的SAA3肠纤维化存档组织或类似肠道纤维化模型中检验miR-29家族及其TUT4/7介导的尿苷化是否调控这些下游ECM靶点的候选基因池；此外scRNA-seq确认GREM1特异于成纤维细胞，可为设计细胞类型特异性miR-29报告系统提供细胞类型选择依据。</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>我要在自己存档的CD/肠纤维化人源组织及类器官体系中，检测GPC6表达是否与miR-29成熟体水平（而非pri/pre-miR-29转录本）呈负相关，并在TUT4/7介导miR-29尿苷化增强的成纤维细胞亚群中验证GPC6是否上调，预期若miR-29降解加速会伴随GPC6及胶原表达升高，从而将GPC6确立为miR-29降解通路下游的人源验证标记物。</t>
+          <t>这周可执行的动作：从Supplementary File 1/2（本文DEG与通路富集完整列表，需联系作者或期刊获取）中调出81个DEG全名单，与他手头miR-29预测靶点列表做交集比对，先确认GREM1/SERPINE1/COL1A1是否在miR-29 3'UTR上有保守结合位点，为后续在SAA3肠道存档组织上做TUT4/7尿苷化-miR-29-靶基因的qPCR验证挑选优先基因。</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】需要从参考文献列表中挑选：①GPC6/glypican家族在纤维化或细胞外基质重塑中作用机制的既往文献（明确该分子是否已知与TGF-β/Smad3通路或miRNA调控有交集）；②RISK队列（儿童CD自然病程队列）的原始队列设计文献，用于评估其样本代表性及是否可获取miRNA相关数据；③本文机器学习建模方法所引用的蛋白组学平台及特征选择算法原始方法学文献，用于判断该建模流程是否可迁移到miRNA/蛋白联合标志物开发。</t>
+          <t>Zhang et al. 2024《TWIST1+FAP+ fibroblasts in the pathogenesis of intestinal fibrosis in Crohn's disease》J Clin Investig — 提供了纤维化特异成纤维细胞亚群及TWIST1药理抑制的小鼠数据，可为方向②的因果验证提供功能学范式参照；Mukherjee/《Stricturing Crohn's disease single-cell RNA sequencing reveals fibroblast heterogeneity and intercellular interactions》Gastroenterology 2023 — 与本文scRNA-seq设计直接对标，是评估GREM1等成纤维细胞标志物细胞类型特异性的关键背景文献；《Epigenetic and metabolic reprogramming of fibroblasts in Crohn's disease strictures reveals histone deacetylases as therapeutic targets》J Crohns Colitis 2023 — 涉及HDAC1（本文8个候选基因之一）在CD狭窄成纤维细胞中的表观遗传重编程，与方向③（乳酸/乳酰化修饰重编程稳态）在机制逻辑上有交叉，值得排队细读；《Targeting gremlin 1 prevents intestinal fibrosis progression by inhibiting the fatty acid oxidation of fibroblast cells》Front Pharmacol 2021 — 直接研究GREM1在肠纤维化中的功能机制，是本文核心候选基因GREM1的因果证据来源，可用于评估其是否适合作为miR-29下游验证靶点；《Inhibition of plasminogen activator inhibitor-1 attenuates against intestinal fibrosis in mice》Intest Res 2020 — SERPINE1（即PAI-1）功能抑制的小鼠肠纤维化数据，可为方向②中SERPINE1下游功能验证提供动物模型参照。</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>同意，T1合理——该文提供人源狭窄型CD的候选分子标记(GPC6)及成纤维细胞亚群定位证据，可作为他机制研究的人源验证锚点，但不涉及miRNA降解机制本身，无需精读方法学细节，T1（快速摘取标志物+验证策略）足够。</t>
+          <t>【替代】原 PMID 42622514（Novel proteomic signatures of stricturing Croh…）无开放全文，换成本篇。理由：同一期刊（Inflammatory Bowel Diseases）、同一疾病与同一问题（纤维狭窄型克罗恩的分子标志），把蛋白质组换成转录组。</t>
         </is>
       </c>
       <c r="AB49" s="2" t="n"/>
@@ -7297,7 +7292,7 @@
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>全文已读 · 你提供的 PDF · 1-s2.0-S1097276522002076-m</t>
+          <t>全文已读 · 你提供的 PDF · 1-s2.0-S1097276522002076</t>
         </is>
       </c>
       <c r="G52" s="2" t="n">
@@ -7561,7 +7556,7 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>全文已读 · 你提供的 PDF · 1-s2.0-S0092867424003970-m</t>
+          <t>全文已读 · 你提供的 PDF · 1-s2.0-S0092867424003970</t>
         </is>
       </c>
       <c r="G54" s="2" t="n">
@@ -8617,7 +8612,7 @@
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>全文已读 · 你提供的 PDF · 1-s2.0-S009286742100012X-m</t>
+          <t>全文已读 · 你提供的 PDF · 1-s2.0-S009286742100012X</t>
         </is>
       </c>
       <c r="G62" s="2" t="n">
@@ -8879,9 +8874,9 @@
           <t>https://pubmed.ncbi.nlm.nih.gov/42763855/</t>
         </is>
       </c>
-      <c r="F64" s="5" t="inlineStr">
-        <is>
-          <t>仍缺全文</t>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>全文已读 · 你提供的 PDF · 978-1-0716-5412-5_9.pdf</t>
         </is>
       </c>
       <c r="G64" s="2" t="n">
@@ -8912,72 +8907,72 @@
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>这是一篇方法学综述/协议篇，核心判断：人肠类器官的3D培养（EGF+Noggin+R-spondin±Wnt agonist，加p38/TGF-β小分子抑制剂促增殖，IGF-1+FGF-2替代EGF/p38抑制剂促多系分化）与2D单层培养（便于顶膜暴露、可与肠道菌群共培养）已被整合为可操作的更新版协议，可作为肠道稳态与疾病建模的标准化平台。</t>
+          <t>这是一篇方法学章节，核心结论不是实验发现，而是给出人源肠道类器官3D与2D（monolayer）培养及FFPE组织学分析（H&amp;E、免疫荧光）的更新版可操作流程。</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>回答的是"如何标准化建立/维持人肠类器官（3D与2D单层）并进行组织学分析"这一操作层面的开放问题，而非任何miRNA降解或TDMD机制问题——它是纯方法学底座，不直接回答方向1/2/3的科学假设。</t>
+          <t>它回答的是"如何标准化地建立、传代、冻存人肠道类器官（3D与2D两种形式），并将其固定包埋、切片后进行组织学与免疫荧光分析"这一技术操作问题，而非某个生物学机制问题。</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】需要找：3D类器官成球/传代的时间轴图与培养基配方表（EGF/Noggin/R-spondin/p38抑制剂/TGF-β抑制剂/IGF-1/FGF-2的具体浓度与更换周期）；2D单层铺板密度、成膜时间与顶膜取样操作图；组织学染色（IHC/免疫荧光）panel示例图及定量方法（阳性细胞计数/面积占比的具体算法）；是否有与肠道菌群共培养的第二种方法（Transwell vs 微流控）。</t>
+          <t>Fig. 1 是3D类器官FFPE制片流程示意图（A-E：悬液→凝胶化→PFA固定→装盒→包埋于石蜡），Fig. 2 是2D单层类器官FFPE制片流程示意图（A-E：取膜→切半→夹Kimwipe→垂直包埋），二者均为操作步骤图而非数据图，不含样本量或统计学信息，可信度需依赖操作者重复性而非统计检验。Fig. 3 是代表性染色结果图，(A)(B)为H&amp;E染色，(C-F)为免疫荧光（Villin/Integrin-β4/ACE2/SGLT1/核染色），用于展示染色方法可行性，图注未给出n值或重复次数，故不能评估统计可信度。</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>①3D类器官培养体系：EGF+Noggin+R-spondin(Wnt agonist)长期维持自我更新与全分化能力——他可直接搬用作为肠类器官平台底座；②促增殖优化：加p38抑制剂+TGF-β通路抑制剂提高传代效率——可搬用，且TGF-β抑制剂使用与他的"TGF-β/Smad3抑制miR-29转录"竞争假说存在潜在方法学关联（需注意抑制剂本身可能改变miR-29转录本底，需在他的实验设计中作为变量控制）；③分化诱导：EGF/p38抑制剂替换为IGF-1+FGF-2促多系分化——可搬用于制造分化梯度以观察TDMD在不同细胞状态下的活性；④2D单层培养：便于顶膜直接给药/取样及菌群共培养——对方向2(TUT4/7-miR-29-纤维化)若涉及肠道SAA3类器官模型，2D体系可用于直接给予尿苷化抑制剂或病原/代谢刺激。</t>
+          <t>体系为人源十二指肠（duodenal）来源肠道类器官，3D培养采用Matrigel包埋+WENRAIF培养基（含Wnt3a条件培养液、R-spondin、Noggin、EGF、IGF-1、FGF-2、A83-01等），2D培养采用Matrigel涂层的cell culture insert（0.4µm孔径）建立单层。关键读出方式为FFPE切片后行H&amp;E染色及多重免疫荧光（Villin、Integrin-β4、ACE2、SGLT1、Hoechst核染色）。</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
         <is>
-          <t>体系边界：小鼠肠干细胞类器官（经典Sato体系）→人肠类器官3D/2D（本文更新版）；未涉及动物体内验证，也未涉及任何miRNA或TDMD相关内容，纯体外类器官平台，外推止步于"体外人源上皮细胞培养系统"这一步，不涉及大动物或临床。</t>
+          <t>该体系仅限于体外人源肠道类器官（十二指肠来源，3D球状结构与2D单层两种培养形式），是离体、去细胞外基质微环境（无间质）的简化模型。外推到活体人肠道组织或体内纤维化/代谢疾病表型时存在明显限制，例如文中提到"further optimization of the culture medium may induce maturation of organoids expressing transport proteins including SGLT1"，说明当前类器官在转运蛋白表达等成熟度上尚未完全模拟体内上皮，外推需谨慎。</t>
         </is>
       </c>
       <c r="R64" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】需要核对：①传代次数/代次是否设有基因组稳定性对照（如核型检测）；②p38/TGF-β抑制剂处理组是否有载体对照（DMSO等）；③2D单层与3D类器官之间的分化标志物（如Lgr5、villin、MUC2、ChgA等）表达是否有平行对照数据；④组织学定量是否设阳性/阴性染色对照及是否有独立重复批次间变异报告。</t>
+          <t>全文未见明确的阴性对照、同型对照抗体或空载体对照等实验设计层面的"对照组"描述，这属于方法学章节的固有性质——它给出的是操作步骤而非对照实验设计。缺少的关键对照包括：免疫荧光染色缺少一抗特异性对照（如isotype control或一抗省略对照），这对确认Villin/Integrin-β4/ACE2/SGLT1信号的特异性很重要；此外无不同批次Matrigel或不同代次类器官之间的重复性对照说明，这对评估该培养体系的稳定性和可重复性是必要的。</t>
         </is>
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>【摘要未报告数字】读全文时优先补：3D类器官传代成功率/形成效率（如出芽率%）、2D单层铺板后达到融合单层所需天数、分化诱导后各细胞谱系比例（如吸收细胞/杯状细胞/内分泌细胞占比%），以及组织学定量分析中给出的具体统计数值范围。</t>
+          <t>【全文未见定量数字】（该文为实验方案章节，无原始实验结果的效应量数据）。方案给出的关键参数包括：3D培养接种密度1–2×10³细胞/孔（48孔板），传代密度1–5×10³细胞/孔，冻存前密度1×10⁴细胞/孔；2D单层接种密度1.5–2×10⁵细胞/孔（24孔insert）；FFPE制样前3D培养密度3×10³细胞/孔培养5–7天；离心条件普遍为400×g、3分钟；抗原修复用pH9.0 Tris/EDTA或pH6.0 Citrate buffer。</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>本文使用TGF-β通路抑制剂来促进类器官增殖传代，这与他的核心竞争假说直接相关——TGF-β/Smad3已被证明在转录层面抑制miR-29；若未来用此类器官体系检测miR-29降解相关表型，必须先排除培养体系本身（TGF-β抑制剂长期存在）对miR-29前体转录本水平的系统性抬高，否则无法区分是TUT4/7介导的成熟体3′尿苷化降解变化，还是培养条件导致的pri/pre-miR-29转录本改变，这是摘要层面就能预见的方法学混杂，本文并未讨论如何解耦。</t>
+          <t>我不相信"IF condition"（去除p38抑制剂+补充IGF-1/FGF-2）真能让2D单层类器官在功能成熟度上普遍达到体内上皮水平，因为文中自己在Fig. 3注释里承认"further optimization of the culture medium may induce maturation of organoids expressing transport proteins, including SGLT1"，这说明当前呈现的SGLT1表达可能并不稳定或普遍，图3的染色结果更像是"潜力展示"而非成熟表型的常规产物。</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
         <is>
-          <t>当前主线|肠类器官培养与分化技术仍是消化道疾病建模的主流平台，Clevers/Sato及后续多个实验室在持续迭代3D→2D单层及类器官-菌群共培养体系；本文属于该主线内的方法更新，非miRNA降解机器领域，热度独立于他的三个核心方向。</t>
+          <t>该文处于肠道类器官技术方法学更新的位置，聚焦于3D/2D培养体系优化及组织学分析流程标准化，属于Sato实验室一脉相承的类器官技术迭代（从Sato 2009的Lgr5单干细胞类器官，到Fujii 2018的IF培养条件，再到本文的2D monolayer与FFPE制片更新），是工具性/平台性文献，不直接触及miRNA稳态、TDMD、乳酸化修饰等分子机制热点。</t>
         </is>
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>作者自己承认/隐含的未解问题：①2D单层与3D类器官在长期分化稳定性上的差异未系统比较；②与菌群共培养的具体验证指标（如屏障功能、炎症标志物）摘要未展开；③本文未涉及任何遗传编辑（CRISPR/ABE/BE4）与类器官联合使用的方案——这一条正是他能补的：他有CRISPR/ABE/BE4内源位点编辑技能，可以在此类器官平台上敲入ZSWIM8 S608/S609磷酸化位点突变或miR-29种子序列报告基因，把本文的"培养底座"升级为"可编辑的TDMD读出平台"。</t>
+          <t>该章节本身承认的空白包括：其一，2D单层类器官的转运蛋白（如SGLT1）表达尚未成熟，需进一步优化培养基（Fig. 3注释明确指出）；其二，全文未涉及任何RNA层面的表观修饰（如尿苷化、乳酰化）分析方法，也未提供miRNA相关的读出方案，这是与Sheldon课题对接时的明显技术空白。</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>未来三年，肠类器官2D单层+菌群共培养会继续成为主线（用于屏障/免疫/代谢互作研究），而"类器官+碱基编辑+miRNA降解读出"这一交叉尚是空白；建议策略为"跟进"该类器官方法学本身（直接采用其协议作为技术底座），但在"类器官+TDMD可视化读出"这一交叉点上"抢先"——用他独有的CRISPR/ABE/BE4能力在此类器官平台上先行布局，无人在做。</t>
+          <t>该技术方向未来三年可能继续朝三个维度发展：一是2D单层类器官在气液界面(air-liquid interface)或流体灌注系统下的进一步成熟化，以更好模拟体内上皮极性与转运功能；二是与肠道菌群共培养体系的整合应用扩展；三是FFPE/免疫荧光平台与单细胞或空间转录组、蛋白质组学技术的联用，以捕捉类器官内的细胞异质性与信号通路动态。</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>可搬的方法：3D类器官EGF/Noggin/R-spondin维持体系及2D单层顶膜暴露培养法，可直接用于建立他自己的肠道类器官miR-29降解报告系统（对接他已有的SAA3肠存档组织及方向2）。竞争风险：本文使用的TGF-β抑制剂促增殖策略与"TGF-β/Smad3转录抑制miR-29"文献直接相关，若他在此类器官体系中做miR-29降解实验，必须先排除该培养添加剂造成的转录层混杂，否则会被质疑其TDMD结论其实是转录调控假象，这是与既有TGF-β/Smad3竞争解释正面碰撞的风险点。</t>
+          <t>与Sheldon课题的接口主要在方向②：TUT4/7对miR-29尿苷化影响器官纤维化，可利用本文2D单层类器官培养及FFPE免疫荧光平台（Fig. 3的Villin/ACE2/SGLT1染色框架可直接替换为纤维化标志物或TUT4/7、miR-29相关探针）来构建体外肠道纤维化模型，尤其是文中提到的SAA3肠道存档组织可与本方案的FFPE制片流程（Fig. 1/Fig. 2步骤）对接，用于验证肠道类器官中TUT4/7-miR-29轴的组织学表型。方向①③（AMPK-ZSWIM8-TDMD、乳酸乳酰化重编程miRNA稳态）在本文中没有直接方法学支持，需要额外引入代谢应激处理或乳酸处理模块才能嫁接到该类器官平台上。</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>我要在人肠类器官2D单层培养体系（采用本文EGF/Noggin/R-spondin+IGF-1/FGF-2分化协议）中，用ABE/BE4内源编辑miR-29前体的3′尿苷化关键位点或TUT4/7结合序列，预期在不使用TGF-β抑制剂的分化培养条件下，通过smallRNA-seq区分pri/pre-miR-29与成熟miR-29水平变化，从而将TDMD效应与Smad3转录抑制效应解耦。</t>
+          <t>这周可执行的具体动作：按照本文3.4节2D单层类器官培养流程（Matrigel涂层insert+WENRAIF培养基），用他手头的肠道来源类器官系建立一批2D monolayer培养，并按3.5/FFPE制片流程（Fig. 2步骤）制作初步FFPE切片，用于后续TUT4/7或miR-29相关标志物的免疫荧光染色可行性测试。</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>【需读全文核对】需要从参考文献里挑三类：①原始Sato 2009类器官培养奠基文献及其后续小分子优化（p38/TGF-β抑制剂、IGF-1/FGF-2配方）的原始出处，用于核实浓度与批次一致性；②2D单层与菌群共培养方法的原始方法学论文，判断是否可直接移植到SAA3肠道模型；③本文作者团队此前发表的组织学定量分析方法原文，核对其定量算法是否可复用于miR-29相关免疫组化读出。</t>
+          <t>Sasaki N et al. (2020) 《Development of a scalable coculture system for gut anaerobes and human colon epithelium》 Gastroenterology — 与SAA3肠道纤维化/菌群互作模型直接相关，可为TUT4/7-miR-29肠道方向提供共培养平台参考，值得排队。Wang Y et al. (2019) 《Long-term culture captures injury-repair cycles of colonic stem cells》 Cell — 涉及肠道损伤-修复周期的长期培养技术，可能为纤维化相关的类器官慢性损伤模型提供方法学借鉴，值得排队。Fujii M et al. (2018) 《Human intestinal organoids maintain self-renewal capacity and cellular diversity in niche-inspired culture condition》 Cell Stem Cell — 建立了IF培养条件的基础方法，是本文2D/3D培养体系的核心依据，理解其原理对改造类器官平台做miRNA相关分子研究很关键，值得排队。Sugimoto S et al. (2021) 《An organoid-based organ-repurposing approach to treat short bowel syndrome》 Nature — 展示了类器官在肠道功能重建中的应用及外部灌注系统技术，可能为构建更成熟的类器官纤维化/代谢模型提供流体培养技术参考，值得排队。</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
@@ -9013,7 +9008,7 @@
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>全文已读 · 你提供的 PDF · nihpp-2026.01.05.697729v1.</t>
+          <t>全文已读 · 你提供的 PDF · nihpp-2026.01.05.697729v</t>
         </is>
       </c>
       <c r="G65" s="2" t="n">
@@ -9086,7 +9081,7 @@
       </c>
       <c r="U65" s="2" t="inlineStr">
         <is>
-          <t>当前主线：TDMD机制解析的结构生物学阵营（很可能是Bartel lab或Joshua-Tor/MacRae等结构生物学团队之一，需读全文核实作者），2023-2026年ZSWIM8-CUL3发现后进入结构确证阶段，这是TDMD领域当前最热的"结构机制"主线，而Xiaodong的方向1（上游信号调控ZSWIM8磷酸化）目前无人在此文中触及，仍是主线之外的空白。</t>
+          <t>当前主线|TDMD机制解析的结构生物学阵营，通讯作者为Brenda A. Schulman（马克斯·普朗克生化研究所）与David P. Bartel（霍华德休斯医学研究所／怀特黑德生物医学研究所／麻省理工学院生物系），并列第一作者为Jakob Farnung与Elena Slobodyanyuk。这是ZSWIM8-CUL3发现后TDMD领域进入结构确证阶段的代表性工作，属于当前该领域最受关注的"结构机制"主线。Xiaodong方向1（上游信号调控ZSWIM8磷酸化）在本文中未被提及，全文未给出相关内容，仍可能是主线之外的空白，但这属于判断而非本文已证实的事实。</t>
         </is>
       </c>
       <c r="V65" s="2" t="inlineStr">
@@ -9279,7 +9274,7 @@
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>全文已读 · 你提供的 PDF · nihpp-2026.01.07.698237v1.</t>
+          <t>全文已读 · 你提供的 PDF · nihpp-2026.01.07.698237v</t>
         </is>
       </c>
       <c r="G67" s="2" t="n">
@@ -9484,7 +9479,7 @@
       </c>
       <c r="U68" s="2" t="inlineStr">
         <is>
-          <t>上升中：TDMD领域正从个案发现（如Cxcr4-miR-17、NREP-miR-29等经典例子）转向全转录组系统预测阶段，Bartel/Duffy/Ipas等实验室及本文作者(推测为TDMDfinder团队，可能来自意大利/西班牙系统生物学组)在做计算预测+高通量验证，ZSWIM8机制发现(2020 Bartel/Jan lab)之后该领域迅速升温。</t>
+          <t>上升中|TDMD领域正从个案发现（如Cxcr4-miR-17、NREP-miR-29等经典例子）转向全转录组系统预测阶段，本文提出的TDMDfinder计算流程即用于在人和小鼠转录组中系统预测TDMD相互作用并结合实验验证与泛癌分析；全文未给出作者所属单位信息。ZSWIM8机制发现之后该领域迅速升温，正文提及该机制由两项近期研究阐明，但具体实验室归属全文未给出。</t>
         </is>
       </c>
       <c r="V68" s="2" t="inlineStr">
@@ -9662,14 +9657,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="118" customWidth="1" min="2" max="2"/>
+    <col width="120" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="96" customHeight="1">
+    <row r="1" ht="100" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
           <t>覆盖情况</t>
@@ -9677,53 +9672,67 @@
       </c>
       <c r="B1" s="7" t="inlineStr">
         <is>
-          <t>68 篇全部 14 栏已填。③关键图与可信度、⑥做了/漏了哪些对照、⑦效应量、⑭要排队的参考文献 这四栏原本标【需读全文核对】/【摘要未报告数字】，现按全文填写。来源分三类：**43 篇**来自 Europe PMC / NCBI PMC 开放全文（绿）；**20 篇**来自你自己上传的 PDF（蓝）；**5 篇**仍缺全文（黄）。</t>
+          <t>68 篇 × 14 栏全部填完，**不再有任何一栏标着「需读全文核对」**。来源三类：**43 篇** Europe PMC / NCBI PMC 开放全文（绿）；**22 篇** 你自己上传的 PDF（蓝，含两本 MMB 的第 9 章与第 40 章）；**3 篇** 是替代文献（紫）—— 原文没有开放全文，我换成了同角色、可拿到全文的论文。</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="96" customHeight="1">
+    <row r="2" ht="150" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>那 5 篇是什么</t>
+          <t>3 篇替代是哪些</t>
         </is>
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>20201077 Arthritis Rheum 2010 (miR-29 系统性硬化症)、20421885 Nat Rev Nephrol 2010 (代谢记忆综述)、32696389 MMB 2020 (IDP 多位点磷酸化检测)、42622514 IBD 2026 (克罗恩狭窄蛋白质组)、42763855 MMB 2027 (肠类器官培养方案)。其中两篇 MMB 章节在你上传的两本整卷书里（MMB 2141 与 MMB 3059），但书是整卷、不是单章，我没有替你从 400+ 页里猜哪一章对应 —— 你若指明章名或页码，我可以单独抽出来补。</t>
+          <t>① 周7：原 PMID 20201077（miR-29 调控系统性硬化症胶原，Arthritis Rheum 2010）→ **PMID 40124162**（miR-29:miR-199 比值协调 MSC 修复博来霉素肺损伤，Mol Ther Nucleic Acids 2025）。保留了 miR-29 作为机制主体与 collagen 读出，代价是组织从皮肤换成肺，与你已有的 20971881 在组织上重叠。曾考虑 PMID 40021656（正好是硬化症皮肤纤维化），但它的机制是 TGF-β1/Smad3、摘要里 miR-29 零提及，故未选。
+② 周6：原 PMID 20421885（代谢记忆与糖尿病肾病综述，Nat Rev Nephrol 2010）→ **PMID 41465114**（从代谢记忆到表观遗传记忆，Genes 2025）。同为综述、同一命题，多 15 年文献。
+③ 周9：原 PMID 42622514（纤维狭窄型克罗恩蛋白质组，IBD 2026）→ **PMID 39977234**（纤维狭窄型克罗恩的新转录组标志，IBD 2025）。同刊、同病、同问题，检测层从蛋白质组换成转录组。</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="96" customHeight="1">
+    <row r="3" ht="100" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
+          <t>替代的代价要说清楚</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>三篇替代的层级都被判为 **T2（支撑）、相关度 3（中）**，而原文分别是 T1/T2、相关度 4/3 —— **这是降级，不是等价替换**。原因写在每行的「层级复核」列里。若你能用 MSKCC 订阅取到原文，建议仍以原文为准，把替代文献当补充。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="100" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
           <t>为什么可以信</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>每条都要求点名文中真实存在的图号、数字、对照与参考文献。已机械核对：PMC 那 43 篇里 ⑭栏引用的 127 个 PMID **全部出自该文自己的参考文献表**；你提供的 20 篇里 ⑭栏引用的文献标题全部能在该文全文中逐字回查到。有 5 篇全文里确实没有定量数字，如实写了【全文未见定量数字】；1 篇（15728188 Hsp27 磷酸化抗体方法学文）如实说明其参考文献与你三个方向无重叠、不予排队 —— 都没有编。</t>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>每条都要求点名文中真实存在的图号、数字、对照与参考文献。已机械核对：PMC 那 43 篇 ⑭栏引用的 127 个 PMID 全部出自该文自己的参考文献表；你提供的 PDF 与 3 篇替代文献，⑭栏引用的标题全部能在该文全文里逐字回查到；③栏图号全部能对应。全文确无定量数字的（含两章实验方案与那篇综述）如实写了【全文未见定量数字】；1 篇方法学文如实说明其参考文献与三个方向无重叠、不予排队 —— 都没有编。</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="96" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>审计中抓到的两个真实问题</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>①Europe PMC 的全文接口对 20 篇返回 500（含 ZSWIM8 两篇 Science），换 NCBI PMC efetch 全部取到 —— 不是没有权限，是单一数据源的缺陷。②我的引文核对一度把 miR-375 那篇的 Tsuboi 2003 判成编造，实因 PDF 文本层把 5′ 抽成 50 并断行；核对逻辑改成避开 prime 的中段子串后确认它**确实在原文**。</t>
+    <row r="5" ht="100" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>替代文献自己承认的短板</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>39977234：样本量极小（9 例 bulk、3 例单细胞）、无健康对照、功效分析基于合成数据，不能当已验证的 biomarker。41465114：Fig.1/Fig.3 是机制示意图而非数据图，只能当背景框架引用。40124162：miR-29/miR-199 的因果验证只用了双转染而非单变量干预。这三条都写进了对应行的 ⑧ 与 ⑥ 栏。</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="96" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
+    <row r="6" ht="100" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>仍然要你做的</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>「我的核对与补充」列留空给你。三件事最值得亲手做：①③栏挑的关键图是否你也认为最关键；②⑥栏指出的「缺失对照」是不是真缺（可能在补充材料里）；③⑭栏排队的文献里哪几篇你要真读。</t>
         </is>
@@ -9740,227 +9749,199 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="58" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="54" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="72" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>PMID</t>
+          <t>周</t>
         </is>
       </c>
       <c r="B1" s="8" t="inlineStr">
         <is>
-          <t>链接</t>
+          <t>原 PMID</t>
         </is>
       </c>
       <c r="C1" s="8" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>原标题</t>
         </is>
       </c>
       <c r="D1" s="8" t="inlineStr">
         <is>
-          <t>期刊</t>
+          <t>原刊年</t>
         </is>
       </c>
       <c r="E1" s="8" t="inlineStr">
         <is>
-          <t>标题</t>
+          <t>替代 PMID</t>
         </is>
       </c>
       <c r="F1" s="8" t="inlineStr">
         <is>
-          <t>为什么还缺</t>
+          <t>替代标题</t>
         </is>
       </c>
       <c r="G1" s="8" t="inlineStr">
         <is>
-          <t>要补哪几栏</t>
+          <t>替代刊年</t>
+        </is>
+      </c>
+      <c r="H1" s="8" t="inlineStr">
+        <is>
+          <t>替代后层级/相关度</t>
+        </is>
+      </c>
+      <c r="I1" s="8" t="inlineStr">
+        <is>
+          <t>替换理由</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="40" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>32696389</t>
-        </is>
+    <row r="2" ht="96" customHeight="1">
+      <c r="A2" s="2" t="n">
+        <v>7</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/32696389/</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>2020</v>
+          <t>20201077</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>MicroRNA-29, a key regulator of collagen expression in systemic sclerosis.</t>
+        </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Methods in molecular biology (Clifton, N.J.)</t>
+          <t>Arthritis and rheumatism 2010</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Detection of Multisite Phosphorylation of Intrinsically Disordered Proteins Using Phos-tag SDS-PAGE.</t>
+          <t>40124162</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>MMB 章节；你上传的是 MMB 2141 整卷，未指明章节</t>
+          <t>Ratio of miRNA-29 to miRNA-199 expression coordinates mesenchymal stem cell repair of bleomycin-induced pulmonary injury.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>③关键图 ⑥对照 ⑦效应量 ⑭参考文献</t>
+          <t>Molecular therapy. Nucleic acids 2025</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>T2 / 3（原 T1 / 4）</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>miR-29 机制主体保留（miR-29/miR-199 比值协调 MSC 抗纤维化修复），原发研究、有 collagen 读出；代价是组织从皮肤换成肺（你已有 20971881 肺）。备选 40021656 正好是硬化症皮肤但机制是 TGF-β1/Smad3、miR-29 零提及，故未选。</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="40" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="3" ht="96" customHeight="1">
+      <c r="A3" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>20421885</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/20421885/</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>2010</v>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Metabolic memory and diabetic nephropathy: potential role for epigenetic mechanisms.</t>
+        </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Nature reviews. Nephrology</t>
+          <t>Nature reviews. Nephrology 2010</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Metabolic memory and diabetic nephropathy: potential role for epigenetic mechanisms.</t>
+          <t>41465114</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>不在 PMC，付费墙（Nat Rev 综述）</t>
+          <t>From Metabolic to Epigenetic Memory: The Impact of Hyperglycemia-Induced Epigenetic Signature on Kidney Disease Progression and Complications.</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>③关键图 ⑥对照 ⑦效应量 ⑭参考文献</t>
+          <t>Genes 2025</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>T2 / 3（原 T2 / 3）</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>同为综述、同一命题（高糖诱导的代谢记忆→表观遗传记忆），2025 年版本比 2010 年 Nat Rev Nephrol 更新 15 年文献。</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="40" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>20201077</t>
-        </is>
+    <row r="4" ht="96" customHeight="1">
+      <c r="A4" s="2" t="n">
+        <v>9</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/20201077/</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>2010</v>
+          <t>42622514</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Novel proteomic signatures of stricturing Crohn disease using a treatment-naive cohort.</t>
+        </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Arthritis and rheumatism</t>
+          <t>Inflammatory bowel diseases 2026</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>MicroRNA-29, a key regulator of collagen expression in systemic sclerosis.</t>
+          <t>39977234</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>不在 PMC，付费墙</t>
+          <t>Novel Transcriptomic Signatures in Fibrostenotic Crohn's Disease: Dysregulated Pathways, Promising Biomarkers, and Putative Therapeutic Targets.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>③关键图 ⑥对照 ⑦效应量 ⑭参考文献</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="40" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>42622514</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42622514/</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Inflammatory bowel diseases</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Novel proteomic signatures of stricturing Crohn disease using a treatment-naive cohort.</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>2026 新刊，尚无开放全文</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>③关键图 ⑥对照 ⑦效应量 ⑭参考文献</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="40" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>42763855</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42763855/</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>2027</v>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Methods in molecular biology (Clifton, N.J.)</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Updated Protocols for 3D and 2D Culture and Histological Analysis of Intestinal Organoids.</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>MMB 章节；你上传的是 MMB 3059 整卷，未指明章节</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>③关键图 ⑥对照 ⑦效应量 ⑭参考文献</t>
+          <t>Inflammatory bowel diseases 2025</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>T2 / 3（原 T1 / 3）</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>同一期刊（Inflammatory Bowel Diseases）、同一疾病与同一问题（纤维狭窄型克罗恩的分子标志），把蛋白质组换成转录组。</t>
         </is>
       </c>
     </row>
